--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:H40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,13 +421,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-08</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-08</v>
@@ -461,13 +461,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
@@ -481,13 +481,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יאיר יראי - נתת לי הכל קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
@@ -521,13 +521,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבישי עוזיאל - שני ילדים בבית</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
@@ -581,13 +581,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
@@ -601,13 +601,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>שני אוחיון - על כל אלה קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-07</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
@@ -617,17 +617,23 @@
       </c>
       <c r="F11" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
@@ -637,17 +643,23 @@
       </c>
       <c r="F12" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>עדי עייש - אהובי קאבר</v>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
@@ -657,17 +669,23 @@
       </c>
       <c r="F13" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>נועם דדון - הו מרגנית קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="B14" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
@@ -677,17 +695,23 @@
       </c>
       <c r="F14" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>משה לדני - בואי בשלום קאבר</v>
+        <v>יאיר יראי - נתת לי הכל קאבר</v>
       </c>
       <c r="B15" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
@@ -697,17 +721,23 @@
       </c>
       <c r="F15" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
       </c>
       <c r="B16" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
@@ -717,17 +747,23 @@
       </c>
       <c r="F16" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אלכס - שובי לביתך קאבר</v>
+        <v>אלון מיכאל - אני בא אלייך קאבר</v>
       </c>
       <c r="B17" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
@@ -737,17 +773,23 @@
       </c>
       <c r="F17" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>אילאי ברדה - עוף מוזר קאבר</v>
+        <v>אבישי עוזיאל - שני ילדים בבית</v>
       </c>
       <c r="B18" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -757,17 +799,23 @@
       </c>
       <c r="F18" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
       </c>
       <c r="B19" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -777,17 +825,23 @@
       </c>
       <c r="F19" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אהרון כהן - פרק אחר קאבר</v>
+        <v>שני אוחיון - על כל אלה קאבר</v>
       </c>
       <c r="B20" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -797,17 +851,23 @@
       </c>
       <c r="F20" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אהרון כהן - נשבע קאבר</v>
+        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
       </c>
       <c r="B21" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -817,17 +877,23 @@
       </c>
       <c r="F21" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אהרון כהן - ממעמקים קאבר</v>
+        <v>עדי עייש - אהובי קאבר</v>
       </c>
       <c r="B22" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -837,17 +903,23 @@
       </c>
       <c r="F22" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>אהרון כהן - יסמין קאבר</v>
+        <v>נועם דדון - הו מרגנית קאבר</v>
       </c>
       <c r="B23" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -857,17 +929,23 @@
       </c>
       <c r="F23" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>אהרון כהן - הפרח בגני קאבר</v>
+        <v>משה לדני - בואי בשלום קאבר</v>
       </c>
       <c r="B24" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -877,17 +955,23 @@
       </c>
       <c r="F24" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>אביאל - שפוי בשבילך קאבר</v>
+        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
       </c>
       <c r="B25" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -897,17 +981,23 @@
       </c>
       <c r="F25" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+        <v>אלכס - שובי לביתך קאבר</v>
       </c>
       <c r="B26" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -917,17 +1007,23 @@
       </c>
       <c r="F26" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+        <v>אילאי ברדה - עוף מוזר קאבר</v>
       </c>
       <c r="B27" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -937,17 +1033,23 @@
       </c>
       <c r="F27" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>רונן לוגסי - גודל הכאב קאבר</v>
+        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
       </c>
       <c r="B28" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -957,17 +1059,23 @@
       </c>
       <c r="F28" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>צביקי רנד - אם אשכחך קאבר</v>
+        <v>אהרון כהן - פרק אחר קאבר</v>
       </c>
       <c r="B29" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -977,17 +1085,23 @@
       </c>
       <c r="F29" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+        <v>אהרון כהן - נשבע קאבר</v>
       </c>
       <c r="B30" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -997,31 +1111,277 @@
       </c>
       <c r="F30" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>אהרון כהן - ממעמקים קאבר</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C31" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>אהרון כהן - יסמין קאבר</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C32" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>אהרון כהן - הפרח בגני קאבר</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C33" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>אביאל - שפוי בשבילך קאבר</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C34" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C35" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C36" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>רונן לוגסי - גודל הכאב קאבר</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C37" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>צביקי רנד - אם אשכחך קאבר</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C38" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C39" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
         <v>נתי שקד - אמן קאבר</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B40" t="str">
         <v>2025-12-26</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C40" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
-      <c r="D31" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+      <c r="D40" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:J41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,13 +421,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-08</v>
@@ -441,13 +441,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-08</v>
@@ -457,17 +457,23 @@
       </c>
       <c r="F3" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-08</v>
@@ -477,17 +483,23 @@
       </c>
       <c r="F4" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-08</v>
@@ -497,17 +509,23 @@
       </c>
       <c r="F5" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-08</v>
@@ -517,17 +535,23 @@
       </c>
       <c r="F6" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-08</v>
@@ -537,17 +561,23 @@
       </c>
       <c r="F7" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-08</v>
@@ -557,17 +587,23 @@
       </c>
       <c r="F8" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-08</v>
@@ -577,17 +613,23 @@
       </c>
       <c r="F9" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-08</v>
@@ -597,17 +639,23 @@
       </c>
       <c r="F10" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-08</v>
@@ -627,13 +675,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-07</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-08</v>
@@ -648,18 +696,24 @@
         <v/>
       </c>
       <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-08</v>
@@ -674,18 +728,24 @@
         <v/>
       </c>
       <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-08</v>
@@ -700,18 +760,24 @@
         <v/>
       </c>
       <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>יאיר יראי - נתת לי הכל קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-08</v>
@@ -726,18 +792,24 @@
         <v/>
       </c>
       <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+        <v>יאיר יראי - נתת לי הכל קאבר</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-08</v>
@@ -752,18 +824,24 @@
         <v/>
       </c>
       <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-08</v>
@@ -778,18 +856,24 @@
         <v/>
       </c>
       <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>אבישי עוזיאל - שני ילדים בבית</v>
+        <v>אלון מיכאל - אני בא אלייך קאבר</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -804,18 +888,24 @@
         <v/>
       </c>
       <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+        <v>אבישי עוזיאל - שני ילדים בבית</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -830,18 +920,24 @@
         <v/>
       </c>
       <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>שני אוחיון - על כל אלה קאבר</v>
+        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
       </c>
       <c r="B20" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -856,18 +952,24 @@
         <v/>
       </c>
       <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+        <v>שני אוחיון - על כל אלה קאבר</v>
       </c>
       <c r="B21" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -882,18 +984,24 @@
         <v/>
       </c>
       <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>עדי עייש - אהובי קאבר</v>
+        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
       </c>
       <c r="B22" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -908,18 +1016,24 @@
         <v/>
       </c>
       <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>נועם דדון - הו מרגנית קאבר</v>
+        <v>עדי עייש - אהובי קאבר</v>
       </c>
       <c r="B23" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -934,18 +1048,24 @@
         <v/>
       </c>
       <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>משה לדני - בואי בשלום קאבר</v>
+        <v>נועם דדון - הו מרגנית קאבר</v>
       </c>
       <c r="B24" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -960,18 +1080,24 @@
         <v/>
       </c>
       <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+        <v>משה לדני - בואי בשלום קאבר</v>
       </c>
       <c r="B25" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -986,18 +1112,24 @@
         <v/>
       </c>
       <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אלכס - שובי לביתך קאבר</v>
+        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
       </c>
       <c r="B26" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -1012,18 +1144,24 @@
         <v/>
       </c>
       <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אילאי ברדה - עוף מוזר קאבר</v>
+        <v>אלכס - שובי לביתך קאבר</v>
       </c>
       <c r="B27" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -1038,18 +1176,24 @@
         <v/>
       </c>
       <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+        <v>אילאי ברדה - עוף מוזר קאבר</v>
       </c>
       <c r="B28" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -1064,18 +1208,24 @@
         <v/>
       </c>
       <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>אהרון כהן - פרק אחר קאבר</v>
+        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
       </c>
       <c r="B29" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -1090,18 +1240,24 @@
         <v/>
       </c>
       <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אהרון כהן - נשבע קאבר</v>
+        <v>אהרון כהן - פרק אחר קאבר</v>
       </c>
       <c r="B30" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1116,18 +1272,24 @@
         <v/>
       </c>
       <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>אהרון כהן - ממעמקים קאבר</v>
+        <v>אהרון כהן - נשבע קאבר</v>
       </c>
       <c r="B31" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1142,18 +1304,24 @@
         <v/>
       </c>
       <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>אהרון כהן - יסמין קאבר</v>
+        <v>אהרון כהן - ממעמקים קאבר</v>
       </c>
       <c r="B32" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1168,18 +1336,24 @@
         <v/>
       </c>
       <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>אהרון כהן - הפרח בגני קאבר</v>
+        <v>אהרון כהן - יסמין קאבר</v>
       </c>
       <c r="B33" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1194,18 +1368,24 @@
         <v/>
       </c>
       <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>אביאל - שפוי בשבילך קאבר</v>
+        <v>אהרון כהן - הפרח בגני קאבר</v>
       </c>
       <c r="B34" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1220,18 +1400,24 @@
         <v/>
       </c>
       <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+        <v>אביאל - שפוי בשבילך קאבר</v>
       </c>
       <c r="B35" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1246,18 +1432,24 @@
         <v/>
       </c>
       <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+        <v>אוריאל לנקרי - באתי לגני קאבר</v>
       </c>
       <c r="B36" t="str">
         <v>2025-12-26</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1272,18 +1464,24 @@
         <v/>
       </c>
       <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>רונן לוגסי - גודל הכאב קאבר</v>
+        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
       </c>
       <c r="B37" t="str">
         <v>2025-12-26</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1298,18 +1496,24 @@
         <v/>
       </c>
       <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>צביקי רנד - אם אשכחך קאבר</v>
+        <v>רונן לוגסי - גודל הכאב קאבר</v>
       </c>
       <c r="B38" t="str">
         <v>2025-12-26</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1324,18 +1528,24 @@
         <v/>
       </c>
       <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+        <v>צביקי רנד - אם אשכחך קאבר</v>
       </c>
       <c r="B39" t="str">
         <v>2025-12-26</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1350,38 +1560,82 @@
         <v/>
       </c>
       <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>נתי שקד - אמן קאבר</v>
+        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
       </c>
       <c r="B40" t="str">
         <v>2025-12-26</v>
       </c>
       <c r="C40" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>נתי שקד - אמן קאבר</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C41" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
-      <c r="D40" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
-      <c r="H40" t="str">
+      <c r="D41" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:L57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,16 +421,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -441,439 +441,313 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>יאיר יראי - נתת לי הכל קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
         <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-08</v>
@@ -888,24 +762,18 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אבישי עוזיאל - שני ילדים בבית</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-08</v>
@@ -931,13 +799,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-08</v>
@@ -963,13 +831,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>שני אוחיון - על כל אלה קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B21" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-08</v>
@@ -995,13 +863,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B22" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-08</v>
@@ -1027,13 +895,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>עדי עייש - אהובי קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B23" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-08</v>
@@ -1059,13 +927,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>נועם דדון - הו מרגנית קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B24" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-08</v>
@@ -1091,13 +959,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>משה לדני - בואי בשלום קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B25" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-08</v>
@@ -1123,13 +991,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B26" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-08</v>
@@ -1155,13 +1023,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אלכס - שובי לביתך קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="B27" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-08</v>
@@ -1187,13 +1055,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>אילאי ברדה - עוף מוזר קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="B28" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-07</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-08</v>
@@ -1214,18 +1082,24 @@
         <v/>
       </c>
       <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="B29" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-08</v>
@@ -1246,18 +1120,24 @@
         <v/>
       </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אהרון כהן - פרק אחר קאבר</v>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="B30" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-08</v>
@@ -1278,18 +1158,24 @@
         <v/>
       </c>
       <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>אהרון כהן - נשבע קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="B31" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-08</v>
@@ -1310,18 +1196,24 @@
         <v/>
       </c>
       <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>אהרון כהן - ממעמקים קאבר</v>
+        <v>יאיר יראי - נתת לי הכל קאבר</v>
       </c>
       <c r="B32" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-08</v>
@@ -1342,18 +1234,24 @@
         <v/>
       </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>אהרון כהן - יסמין קאבר</v>
+        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
       </c>
       <c r="B33" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-08</v>
@@ -1374,18 +1272,24 @@
         <v/>
       </c>
       <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>אהרון כהן - הפרח בגני קאבר</v>
+        <v>אלון מיכאל - אני בא אלייך קאבר</v>
       </c>
       <c r="B34" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-08</v>
@@ -1406,18 +1310,24 @@
         <v/>
       </c>
       <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>אביאל - שפוי בשבילך קאבר</v>
+        <v>אבישי עוזיאל - שני ילדים בבית</v>
       </c>
       <c r="B35" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-08</v>
@@ -1438,18 +1348,24 @@
         <v/>
       </c>
       <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
       </c>
       <c r="B36" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-08</v>
@@ -1470,18 +1386,24 @@
         <v/>
       </c>
       <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+        <v>שני אוחיון - על כל אלה קאבר</v>
       </c>
       <c r="B37" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-08</v>
@@ -1502,18 +1424,24 @@
         <v/>
       </c>
       <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>רונן לוגסי - גודל הכאב קאבר</v>
+        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
       </c>
       <c r="B38" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-08</v>
@@ -1534,18 +1462,24 @@
         <v/>
       </c>
       <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>צביקי רנד - אם אשכחך קאבר</v>
+        <v>עדי עייש - אהובי קאבר</v>
       </c>
       <c r="B39" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-08</v>
@@ -1566,18 +1500,24 @@
         <v/>
       </c>
       <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+        <v>נועם דדון - הו מרגנית קאבר</v>
       </c>
       <c r="B40" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-08</v>
@@ -1598,44 +1538,664 @@
         <v/>
       </c>
       <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v>משה לדני - בואי בשלום קאבר</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C41" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C42" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>אלכס - שובי לביתך קאבר</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C43" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>אילאי ברדה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C44" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C45" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>אהרון כהן - פרק אחר קאבר</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C46" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>אהרון כהן - נשבע קאבר</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C47" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>אהרון כהן - ממעמקים קאבר</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C48" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>אהרון כהן - יסמין קאבר</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C49" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>אהרון כהן - הפרח בגני קאבר</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C50" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>אביאל - שפוי בשבילך קאבר</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C51" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C52" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C53" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>רונן לוגסי - גודל הכאב קאבר</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C54" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>צביקי רנד - אם אשכחך קאבר</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C55" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C56" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>נתי שקד - אמן קאבר</v>
       </c>
-      <c r="B41" t="str">
+      <c r="B57" t="str">
         <v>2025-12-26</v>
       </c>
-      <c r="C41" t="str">
+      <c r="C57" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
-      <c r="D41" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
-      <c r="J41" t="str">
+      <c r="D57" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L57"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:P87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,7 +416,22 @@
         <v>תיאור</v>
       </c>
       <c r="F1" t="str">
+        <v>משך</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ערוץ</v>
+      </c>
+      <c r="H1" t="str">
         <v>תגית</v>
+      </c>
+      <c r="I1" t="str">
+        <v>קישור אמן</v>
+      </c>
+      <c r="J1" t="str">
+        <v>קישור אלבום</v>
+      </c>
+      <c r="K1" t="str">
+        <v>שיר - אמן</v>
       </c>
     </row>
     <row r="2">
@@ -427,7 +442,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-15</v>
@@ -436,7 +451,22 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +477,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-15</v>
@@ -456,7 +486,22 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +512,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-15</v>
@@ -476,7 +521,22 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>פארידה - Darixdim Cover</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +547,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-15</v>
@@ -496,7 +556,22 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +582,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-15</v>
@@ -516,7 +591,22 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +617,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-15</v>
@@ -536,7 +626,22 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +652,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-15</v>
@@ -556,7 +661,22 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
     </row>
     <row r="9">
@@ -567,7 +687,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-15</v>
@@ -576,7 +696,22 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
     </row>
     <row r="10">
@@ -587,7 +722,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-15</v>
@@ -596,7 +731,22 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +757,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-15</v>
@@ -616,7 +766,22 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
     </row>
     <row r="12">
@@ -627,7 +792,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-15</v>
@@ -636,7 +801,22 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
     </row>
     <row r="13">
@@ -647,7 +827,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-15</v>
@@ -656,7 +836,22 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
     </row>
     <row r="14">
@@ -667,7 +862,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-15</v>
@@ -676,7 +871,22 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>אלירן עטר - את קאבר</v>
       </c>
     </row>
     <row r="15">
@@ -687,7 +897,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-15</v>
@@ -696,7 +906,22 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>אליקיר - מזל קאבר</v>
       </c>
     </row>
     <row r="16">
@@ -707,7 +932,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-15</v>
@@ -716,7 +941,22 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
     </row>
     <row r="17">
@@ -727,7 +967,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-15</v>
@@ -736,7 +976,22 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
     </row>
     <row r="18">
@@ -747,22 +1002,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
     </row>
     <row r="19">
@@ -773,28 +1037,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
         <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
     </row>
     <row r="20">
@@ -805,28 +1072,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
         <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
     </row>
     <row r="21">
@@ -837,28 +1107,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I21" t="str">
         <v/>
       </c>
       <c r="J21" t="str">
         <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
     </row>
     <row r="22">
@@ -869,28 +1142,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
         <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
     </row>
     <row r="23">
@@ -901,28 +1177,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
         <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
     </row>
     <row r="24">
@@ -933,28 +1212,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
         <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
     </row>
     <row r="25">
@@ -965,28 +1247,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
         <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
     </row>
     <row r="26">
@@ -997,28 +1282,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
         <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
     </row>
     <row r="27">
@@ -1029,28 +1317,31 @@
         <v>2026-01-08</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I27" t="str">
         <v/>
       </c>
       <c r="J27" t="str">
         <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
     </row>
     <row r="28">
@@ -1061,22 +1352,22 @@
         <v>2026-01-07</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1085,10 +1376,7 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
     </row>
     <row r="29">
@@ -1099,22 +1387,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1123,10 +1411,7 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
     </row>
     <row r="30">
@@ -1137,22 +1422,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1161,10 +1446,7 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
+        <v>שי עזאני - גאולה</v>
       </c>
     </row>
     <row r="31">
@@ -1175,22 +1457,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1199,24 +1481,21 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>יאיר יראי - נתת לי הכל קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1234,27 +1513,21 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1272,27 +1545,21 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v/>
-      </c>
-      <c r="K33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1310,27 +1577,21 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v/>
-      </c>
-      <c r="K34" t="str">
-        <v/>
-      </c>
-      <c r="L34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>אבישי עוזיאל - שני ילדים בבית</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1348,27 +1609,21 @@
         <v/>
       </c>
       <c r="J35" t="str">
-        <v/>
-      </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1386,27 +1641,21 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v/>
-      </c>
-      <c r="K36" t="str">
-        <v/>
-      </c>
-      <c r="L36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>שני אוחיון - על כל אלה קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B37" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1424,27 +1673,21 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v/>
-      </c>
-      <c r="K37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B38" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1462,27 +1705,21 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v/>
-      </c>
-      <c r="K38" t="str">
-        <v/>
-      </c>
-      <c r="L38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>עדי עייש - אהובי קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B39" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1500,27 +1737,21 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v/>
-      </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>נועם דדון - הו מרגנית קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B40" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1538,27 +1769,21 @@
         <v/>
       </c>
       <c r="J40" t="str">
-        <v/>
-      </c>
-      <c r="K40" t="str">
-        <v/>
-      </c>
-      <c r="L40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>משה לדני - בואי בשלום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B41" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1576,27 +1801,21 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v/>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B42" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1614,27 +1833,21 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v/>
-      </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
-      <c r="L42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>אלכס - שובי לביתך קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B43" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1652,27 +1865,21 @@
         <v/>
       </c>
       <c r="J43" t="str">
-        <v/>
-      </c>
-      <c r="K43" t="str">
-        <v/>
-      </c>
-      <c r="L43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>אילאי ברדה - עוף מוזר קאבר</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B44" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1690,27 +1897,21 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v/>
-      </c>
-      <c r="K44" t="str">
-        <v/>
-      </c>
-      <c r="L44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B45" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1728,27 +1929,21 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v/>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>אהרון כהן - פרק אחר קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B46" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1766,27 +1961,21 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v/>
-      </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-      <c r="L46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>אהרון כהן - נשבע קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B47" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -1804,24 +1993,18 @@
         <v/>
       </c>
       <c r="J47" t="str">
-        <v/>
-      </c>
-      <c r="K47" t="str">
-        <v/>
-      </c>
-      <c r="L47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>אהרון כהן - ממעמקים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B48" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-08</v>
@@ -1853,13 +2036,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>אהרון כהן - יסמין קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B49" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-08</v>
@@ -1886,18 +2069,24 @@
         <v/>
       </c>
       <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>אהרון כהן - הפרח בגני קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B50" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-08</v>
@@ -1924,18 +2113,24 @@
         <v/>
       </c>
       <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>אביאל - שפוי בשבילך קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-08</v>
@@ -1962,18 +2157,24 @@
         <v/>
       </c>
       <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-08</v>
@@ -2000,18 +2201,24 @@
         <v/>
       </c>
       <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-08</v>
@@ -2038,18 +2245,24 @@
         <v/>
       </c>
       <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>רונן לוגסי - גודל הכאב קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-08</v>
@@ -2076,18 +2289,24 @@
         <v/>
       </c>
       <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>צביקי רנד - אם אשכחך קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-08</v>
@@ -2114,18 +2333,24 @@
         <v/>
       </c>
       <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-08</v>
@@ -2152,50 +2377,1562 @@
         <v/>
       </c>
       <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
+        <v>אבישי רווה - דברי אליי קאבר</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C57" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="C58" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C59" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>שי עזאני - גאולה</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C60" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C61" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>יאיר יראי - נתת לי הכל קאבר</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C62" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C63" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C64" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>אבישי עוזיאל - שני ילדים בבית</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C65" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C66" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>שני אוחיון - על כל אלה קאבר</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C67" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C68" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>עדי עייש - אהובי קאבר</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C69" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>נועם דדון - הו מרגנית קאבר</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C70" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>משה לדני - בואי בשלום קאבר</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C71" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C72" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>אלכס - שובי לביתך קאבר</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C73" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>אילאי ברדה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C74" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C75" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>אהרון כהן - פרק אחר קאבר</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C76" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>אהרון כהן - נשבע קאבר</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C77" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>אהרון כהן - ממעמקים קאבר</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C78" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>אהרון כהן - יסמין קאבר</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C79" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>אהרון כהן - הפרח בגני קאבר</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C80" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>אביאל - שפוי בשבילך קאבר</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C81" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C82" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C83" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>רונן לוגסי - גודל הכאב קאבר</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C84" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>צביקי רנד - אם אשכחך קאבר</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C85" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C86" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>נתי שקד - אמן קאבר</v>
       </c>
-      <c r="B57" t="str">
+      <c r="B87" t="str">
         <v>2025-12-26</v>
       </c>
-      <c r="C57" t="str">
+      <c r="C87" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
-      <c r="D57" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E57" t="str">
-        <v/>
-      </c>
-      <c r="F57" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
-      <c r="I57" t="str">
-        <v/>
-      </c>
-      <c r="J57" t="str">
-        <v/>
-      </c>
-      <c r="K57" t="str">
-        <v/>
-      </c>
-      <c r="L57" t="str">
+      <c r="D87" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:T117"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-15</v>
@@ -466,18 +466,18 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-15</v>
@@ -501,18 +501,18 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-15</v>
@@ -536,18 +536,18 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-15</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-15</v>
@@ -606,18 +606,18 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-15</v>
@@ -641,18 +641,18 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-15</v>
@@ -676,18 +676,18 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-15</v>
@@ -711,18 +711,18 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-15</v>
@@ -746,18 +746,18 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-15</v>
@@ -781,18 +781,18 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-15</v>
@@ -816,18 +816,18 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-15</v>
@@ -851,18 +851,18 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-15</v>
@@ -886,18 +886,18 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-15</v>
@@ -921,18 +921,18 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-15</v>
@@ -956,18 +956,18 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-15</v>
@@ -991,18 +991,18 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-15</v>
@@ -1026,18 +1026,18 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-15</v>
@@ -1061,18 +1061,18 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-15</v>
@@ -1096,18 +1096,18 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-15</v>
@@ -1131,18 +1131,18 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-15</v>
@@ -1166,18 +1166,18 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-15</v>
@@ -1201,18 +1201,18 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-15</v>
@@ -1236,18 +1236,18 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-15</v>
@@ -1271,18 +1271,18 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-15</v>
@@ -1306,18 +1306,18 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-15</v>
@@ -1341,18 +1341,18 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
       </c>
       <c r="B28" t="str">
         <v>2026-01-07</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-15</v>
@@ -1376,18 +1376,18 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
       </c>
       <c r="B29" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-15</v>
@@ -1411,18 +1411,18 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>שי עזאני - גאולה להורדה</v>
       </c>
       <c r="B30" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-15</v>
@@ -1446,18 +1446,18 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>שי עזאני - גאולה להורדה</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
       </c>
       <c r="B31" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-15</v>
@@ -1481,7 +1481,7 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
       </c>
     </row>
     <row r="32">
@@ -1492,7 +1492,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-15</v>
@@ -1501,18 +1501,33 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
         <v/>
       </c>
     </row>
@@ -1524,7 +1539,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-15</v>
@@ -1533,18 +1548,33 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I33" t="str">
         <v/>
       </c>
       <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
         <v/>
       </c>
     </row>
@@ -1556,7 +1586,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-15</v>
@@ -1565,18 +1595,33 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
         <v/>
       </c>
     </row>
@@ -1588,7 +1633,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-15</v>
@@ -1597,18 +1642,33 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
         <v/>
       </c>
     </row>
@@ -1620,7 +1680,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-15</v>
@@ -1629,18 +1689,33 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
         <v/>
       </c>
     </row>
@@ -1652,7 +1727,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-15</v>
@@ -1661,18 +1736,33 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I37" t="str">
         <v/>
       </c>
       <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
         <v/>
       </c>
     </row>
@@ -1684,7 +1774,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-15</v>
@@ -1693,18 +1783,33 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I38" t="str">
         <v/>
       </c>
       <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
         <v/>
       </c>
     </row>
@@ -1716,7 +1821,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-15</v>
@@ -1725,18 +1830,33 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I39" t="str">
         <v/>
       </c>
       <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
         <v/>
       </c>
     </row>
@@ -1748,7 +1868,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-15</v>
@@ -1757,18 +1877,33 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I40" t="str">
         <v/>
       </c>
       <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
         <v/>
       </c>
     </row>
@@ -1780,7 +1915,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-15</v>
@@ -1789,18 +1924,33 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I41" t="str">
         <v/>
       </c>
       <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
         <v/>
       </c>
     </row>
@@ -1812,7 +1962,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-15</v>
@@ -1821,18 +1971,33 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I42" t="str">
         <v/>
       </c>
       <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
         <v/>
       </c>
     </row>
@@ -1844,7 +2009,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-15</v>
@@ -1853,18 +2018,33 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I43" t="str">
         <v/>
       </c>
       <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
         <v/>
       </c>
     </row>
@@ -1876,7 +2056,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-15</v>
@@ -1885,18 +2065,33 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I44" t="str">
         <v/>
       </c>
       <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
         <v/>
       </c>
     </row>
@@ -1908,7 +2103,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-15</v>
@@ -1917,18 +2112,33 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I45" t="str">
         <v/>
       </c>
       <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
         <v/>
       </c>
     </row>
@@ -1940,7 +2150,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-15</v>
@@ -1949,18 +2159,33 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I46" t="str">
         <v/>
       </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
         <v/>
       </c>
     </row>
@@ -1972,7 +2197,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-15</v>
@@ -1981,18 +2206,33 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I47" t="str">
         <v/>
       </c>
       <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
         <v/>
       </c>
     </row>
@@ -2004,22 +2244,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2028,9 +2268,18 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
         <v/>
       </c>
     </row>
@@ -2042,22 +2291,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2066,7 +2315,7 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2075,6 +2324,9 @@
         <v/>
       </c>
       <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
         <v/>
       </c>
     </row>
@@ -2086,22 +2338,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2110,7 +2362,7 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2119,6 +2371,9 @@
         <v/>
       </c>
       <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
         <v/>
       </c>
     </row>
@@ -2130,22 +2385,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2154,7 +2409,7 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2163,6 +2418,9 @@
         <v/>
       </c>
       <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
         <v/>
       </c>
     </row>
@@ -2174,22 +2432,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2198,7 +2456,7 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2207,6 +2465,9 @@
         <v/>
       </c>
       <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
         <v/>
       </c>
     </row>
@@ -2218,22 +2479,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2242,7 +2503,7 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v/>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2251,6 +2512,9 @@
         <v/>
       </c>
       <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
         <v/>
       </c>
     </row>
@@ -2262,22 +2526,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2286,7 +2550,7 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2295,6 +2559,9 @@
         <v/>
       </c>
       <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
         <v/>
       </c>
     </row>
@@ -2306,22 +2573,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2330,7 +2597,7 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2339,6 +2606,9 @@
         <v/>
       </c>
       <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
         <v/>
       </c>
     </row>
@@ -2350,22 +2620,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2374,7 +2644,7 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -2383,6 +2653,9 @@
         <v/>
       </c>
       <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
         <v/>
       </c>
     </row>
@@ -2394,22 +2667,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2418,7 +2691,7 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v/>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -2427,6 +2700,9 @@
         <v/>
       </c>
       <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
         <v/>
       </c>
     </row>
@@ -2438,22 +2714,22 @@
         <v>2026-01-07</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2462,7 +2738,7 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v/>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -2474,9 +2750,6 @@
         <v/>
       </c>
       <c r="O58" t="str">
-        <v/>
-      </c>
-      <c r="P58" t="str">
         <v/>
       </c>
     </row>
@@ -2488,22 +2761,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2512,7 +2785,7 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v/>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -2524,9 +2797,6 @@
         <v/>
       </c>
       <c r="O59" t="str">
-        <v/>
-      </c>
-      <c r="P59" t="str">
         <v/>
       </c>
     </row>
@@ -2538,22 +2808,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2562,7 +2832,7 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -2574,9 +2844,6 @@
         <v/>
       </c>
       <c r="O60" t="str">
-        <v/>
-      </c>
-      <c r="P60" t="str">
         <v/>
       </c>
     </row>
@@ -2588,22 +2855,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2612,7 +2879,7 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -2624,24 +2891,21 @@
         <v/>
       </c>
       <c r="O61" t="str">
-        <v/>
-      </c>
-      <c r="P61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>יאיר יראי - נתת לי הכל קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2671,27 +2935,21 @@
         <v/>
       </c>
       <c r="N62" t="str">
-        <v/>
-      </c>
-      <c r="O62" t="str">
-        <v/>
-      </c>
-      <c r="P62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B63" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2721,27 +2979,21 @@
         <v/>
       </c>
       <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63" t="str">
-        <v/>
-      </c>
-      <c r="P63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2771,27 +3023,21 @@
         <v/>
       </c>
       <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="O64" t="str">
-        <v/>
-      </c>
-      <c r="P64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>אבישי עוזיאל - שני ילדים בבית</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B65" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2821,27 +3067,21 @@
         <v/>
       </c>
       <c r="N65" t="str">
-        <v/>
-      </c>
-      <c r="O65" t="str">
-        <v/>
-      </c>
-      <c r="P65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B66" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2871,27 +3111,21 @@
         <v/>
       </c>
       <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66" t="str">
-        <v/>
-      </c>
-      <c r="P66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>שני אוחיון - על כל אלה קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2921,27 +3155,21 @@
         <v/>
       </c>
       <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67" t="str">
-        <v/>
-      </c>
-      <c r="P67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B68" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2971,27 +3199,21 @@
         <v/>
       </c>
       <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68" t="str">
-        <v/>
-      </c>
-      <c r="P68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>עדי עייש - אהובי קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3021,27 +3243,21 @@
         <v/>
       </c>
       <c r="N69" t="str">
-        <v/>
-      </c>
-      <c r="O69" t="str">
-        <v/>
-      </c>
-      <c r="P69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>נועם דדון - הו מרגנית קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3071,27 +3287,21 @@
         <v/>
       </c>
       <c r="N70" t="str">
-        <v/>
-      </c>
-      <c r="O70" t="str">
-        <v/>
-      </c>
-      <c r="P70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>משה לדני - בואי בשלום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3121,27 +3331,21 @@
         <v/>
       </c>
       <c r="N71" t="str">
-        <v/>
-      </c>
-      <c r="O71" t="str">
-        <v/>
-      </c>
-      <c r="P71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B72" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3171,27 +3375,21 @@
         <v/>
       </c>
       <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="O72" t="str">
-        <v/>
-      </c>
-      <c r="P72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>אלכס - שובי לביתך קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B73" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3221,27 +3419,21 @@
         <v/>
       </c>
       <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="O73" t="str">
-        <v/>
-      </c>
-      <c r="P73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>אילאי ברדה - עוף מוזר קאבר</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B74" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3271,27 +3463,21 @@
         <v/>
       </c>
       <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74" t="str">
-        <v/>
-      </c>
-      <c r="P74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B75" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3321,27 +3507,21 @@
         <v/>
       </c>
       <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="O75" t="str">
-        <v/>
-      </c>
-      <c r="P75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>אהרון כהן - פרק אחר קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3371,27 +3551,21 @@
         <v/>
       </c>
       <c r="N76" t="str">
-        <v/>
-      </c>
-      <c r="O76" t="str">
-        <v/>
-      </c>
-      <c r="P76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>אהרון כהן - נשבע קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3421,24 +3595,18 @@
         <v/>
       </c>
       <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="O77" t="str">
-        <v/>
-      </c>
-      <c r="P77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>אהרון כהן - ממעמקים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B78" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-08</v>
@@ -3482,13 +3650,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>אהרון כהן - יסמין קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B79" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-08</v>
@@ -3527,18 +3695,24 @@
         <v/>
       </c>
       <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>אהרון כהן - הפרח בגני קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B80" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-08</v>
@@ -3577,18 +3751,24 @@
         <v/>
       </c>
       <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>אביאל - שפוי בשבילך קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B81" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-08</v>
@@ -3627,18 +3807,24 @@
         <v/>
       </c>
       <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B82" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-08</v>
@@ -3677,18 +3863,24 @@
         <v/>
       </c>
       <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B83" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-08</v>
@@ -3727,18 +3919,24 @@
         <v/>
       </c>
       <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>רונן לוגסי - גודל הכאב קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-08</v>
@@ -3777,18 +3975,24 @@
         <v/>
       </c>
       <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>צביקי רנד - אם אשכחך קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
@@ -3827,18 +4031,24 @@
         <v/>
       </c>
       <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
@@ -3877,62 +4087,1934 @@
         <v/>
       </c>
       <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>אבישי רווה - דברי אליי קאבר</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C87" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="C88" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+      <c r="T88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C89" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+      <c r="T89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>שי עזאני - גאולה</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C90" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+      <c r="T90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C91" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+      <c r="T91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>יאיר יראי - נתת לי הכל קאבר</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C92" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C93" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+      <c r="T93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C94" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>אבישי עוזיאל - שני ילדים בבית</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C95" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C96" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>שני אוחיון - על כל אלה קאבר</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C97" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+      <c r="T97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C98" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>עדי עייש - אהובי קאבר</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C99" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>נועם דדון - הו מרגנית קאבר</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C100" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>משה לדני - בואי בשלום קאבר</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C101" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C102" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>אלכס - שובי לביתך קאבר</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C103" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>אילאי ברדה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C104" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C105" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>אהרון כהן - פרק אחר קאבר</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C106" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>אהרון כהן - נשבע קאבר</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C107" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>אהרון כהן - ממעמקים קאבר</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C108" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>אהרון כהן - יסמין קאבר</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C109" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>אהרון כהן - הפרח בגני קאבר</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C110" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>אביאל - שפוי בשבילך קאבר</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C111" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C112" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C113" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>רונן לוגסי - גודל הכאב קאבר</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C114" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>צביקי רנד - אם אשכחך קאבר</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C115" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C116" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v/>
+      </c>
+      <c r="T116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
         <v>נתי שקד - אמן קאבר</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B117" t="str">
         <v>2025-12-26</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C117" t="str">
         <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
-      <c r="D87" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="E87" t="str">
-        <v/>
-      </c>
-      <c r="F87" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="G87" t="str">
-        <v/>
-      </c>
-      <c r="H87" t="str">
-        <v/>
-      </c>
-      <c r="I87" t="str">
-        <v/>
-      </c>
-      <c r="J87" t="str">
-        <v/>
-      </c>
-      <c r="K87" t="str">
-        <v/>
-      </c>
-      <c r="L87" t="str">
-        <v/>
-      </c>
-      <c r="M87" t="str">
-        <v/>
-      </c>
-      <c r="N87" t="str">
-        <v/>
-      </c>
-      <c r="O87" t="str">
-        <v/>
-      </c>
-      <c r="P87" t="str">
+      <c r="D117" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+      <c r="T117" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T117"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T117"/>
+  <dimension ref="A1:X124"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -466,21 +466,21 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -501,21 +501,21 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -536,21 +536,21 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -571,21 +571,21 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -606,21 +606,21 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -641,21 +641,21 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -676,18 +676,18 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-15</v>
@@ -711,18 +711,30 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-15</v>
@@ -746,18 +758,30 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-15</v>
@@ -781,18 +805,30 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ברטין - שביל האושר קאבר להורדה</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-15</v>
@@ -816,18 +852,30 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>ברטין - שביל האושר קאבר להורדה</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-15</v>
@@ -851,18 +899,30 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אלירן עטר - את קאבר להורדה</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-15</v>
@@ -886,18 +946,30 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>אלירן עטר - את קאבר להורדה</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אליקיר - מזל קאבר להורדה</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-15</v>
@@ -921,18 +993,30 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>אליקיר - מזל קאבר להורדה</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-15</v>
@@ -956,18 +1040,30 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-15</v>
@@ -991,18 +1087,30 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-15</v>
@@ -1026,18 +1134,30 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-15</v>
@@ -1061,18 +1181,30 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-15</v>
@@ -1096,18 +1228,30 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-15</v>
@@ -1131,18 +1275,30 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-15</v>
@@ -1166,18 +1322,30 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-15</v>
@@ -1201,18 +1369,30 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>משה סונה - הינך יפה קאבר להורדה</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-15</v>
@@ -1236,18 +1416,30 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>משה סונה - הינך יפה קאבר להורדה</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-15</v>
@@ -1271,18 +1463,30 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-15</v>
@@ -1306,18 +1510,30 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-15</v>
@@ -1341,18 +1557,30 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-15</v>
@@ -1376,18 +1604,30 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-15</v>
@@ -1411,18 +1651,30 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>שי עזאני - גאולה להורדה</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-15</v>
@@ -1446,18 +1698,30 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>שי עזאני - גאולה להורדה</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-15</v>
@@ -1481,18 +1745,30 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-15</v>
@@ -1516,7 +1792,7 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1533,13 +1809,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-15</v>
@@ -1563,7 +1839,7 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1580,13 +1856,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-15</v>
@@ -1610,7 +1886,7 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1627,13 +1903,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-07</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-15</v>
@@ -1657,7 +1933,7 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -1674,13 +1950,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-15</v>
@@ -1704,7 +1980,7 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -1721,13 +1997,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>שי עזאני - גאולה להורדה</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-15</v>
@@ -1751,7 +2027,7 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>שי עזאני - גאולה להורדה</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -1768,13 +2044,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-15</v>
@@ -1798,7 +2074,7 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -1815,13 +2091,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B39" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-15</v>
@@ -1845,7 +2121,7 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -1857,18 +2133,30 @@
         <v/>
       </c>
       <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B40" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-15</v>
@@ -1892,7 +2180,7 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -1904,18 +2192,30 @@
         <v/>
       </c>
       <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B41" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-15</v>
@@ -1939,7 +2239,7 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -1951,18 +2251,30 @@
         <v/>
       </c>
       <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B42" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-15</v>
@@ -1986,7 +2298,7 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -1998,18 +2310,30 @@
         <v/>
       </c>
       <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B43" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-15</v>
@@ -2033,7 +2357,7 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2045,18 +2369,30 @@
         <v/>
       </c>
       <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B44" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-15</v>
@@ -2080,7 +2416,7 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2092,18 +2428,30 @@
         <v/>
       </c>
       <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+      <c r="S44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B45" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-15</v>
@@ -2127,7 +2475,7 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2139,18 +2487,30 @@
         <v/>
       </c>
       <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v/>
+      </c>
+      <c r="S45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B46" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-15</v>
@@ -2174,7 +2534,7 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2186,18 +2546,30 @@
         <v/>
       </c>
       <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+      <c r="S46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B47" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-15</v>
@@ -2221,7 +2593,7 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2233,18 +2605,30 @@
         <v/>
       </c>
       <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
+        <v/>
+      </c>
+      <c r="S47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-15</v>
@@ -2268,7 +2652,7 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2280,18 +2664,30 @@
         <v/>
       </c>
       <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v/>
+      </c>
+      <c r="S48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-15</v>
@@ -2315,7 +2711,7 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2327,18 +2723,30 @@
         <v/>
       </c>
       <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
+        <v/>
+      </c>
+      <c r="S49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-15</v>
@@ -2362,7 +2770,7 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2374,18 +2782,30 @@
         <v/>
       </c>
       <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+      <c r="S50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-15</v>
@@ -2409,7 +2829,7 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2421,18 +2841,30 @@
         <v/>
       </c>
       <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+      <c r="S51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-15</v>
@@ -2456,7 +2888,7 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2468,18 +2900,30 @@
         <v/>
       </c>
       <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-15</v>
@@ -2503,7 +2947,7 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2515,18 +2959,30 @@
         <v/>
       </c>
       <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-15</v>
@@ -2550,7 +3006,7 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2562,18 +3018,30 @@
         <v/>
       </c>
       <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B55" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-15</v>
@@ -2597,7 +3065,7 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2609,18 +3077,30 @@
         <v/>
       </c>
       <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B56" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-15</v>
@@ -2644,7 +3124,7 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -2656,18 +3136,30 @@
         <v/>
       </c>
       <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B57" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-15</v>
@@ -2691,7 +3183,7 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -2703,18 +3195,30 @@
         <v/>
       </c>
       <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B58" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-15</v>
@@ -2738,7 +3242,7 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -2750,18 +3254,30 @@
         <v/>
       </c>
       <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B59" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-15</v>
@@ -2785,7 +3301,7 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -2797,18 +3313,30 @@
         <v/>
       </c>
       <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B60" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-15</v>
@@ -2832,7 +3360,7 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -2844,18 +3372,30 @@
         <v/>
       </c>
       <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-15</v>
@@ -2879,7 +3419,7 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -2891,18 +3431,30 @@
         <v/>
       </c>
       <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-15</v>
@@ -2911,13 +3463,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2926,7 +3478,7 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v/>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -2935,18 +3487,33 @@
         <v/>
       </c>
       <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B63" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-15</v>
@@ -2955,13 +3522,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2970,7 +3537,7 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v/>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -2979,18 +3546,33 @@
         <v/>
       </c>
       <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-15</v>
@@ -2999,13 +3581,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -3014,7 +3596,7 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v/>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3023,18 +3605,33 @@
         <v/>
       </c>
       <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="B65" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-07</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-15</v>
@@ -3043,13 +3640,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -3058,7 +3655,7 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v/>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3067,18 +3664,33 @@
         <v/>
       </c>
       <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="B66" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-15</v>
@@ -3087,13 +3699,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -3102,7 +3714,7 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v/>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3111,18 +3723,33 @@
         <v/>
       </c>
       <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="B67" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-15</v>
@@ -3131,13 +3758,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -3146,7 +3773,7 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v/>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3155,18 +3782,33 @@
         <v/>
       </c>
       <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="B68" t="str">
-        <v>2026-01-13</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-15</v>
@@ -3175,13 +3817,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -3190,7 +3832,7 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v/>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3199,18 +3841,33 @@
         <v/>
       </c>
       <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B69" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-15</v>
@@ -3245,16 +3902,28 @@
       <c r="N69" t="str">
         <v/>
       </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B70" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-15</v>
@@ -3289,16 +3958,28 @@
       <c r="N70" t="str">
         <v/>
       </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B71" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-15</v>
@@ -3333,16 +4014,28 @@
       <c r="N71" t="str">
         <v/>
       </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B72" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-15</v>
@@ -3377,16 +4070,28 @@
       <c r="N72" t="str">
         <v/>
       </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B73" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-15</v>
@@ -3421,16 +4126,28 @@
       <c r="N73" t="str">
         <v/>
       </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B74" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-15</v>
@@ -3465,16 +4182,28 @@
       <c r="N74" t="str">
         <v/>
       </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B75" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-15</v>
@@ -3509,16 +4238,28 @@
       <c r="N75" t="str">
         <v/>
       </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B76" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-15</v>
@@ -3553,16 +4294,28 @@
       <c r="N76" t="str">
         <v/>
       </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B77" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-15</v>
@@ -3597,19 +4350,31 @@
       <c r="N77" t="str">
         <v/>
       </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B78" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3645,21 +4410,27 @@
         <v/>
       </c>
       <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B79" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3706,16 +4477,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B80" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3762,16 +4533,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B81" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3818,16 +4589,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B82" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3874,16 +4645,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B83" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3930,16 +4701,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B84" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3986,13 +4757,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B85" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-08</v>
@@ -4039,16 +4810,22 @@
       <c r="R85" t="str">
         <v/>
       </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+      <c r="T85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B86" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-08</v>
@@ -4095,16 +4872,28 @@
       <c r="R86" t="str">
         <v/>
       </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+      <c r="T86" t="str">
+        <v/>
+      </c>
+      <c r="U86" t="str">
+        <v/>
+      </c>
+      <c r="V86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B87" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-08</v>
@@ -4151,16 +4940,28 @@
       <c r="R87" t="str">
         <v/>
       </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+      <c r="T87" t="str">
+        <v/>
+      </c>
+      <c r="U87" t="str">
+        <v/>
+      </c>
+      <c r="V87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B88" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-08</v>
@@ -4213,16 +5014,22 @@
       <c r="T88" t="str">
         <v/>
       </c>
+      <c r="U88" t="str">
+        <v/>
+      </c>
+      <c r="V88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B89" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-08</v>
@@ -4275,16 +5082,22 @@
       <c r="T89" t="str">
         <v/>
       </c>
+      <c r="U89" t="str">
+        <v/>
+      </c>
+      <c r="V89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B90" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-08</v>
@@ -4337,16 +5150,22 @@
       <c r="T90" t="str">
         <v/>
       </c>
+      <c r="U90" t="str">
+        <v/>
+      </c>
+      <c r="V90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B91" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-08</v>
@@ -4399,16 +5218,22 @@
       <c r="T91" t="str">
         <v/>
       </c>
+      <c r="U91" t="str">
+        <v/>
+      </c>
+      <c r="V91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>יאיר יראי - נתת לי הכל קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B92" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-08</v>
@@ -4461,16 +5286,22 @@
       <c r="T92" t="str">
         <v/>
       </c>
+      <c r="U92" t="str">
+        <v/>
+      </c>
+      <c r="V92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B93" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-08</v>
@@ -4523,16 +5354,22 @@
       <c r="T93" t="str">
         <v/>
       </c>
+      <c r="U93" t="str">
+        <v/>
+      </c>
+      <c r="V93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="B94" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-08</v>
@@ -4585,16 +5422,22 @@
       <c r="T94" t="str">
         <v/>
       </c>
+      <c r="U94" t="str">
+        <v/>
+      </c>
+      <c r="V94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>אבישי עוזיאל - שני ילדים בבית</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="B95" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-07</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-08</v>
@@ -4647,16 +5490,28 @@
       <c r="T95" t="str">
         <v/>
       </c>
+      <c r="U95" t="str">
+        <v/>
+      </c>
+      <c r="V95" t="str">
+        <v/>
+      </c>
+      <c r="W95" t="str">
+        <v/>
+      </c>
+      <c r="X95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="B96" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-08</v>
@@ -4709,16 +5564,28 @@
       <c r="T96" t="str">
         <v/>
       </c>
+      <c r="U96" t="str">
+        <v/>
+      </c>
+      <c r="V96" t="str">
+        <v/>
+      </c>
+      <c r="W96" t="str">
+        <v/>
+      </c>
+      <c r="X96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>שני אוחיון - על כל אלה קאבר</v>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C97" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-08</v>
@@ -4771,16 +5638,28 @@
       <c r="T97" t="str">
         <v/>
       </c>
+      <c r="U97" t="str">
+        <v/>
+      </c>
+      <c r="V97" t="str">
+        <v/>
+      </c>
+      <c r="W97" t="str">
+        <v/>
+      </c>
+      <c r="X97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C98" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-08</v>
@@ -4833,16 +5712,28 @@
       <c r="T98" t="str">
         <v/>
       </c>
+      <c r="U98" t="str">
+        <v/>
+      </c>
+      <c r="V98" t="str">
+        <v/>
+      </c>
+      <c r="W98" t="str">
+        <v/>
+      </c>
+      <c r="X98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>עדי עייש - אהובי קאבר</v>
+        <v>יאיר יראי - נתת לי הכל קאבר</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C99" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-08</v>
@@ -4895,16 +5786,28 @@
       <c r="T99" t="str">
         <v/>
       </c>
+      <c r="U99" t="str">
+        <v/>
+      </c>
+      <c r="V99" t="str">
+        <v/>
+      </c>
+      <c r="W99" t="str">
+        <v/>
+      </c>
+      <c r="X99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>נועם דדון - הו מרגנית קאבר</v>
+        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C100" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-08</v>
@@ -4957,16 +5860,28 @@
       <c r="T100" t="str">
         <v/>
       </c>
+      <c r="U100" t="str">
+        <v/>
+      </c>
+      <c r="V100" t="str">
+        <v/>
+      </c>
+      <c r="W100" t="str">
+        <v/>
+      </c>
+      <c r="X100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>משה לדני - בואי בשלום קאבר</v>
+        <v>אלון מיכאל - אני בא אלייך קאבר</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C101" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-08</v>
@@ -5019,16 +5934,28 @@
       <c r="T101" t="str">
         <v/>
       </c>
+      <c r="U101" t="str">
+        <v/>
+      </c>
+      <c r="V101" t="str">
+        <v/>
+      </c>
+      <c r="W101" t="str">
+        <v/>
+      </c>
+      <c r="X101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+        <v>אבישי עוזיאל - שני ילדים בבית</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C102" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-08</v>
@@ -5081,16 +6008,28 @@
       <c r="T102" t="str">
         <v/>
       </c>
+      <c r="U102" t="str">
+        <v/>
+      </c>
+      <c r="V102" t="str">
+        <v/>
+      </c>
+      <c r="W102" t="str">
+        <v/>
+      </c>
+      <c r="X102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>אלכס - שובי לביתך קאבר</v>
+        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-02</v>
       </c>
       <c r="C103" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-08</v>
@@ -5143,16 +6082,28 @@
       <c r="T103" t="str">
         <v/>
       </c>
+      <c r="U103" t="str">
+        <v/>
+      </c>
+      <c r="V103" t="str">
+        <v/>
+      </c>
+      <c r="W103" t="str">
+        <v/>
+      </c>
+      <c r="X103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>אילאי ברדה - עוף מוזר קאבר</v>
+        <v>שני אוחיון - על כל אלה קאבר</v>
       </c>
       <c r="B104" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C104" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-08</v>
@@ -5205,16 +6156,28 @@
       <c r="T104" t="str">
         <v/>
       </c>
+      <c r="U104" t="str">
+        <v/>
+      </c>
+      <c r="V104" t="str">
+        <v/>
+      </c>
+      <c r="W104" t="str">
+        <v/>
+      </c>
+      <c r="X104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
       </c>
       <c r="B105" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C105" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-08</v>
@@ -5267,16 +6230,28 @@
       <c r="T105" t="str">
         <v/>
       </c>
+      <c r="U105" t="str">
+        <v/>
+      </c>
+      <c r="V105" t="str">
+        <v/>
+      </c>
+      <c r="W105" t="str">
+        <v/>
+      </c>
+      <c r="X105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>אהרון כהן - פרק אחר קאבר</v>
+        <v>עדי עייש - אהובי קאבר</v>
       </c>
       <c r="B106" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C106" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-08</v>
@@ -5329,16 +6304,28 @@
       <c r="T106" t="str">
         <v/>
       </c>
+      <c r="U106" t="str">
+        <v/>
+      </c>
+      <c r="V106" t="str">
+        <v/>
+      </c>
+      <c r="W106" t="str">
+        <v/>
+      </c>
+      <c r="X106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>אהרון כהן - נשבע קאבר</v>
+        <v>נועם דדון - הו מרגנית קאבר</v>
       </c>
       <c r="B107" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C107" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-08</v>
@@ -5391,16 +6378,28 @@
       <c r="T107" t="str">
         <v/>
       </c>
+      <c r="U107" t="str">
+        <v/>
+      </c>
+      <c r="V107" t="str">
+        <v/>
+      </c>
+      <c r="W107" t="str">
+        <v/>
+      </c>
+      <c r="X107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>אהרון כהן - ממעמקים קאבר</v>
+        <v>משה לדני - בואי בשלום קאבר</v>
       </c>
       <c r="B108" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C108" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-08</v>
@@ -5453,16 +6452,28 @@
       <c r="T108" t="str">
         <v/>
       </c>
+      <c r="U108" t="str">
+        <v/>
+      </c>
+      <c r="V108" t="str">
+        <v/>
+      </c>
+      <c r="W108" t="str">
+        <v/>
+      </c>
+      <c r="X108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>אהרון כהן - יסמין קאבר</v>
+        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
       </c>
       <c r="B109" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C109" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-08</v>
@@ -5515,16 +6526,28 @@
       <c r="T109" t="str">
         <v/>
       </c>
+      <c r="U109" t="str">
+        <v/>
+      </c>
+      <c r="V109" t="str">
+        <v/>
+      </c>
+      <c r="W109" t="str">
+        <v/>
+      </c>
+      <c r="X109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>אהרון כהן - הפרח בגני קאבר</v>
+        <v>אלכס - שובי לביתך קאבר</v>
       </c>
       <c r="B110" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C110" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-08</v>
@@ -5577,16 +6600,28 @@
       <c r="T110" t="str">
         <v/>
       </c>
+      <c r="U110" t="str">
+        <v/>
+      </c>
+      <c r="V110" t="str">
+        <v/>
+      </c>
+      <c r="W110" t="str">
+        <v/>
+      </c>
+      <c r="X110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>אביאל - שפוי בשבילך קאבר</v>
+        <v>אילאי ברדה - עוף מוזר קאבר</v>
       </c>
       <c r="B111" t="str">
         <v>2025-12-30</v>
       </c>
       <c r="C111" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-08</v>
@@ -5639,16 +6674,28 @@
       <c r="T111" t="str">
         <v/>
       </c>
+      <c r="U111" t="str">
+        <v/>
+      </c>
+      <c r="V111" t="str">
+        <v/>
+      </c>
+      <c r="W111" t="str">
+        <v/>
+      </c>
+      <c r="X111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
       </c>
       <c r="B112" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C112" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-08</v>
@@ -5701,16 +6748,28 @@
       <c r="T112" t="str">
         <v/>
       </c>
+      <c r="U112" t="str">
+        <v/>
+      </c>
+      <c r="V112" t="str">
+        <v/>
+      </c>
+      <c r="W112" t="str">
+        <v/>
+      </c>
+      <c r="X112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+        <v>אהרון כהן - פרק אחר קאבר</v>
       </c>
       <c r="B113" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C113" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-08</v>
@@ -5763,16 +6822,28 @@
       <c r="T113" t="str">
         <v/>
       </c>
+      <c r="U113" t="str">
+        <v/>
+      </c>
+      <c r="V113" t="str">
+        <v/>
+      </c>
+      <c r="W113" t="str">
+        <v/>
+      </c>
+      <c r="X113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>רונן לוגסי - גודל הכאב קאבר</v>
+        <v>אהרון כהן - נשבע קאבר</v>
       </c>
       <c r="B114" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C114" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-08</v>
@@ -5825,16 +6896,28 @@
       <c r="T114" t="str">
         <v/>
       </c>
+      <c r="U114" t="str">
+        <v/>
+      </c>
+      <c r="V114" t="str">
+        <v/>
+      </c>
+      <c r="W114" t="str">
+        <v/>
+      </c>
+      <c r="X114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>צביקי רנד - אם אשכחך קאבר</v>
+        <v>אהרון כהן - ממעמקים קאבר</v>
       </c>
       <c r="B115" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C115" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-08</v>
@@ -5887,16 +6970,28 @@
       <c r="T115" t="str">
         <v/>
       </c>
+      <c r="U115" t="str">
+        <v/>
+      </c>
+      <c r="V115" t="str">
+        <v/>
+      </c>
+      <c r="W115" t="str">
+        <v/>
+      </c>
+      <c r="X115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+        <v>אהרון כהן - יסמין קאבר</v>
       </c>
       <c r="B116" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C116" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-08</v>
@@ -5949,16 +7044,28 @@
       <c r="T116" t="str">
         <v/>
       </c>
+      <c r="U116" t="str">
+        <v/>
+      </c>
+      <c r="V116" t="str">
+        <v/>
+      </c>
+      <c r="W116" t="str">
+        <v/>
+      </c>
+      <c r="X116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>נתי שקד - אמן קאבר</v>
+        <v>אהרון כהן - הפרח בגני קאבר</v>
       </c>
       <c r="B117" t="str">
-        <v>2025-12-26</v>
+        <v>2025-12-30</v>
       </c>
       <c r="C117" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-08</v>
@@ -6011,10 +7118,540 @@
       <c r="T117" t="str">
         <v/>
       </c>
+      <c r="U117" t="str">
+        <v/>
+      </c>
+      <c r="V117" t="str">
+        <v/>
+      </c>
+      <c r="W117" t="str">
+        <v/>
+      </c>
+      <c r="X117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>אביאל - שפוי בשבילך קאבר</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C118" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+      <c r="T118" t="str">
+        <v/>
+      </c>
+      <c r="U118" t="str">
+        <v/>
+      </c>
+      <c r="V118" t="str">
+        <v/>
+      </c>
+      <c r="W118" t="str">
+        <v/>
+      </c>
+      <c r="X118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C119" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D119" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119" t="str">
+        <v/>
+      </c>
+      <c r="V119" t="str">
+        <v/>
+      </c>
+      <c r="W119" t="str">
+        <v/>
+      </c>
+      <c r="X119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C120" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120" t="str">
+        <v/>
+      </c>
+      <c r="V120" t="str">
+        <v/>
+      </c>
+      <c r="W120" t="str">
+        <v/>
+      </c>
+      <c r="X120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>רונן לוגסי - גודל הכאב קאבר</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C121" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v/>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+      <c r="U121" t="str">
+        <v/>
+      </c>
+      <c r="V121" t="str">
+        <v/>
+      </c>
+      <c r="W121" t="str">
+        <v/>
+      </c>
+      <c r="X121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>צביקי רנד - אם אשכחך קאבר</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C122" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v/>
+      </c>
+      <c r="T122" t="str">
+        <v/>
+      </c>
+      <c r="U122" t="str">
+        <v/>
+      </c>
+      <c r="V122" t="str">
+        <v/>
+      </c>
+      <c r="W122" t="str">
+        <v/>
+      </c>
+      <c r="X122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C123" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+      <c r="T123" t="str">
+        <v/>
+      </c>
+      <c r="U123" t="str">
+        <v/>
+      </c>
+      <c r="V123" t="str">
+        <v/>
+      </c>
+      <c r="W123" t="str">
+        <v/>
+      </c>
+      <c r="X123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>נתי שקד - אמן קאבר</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C124" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+      <c r="U124" t="str">
+        <v/>
+      </c>
+      <c r="V124" t="str">
+        <v/>
+      </c>
+      <c r="W124" t="str">
+        <v/>
+      </c>
+      <c r="X124" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X124"/>
+  <dimension ref="A1:AB154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=55bf5229479141598ad934265526d81a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -466,18 +466,18 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=55bf5229479141598ad934265526d81a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -501,18 +501,18 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=55bf5229479141598ad934265526d81a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -536,18 +536,18 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=55bf5229479141598ad934265526d81a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=55bf5229479141598ad934265526d81a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -606,18 +606,18 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=55bf5229479141598ad934265526d81a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -641,18 +641,18 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>איימי - אהבה רעילה קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=55bf5229479141598ad934265526d81a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -676,21 +676,21 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>איימי - אהבה רעילה קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -711,33 +711,21 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -758,33 +746,21 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -805,33 +781,21 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
+        <v>פארידה - Darixdim Cover</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -852,33 +816,21 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -899,33 +851,21 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -946,33 +886,21 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -993,33 +921,21 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1040,33 +956,21 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1087,33 +991,21 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1134,33 +1026,21 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ברטין - שביל האושר קאבר להורדה</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1181,33 +1061,21 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>ברטין - שביל האושר קאבר להורדה</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1228,33 +1096,21 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <v/>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אלירן עטר - את קאבר להורדה</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1275,33 +1131,21 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>אלירן עטר - את קאבר להורדה</v>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
+        <v>אלירן עטר - את קאבר</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אליקיר - מזל קאבר להורדה</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1322,33 +1166,21 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>אליקיר - מזל קאבר להורדה</v>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
+        <v>אליקיר - מזל קאבר</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1369,33 +1201,21 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1416,33 +1236,21 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1463,33 +1271,21 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1510,33 +1306,21 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1557,33 +1341,21 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v/>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B28" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1604,33 +1376,21 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <v/>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B29" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1651,33 +1411,21 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <v/>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B30" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1698,33 +1446,21 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <v/>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>משה סונה - הינך יפה קאבר להורדה</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B31" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b233deb1707699b7a5fa526d52dba17c</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1745,33 +1481,21 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>משה סונה - הינך יפה קאבר להורדה</v>
-      </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31" t="str">
-        <v/>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1792,7 +1516,7 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1809,16 +1533,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1839,7 +1563,7 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1856,16 +1580,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1886,7 +1610,7 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1903,16 +1627,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1933,7 +1657,7 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -1950,16 +1674,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1980,7 +1704,7 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -1997,16 +1721,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>שי עזאני - גאולה להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -2027,7 +1751,7 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>שי עזאני - גאולה להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2044,16 +1768,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-16</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=881f499716cf30725fab277034b55fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=55bf5229479141598ad934265526d81a</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-15</v>
+        <v>2026-01-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -2074,7 +1798,7 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2091,13 +1815,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
       <c r="B39" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-15</v>
@@ -2121,7 +1845,7 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2150,13 +1874,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
       <c r="B40" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-15</v>
@@ -2180,7 +1904,7 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2209,13 +1933,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
       </c>
       <c r="B41" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-15</v>
@@ -2239,7 +1963,7 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2268,13 +1992,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
       <c r="B42" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-15</v>
@@ -2298,7 +2022,7 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2327,13 +2051,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
       <c r="B43" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-15</v>
@@ -2357,7 +2081,7 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2386,13 +2110,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
       <c r="B44" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-15</v>
@@ -2416,7 +2140,7 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2445,13 +2169,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
       <c r="B45" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-15</v>
@@ -2475,7 +2199,7 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2504,13 +2228,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
       <c r="B46" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-15</v>
@@ -2534,7 +2258,7 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2563,13 +2287,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
       <c r="B47" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-15</v>
@@ -2593,7 +2317,7 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2622,13 +2346,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
       <c r="B48" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-15</v>
@@ -2652,7 +2376,7 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2681,13 +2405,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
       <c r="B49" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-15</v>
@@ -2711,7 +2435,7 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2740,13 +2464,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
       </c>
       <c r="B50" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-15</v>
@@ -2770,7 +2494,7 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2799,13 +2523,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
       </c>
       <c r="B51" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-15</v>
@@ -2829,7 +2553,7 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2858,13 +2582,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
       </c>
       <c r="B52" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-15</v>
@@ -2888,7 +2612,7 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2917,13 +2641,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
       </c>
       <c r="B53" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-15</v>
@@ -2947,7 +2671,7 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2976,13 +2700,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
       </c>
       <c r="B54" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-15</v>
@@ -3006,7 +2730,7 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -3035,13 +2759,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
       </c>
       <c r="B55" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-15</v>
@@ -3065,7 +2789,7 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -3094,13 +2818,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
       </c>
       <c r="B56" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-15</v>
@@ -3124,7 +2848,7 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -3153,13 +2877,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
       </c>
       <c r="B57" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-15</v>
@@ -3183,7 +2907,7 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -3212,13 +2936,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
       </c>
       <c r="B58" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-15</v>
@@ -3242,7 +2966,7 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -3271,13 +2995,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
       </c>
       <c r="B59" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-15</v>
@@ -3301,7 +3025,7 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3330,13 +3054,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
       </c>
       <c r="B60" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-15</v>
@@ -3360,7 +3084,7 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3389,13 +3113,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
       </c>
       <c r="B61" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-15</v>
@@ -3419,7 +3143,7 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3448,13 +3172,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
       </c>
       <c r="B62" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-15</v>
@@ -3478,7 +3202,7 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>משה ברששת - יש בך הכל קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר להורדה</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3507,13 +3231,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
       </c>
       <c r="B63" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-15</v>
@@ -3537,7 +3261,7 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>אורי אוחיון - לב שבור קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר להורדה</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3566,13 +3290,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
       </c>
       <c r="B64" t="str">
         <v>2026-01-08</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-15</v>
@@ -3596,7 +3320,7 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>אבישי רווה - דברי אליי קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר להורדה</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3625,13 +3349,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
       </c>
       <c r="B65" t="str">
         <v>2026-01-07</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-15</v>
@@ -3655,7 +3379,7 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+        <v>אלין לינהרד - המבט בעינייך קאבר להורדה</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3684,13 +3408,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
       </c>
       <c r="B66" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-15</v>
@@ -3714,7 +3438,7 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+        <v>שליו חנן - כל הדרך הביתה קאבר להורדה</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3743,13 +3467,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>שי עזאני - גאולה להורדה</v>
       </c>
       <c r="B67" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-15</v>
@@ -3773,7 +3497,7 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>שי עזאני - גאולה</v>
+        <v>שי עזאני - גאולה להורדה</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3802,13 +3526,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
       </c>
       <c r="B68" t="str">
         <v>2026-01-02</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=881f499716cf30725fab277034b55fc2</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-15</v>
@@ -3832,7 +3556,7 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>נועם דדון - את כבר לא איתי קאבר</v>
+        <v>נועם דדון - את כבר לא איתי קאבר להורדה</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3867,7 +3591,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-15</v>
@@ -3876,13 +3600,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3891,7 +3615,7 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3912,6 +3636,21 @@
         <v/>
       </c>
       <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+      <c r="T69" t="str">
+        <v/>
+      </c>
+      <c r="U69" t="str">
+        <v/>
+      </c>
+      <c r="V69" t="str">
+        <v/>
+      </c>
+      <c r="W69" t="str">
         <v/>
       </c>
     </row>
@@ -3923,7 +3662,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-15</v>
@@ -3932,13 +3671,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -3947,7 +3686,7 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v/>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3968,6 +3707,21 @@
         <v/>
       </c>
       <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
+      <c r="U70" t="str">
+        <v/>
+      </c>
+      <c r="V70" t="str">
+        <v/>
+      </c>
+      <c r="W70" t="str">
         <v/>
       </c>
     </row>
@@ -3979,7 +3733,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-15</v>
@@ -3988,13 +3742,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -4003,7 +3757,7 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v/>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -4024,6 +3778,21 @@
         <v/>
       </c>
       <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
+      <c r="U71" t="str">
+        <v/>
+      </c>
+      <c r="V71" t="str">
+        <v/>
+      </c>
+      <c r="W71" t="str">
         <v/>
       </c>
     </row>
@@ -4035,7 +3804,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-15</v>
@@ -4044,13 +3813,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -4059,7 +3828,7 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v/>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -4080,6 +3849,21 @@
         <v/>
       </c>
       <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+      <c r="T72" t="str">
+        <v/>
+      </c>
+      <c r="U72" t="str">
+        <v/>
+      </c>
+      <c r="V72" t="str">
+        <v/>
+      </c>
+      <c r="W72" t="str">
         <v/>
       </c>
     </row>
@@ -4091,7 +3875,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-15</v>
@@ -4100,13 +3884,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -4115,7 +3899,7 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v/>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -4136,6 +3920,21 @@
         <v/>
       </c>
       <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+      <c r="T73" t="str">
+        <v/>
+      </c>
+      <c r="U73" t="str">
+        <v/>
+      </c>
+      <c r="V73" t="str">
+        <v/>
+      </c>
+      <c r="W73" t="str">
         <v/>
       </c>
     </row>
@@ -4147,7 +3946,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-15</v>
@@ -4156,13 +3955,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -4171,7 +3970,7 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -4192,6 +3991,21 @@
         <v/>
       </c>
       <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
+      <c r="U74" t="str">
+        <v/>
+      </c>
+      <c r="V74" t="str">
+        <v/>
+      </c>
+      <c r="W74" t="str">
         <v/>
       </c>
     </row>
@@ -4203,7 +4017,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-15</v>
@@ -4212,13 +4026,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -4227,7 +4041,7 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v/>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -4248,6 +4062,21 @@
         <v/>
       </c>
       <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+      <c r="T75" t="str">
+        <v/>
+      </c>
+      <c r="U75" t="str">
+        <v/>
+      </c>
+      <c r="V75" t="str">
+        <v/>
+      </c>
+      <c r="W75" t="str">
         <v/>
       </c>
     </row>
@@ -4259,7 +4088,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-15</v>
@@ -4268,13 +4097,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -4283,7 +4112,7 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -4304,6 +4133,21 @@
         <v/>
       </c>
       <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
+      <c r="U76" t="str">
+        <v/>
+      </c>
+      <c r="V76" t="str">
+        <v/>
+      </c>
+      <c r="W76" t="str">
         <v/>
       </c>
     </row>
@@ -4315,7 +4159,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-15</v>
@@ -4324,13 +4168,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -4339,7 +4183,7 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v/>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -4360,6 +4204,21 @@
         <v/>
       </c>
       <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+      <c r="T77" t="str">
+        <v/>
+      </c>
+      <c r="U77" t="str">
+        <v/>
+      </c>
+      <c r="V77" t="str">
+        <v/>
+      </c>
+      <c r="W77" t="str">
         <v/>
       </c>
     </row>
@@ -4371,7 +4230,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-15</v>
@@ -4380,13 +4239,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -4395,7 +4254,7 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -4416,6 +4275,21 @@
         <v/>
       </c>
       <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
+      <c r="U78" t="str">
+        <v/>
+      </c>
+      <c r="V78" t="str">
+        <v/>
+      </c>
+      <c r="W78" t="str">
         <v/>
       </c>
     </row>
@@ -4427,7 +4301,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-15</v>
@@ -4436,13 +4310,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -4451,7 +4325,7 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v/>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -4472,6 +4346,21 @@
         <v/>
       </c>
       <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
+      </c>
+      <c r="U79" t="str">
+        <v/>
+      </c>
+      <c r="V79" t="str">
+        <v/>
+      </c>
+      <c r="W79" t="str">
         <v/>
       </c>
     </row>
@@ -4483,7 +4372,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-15</v>
@@ -4492,13 +4381,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -4507,7 +4396,7 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v/>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -4528,6 +4417,21 @@
         <v/>
       </c>
       <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+      <c r="T80" t="str">
+        <v/>
+      </c>
+      <c r="U80" t="str">
+        <v/>
+      </c>
+      <c r="V80" t="str">
+        <v/>
+      </c>
+      <c r="W80" t="str">
         <v/>
       </c>
     </row>
@@ -4539,7 +4443,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-15</v>
@@ -4548,13 +4452,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -4563,7 +4467,7 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -4584,6 +4488,21 @@
         <v/>
       </c>
       <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+      <c r="T81" t="str">
+        <v/>
+      </c>
+      <c r="U81" t="str">
+        <v/>
+      </c>
+      <c r="V81" t="str">
+        <v/>
+      </c>
+      <c r="W81" t="str">
         <v/>
       </c>
     </row>
@@ -4595,7 +4514,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-15</v>
@@ -4604,13 +4523,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -4619,7 +4538,7 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v/>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -4640,6 +4559,21 @@
         <v/>
       </c>
       <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+      <c r="T82" t="str">
+        <v/>
+      </c>
+      <c r="U82" t="str">
+        <v/>
+      </c>
+      <c r="V82" t="str">
+        <v/>
+      </c>
+      <c r="W82" t="str">
         <v/>
       </c>
     </row>
@@ -4651,7 +4585,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-15</v>
@@ -4660,13 +4594,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -4675,7 +4609,7 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -4696,6 +4630,21 @@
         <v/>
       </c>
       <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+      <c r="T83" t="str">
+        <v/>
+      </c>
+      <c r="U83" t="str">
+        <v/>
+      </c>
+      <c r="V83" t="str">
+        <v/>
+      </c>
+      <c r="W83" t="str">
         <v/>
       </c>
     </row>
@@ -4707,7 +4656,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-15</v>
@@ -4716,13 +4665,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -4731,7 +4680,7 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -4752,6 +4701,21 @@
         <v/>
       </c>
       <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+      <c r="T84" t="str">
+        <v/>
+      </c>
+      <c r="U84" t="str">
+        <v/>
+      </c>
+      <c r="V84" t="str">
+        <v/>
+      </c>
+      <c r="W84" t="str">
         <v/>
       </c>
     </row>
@@ -4763,22 +4727,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -4787,7 +4751,7 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -4814,6 +4778,15 @@
         <v/>
       </c>
       <c r="T85" t="str">
+        <v/>
+      </c>
+      <c r="U85" t="str">
+        <v/>
+      </c>
+      <c r="V85" t="str">
+        <v/>
+      </c>
+      <c r="W85" t="str">
         <v/>
       </c>
     </row>
@@ -4825,22 +4798,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -4849,7 +4822,7 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -4882,6 +4855,9 @@
         <v/>
       </c>
       <c r="V86" t="str">
+        <v/>
+      </c>
+      <c r="W86" t="str">
         <v/>
       </c>
     </row>
@@ -4893,22 +4869,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -4917,7 +4893,7 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -4950,6 +4926,9 @@
         <v/>
       </c>
       <c r="V87" t="str">
+        <v/>
+      </c>
+      <c r="W87" t="str">
         <v/>
       </c>
     </row>
@@ -4961,22 +4940,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -4985,7 +4964,7 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -5018,6 +4997,9 @@
         <v/>
       </c>
       <c r="V88" t="str">
+        <v/>
+      </c>
+      <c r="W88" t="str">
         <v/>
       </c>
     </row>
@@ -5029,22 +5011,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -5053,7 +5035,7 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v/>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -5086,6 +5068,9 @@
         <v/>
       </c>
       <c r="V89" t="str">
+        <v/>
+      </c>
+      <c r="W89" t="str">
         <v/>
       </c>
     </row>
@@ -5097,22 +5082,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -5121,7 +5106,7 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -5154,6 +5139,9 @@
         <v/>
       </c>
       <c r="V90" t="str">
+        <v/>
+      </c>
+      <c r="W90" t="str">
         <v/>
       </c>
     </row>
@@ -5165,22 +5153,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -5189,7 +5177,7 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -5222,6 +5210,9 @@
         <v/>
       </c>
       <c r="V91" t="str">
+        <v/>
+      </c>
+      <c r="W91" t="str">
         <v/>
       </c>
     </row>
@@ -5233,22 +5224,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -5257,7 +5248,7 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v/>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -5290,6 +5281,9 @@
         <v/>
       </c>
       <c r="V92" t="str">
+        <v/>
+      </c>
+      <c r="W92" t="str">
         <v/>
       </c>
     </row>
@@ -5301,22 +5295,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -5325,7 +5319,7 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v/>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -5358,6 +5352,9 @@
         <v/>
       </c>
       <c r="V93" t="str">
+        <v/>
+      </c>
+      <c r="W93" t="str">
         <v/>
       </c>
     </row>
@@ -5369,22 +5366,22 @@
         <v>2026-01-08</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -5393,7 +5390,7 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v/>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -5426,6 +5423,9 @@
         <v/>
       </c>
       <c r="V94" t="str">
+        <v/>
+      </c>
+      <c r="W94" t="str">
         <v/>
       </c>
     </row>
@@ -5437,22 +5437,22 @@
         <v>2026-01-07</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v/>
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -5497,9 +5497,6 @@
         <v/>
       </c>
       <c r="W95" t="str">
-        <v/>
-      </c>
-      <c r="X95" t="str">
         <v/>
       </c>
     </row>
@@ -5511,22 +5508,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -5535,7 +5532,7 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v/>
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -5571,9 +5568,6 @@
         <v/>
       </c>
       <c r="W96" t="str">
-        <v/>
-      </c>
-      <c r="X96" t="str">
         <v/>
       </c>
     </row>
@@ -5585,22 +5579,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C97" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -5609,7 +5603,7 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>שי עזאני - גאולה</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -5645,9 +5639,6 @@
         <v/>
       </c>
       <c r="W97" t="str">
-        <v/>
-      </c>
-      <c r="X97" t="str">
         <v/>
       </c>
     </row>
@@ -5659,22 +5650,22 @@
         <v>2026-01-02</v>
       </c>
       <c r="C98" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=5b187402ef10921fad110cbe5b66d189</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -5683,7 +5674,7 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v/>
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
       </c>
       <c r="L98" t="str">
         <v/>
@@ -5719,24 +5710,21 @@
         <v/>
       </c>
       <c r="W98" t="str">
-        <v/>
-      </c>
-      <c r="X98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>יאיר יראי - נתת לי הכל קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B99" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C99" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -5790,27 +5778,21 @@
         <v/>
       </c>
       <c r="V99" t="str">
-        <v/>
-      </c>
-      <c r="W99" t="str">
-        <v/>
-      </c>
-      <c r="X99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B100" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C100" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -5864,27 +5846,21 @@
         <v/>
       </c>
       <c r="V100" t="str">
-        <v/>
-      </c>
-      <c r="W100" t="str">
-        <v/>
-      </c>
-      <c r="X100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B101" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C101" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -5938,27 +5914,21 @@
         <v/>
       </c>
       <c r="V101" t="str">
-        <v/>
-      </c>
-      <c r="W101" t="str">
-        <v/>
-      </c>
-      <c r="X101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>אבישי עוזיאל - שני ילדים בבית</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B102" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C102" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -6012,27 +5982,21 @@
         <v/>
       </c>
       <c r="V102" t="str">
-        <v/>
-      </c>
-      <c r="W102" t="str">
-        <v/>
-      </c>
-      <c r="X102" t="str">
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B103" t="str">
-        <v>2026-01-02</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C103" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -6086,27 +6050,21 @@
         <v/>
       </c>
       <c r="V103" t="str">
-        <v/>
-      </c>
-      <c r="W103" t="str">
-        <v/>
-      </c>
-      <c r="X103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>שני אוחיון - על כל אלה קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B104" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C104" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -6160,27 +6118,21 @@
         <v/>
       </c>
       <c r="V104" t="str">
-        <v/>
-      </c>
-      <c r="W104" t="str">
-        <v/>
-      </c>
-      <c r="X104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+        <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B105" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C105" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -6234,27 +6186,21 @@
         <v/>
       </c>
       <c r="V105" t="str">
-        <v/>
-      </c>
-      <c r="W105" t="str">
-        <v/>
-      </c>
-      <c r="X105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>עדי עייש - אהובי קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B106" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C106" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -6308,27 +6254,21 @@
         <v/>
       </c>
       <c r="V106" t="str">
-        <v/>
-      </c>
-      <c r="W106" t="str">
-        <v/>
-      </c>
-      <c r="X106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>נועם דדון - הו מרגנית קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B107" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C107" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -6382,27 +6322,21 @@
         <v/>
       </c>
       <c r="V107" t="str">
-        <v/>
-      </c>
-      <c r="W107" t="str">
-        <v/>
-      </c>
-      <c r="X107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>משה לדני - בואי בשלום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B108" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C108" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -6456,27 +6390,21 @@
         <v/>
       </c>
       <c r="V108" t="str">
-        <v/>
-      </c>
-      <c r="W108" t="str">
-        <v/>
-      </c>
-      <c r="X108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+        <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B109" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C109" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -6530,27 +6458,21 @@
         <v/>
       </c>
       <c r="V109" t="str">
-        <v/>
-      </c>
-      <c r="W109" t="str">
-        <v/>
-      </c>
-      <c r="X109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>אלכס - שובי לביתך קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B110" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C110" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -6604,27 +6526,21 @@
         <v/>
       </c>
       <c r="V110" t="str">
-        <v/>
-      </c>
-      <c r="W110" t="str">
-        <v/>
-      </c>
-      <c r="X110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>אילאי ברדה - עוף מוזר קאבר</v>
+        <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B111" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C111" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -6678,27 +6594,21 @@
         <v/>
       </c>
       <c r="V111" t="str">
-        <v/>
-      </c>
-      <c r="W111" t="str">
-        <v/>
-      </c>
-      <c r="X111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+        <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B112" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C112" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -6752,27 +6662,21 @@
         <v/>
       </c>
       <c r="V112" t="str">
-        <v/>
-      </c>
-      <c r="W112" t="str">
-        <v/>
-      </c>
-      <c r="X112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>אהרון כהן - פרק אחר קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B113" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C113" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -6826,27 +6730,21 @@
         <v/>
       </c>
       <c r="V113" t="str">
-        <v/>
-      </c>
-      <c r="W113" t="str">
-        <v/>
-      </c>
-      <c r="X113" t="str">
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>אהרון כהן - נשבע קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B114" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-13</v>
       </c>
       <c r="C114" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=2ea4d024e78c65e38441a3d18d027261</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-15</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -6900,24 +6798,18 @@
         <v/>
       </c>
       <c r="V114" t="str">
-        <v/>
-      </c>
-      <c r="W114" t="str">
-        <v/>
-      </c>
-      <c r="X114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>אהרון כהן - ממעמקים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B115" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C115" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=a5254a19f5b2f9ff40856ebe2ce38632</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-08</v>
@@ -6985,13 +6877,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>אהרון כהן - יסמין קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B116" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C116" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-08</v>
@@ -7056,16 +6948,22 @@
       <c r="X116" t="str">
         <v/>
       </c>
+      <c r="Y116" t="str">
+        <v/>
+      </c>
+      <c r="Z116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>אהרון כהן - הפרח בגני קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B117" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C117" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-08</v>
@@ -7130,16 +7028,22 @@
       <c r="X117" t="str">
         <v/>
       </c>
+      <c r="Y117" t="str">
+        <v/>
+      </c>
+      <c r="Z117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>אביאל - שפוי בשבילך קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B118" t="str">
-        <v>2025-12-30</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C118" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-08</v>
@@ -7204,16 +7108,22 @@
       <c r="X118" t="str">
         <v/>
       </c>
+      <c r="Y118" t="str">
+        <v/>
+      </c>
+      <c r="Z118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B119" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C119" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-08</v>
@@ -7278,16 +7188,22 @@
       <c r="X119" t="str">
         <v/>
       </c>
+      <c r="Y119" t="str">
+        <v/>
+      </c>
+      <c r="Z119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B120" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C120" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-08</v>
@@ -7352,16 +7268,22 @@
       <c r="X120" t="str">
         <v/>
       </c>
+      <c r="Y120" t="str">
+        <v/>
+      </c>
+      <c r="Z120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>רונן לוגסי - גודל הכאב קאבר</v>
+        <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B121" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C121" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-08</v>
@@ -7426,16 +7348,22 @@
       <c r="X121" t="str">
         <v/>
       </c>
+      <c r="Y121" t="str">
+        <v/>
+      </c>
+      <c r="Z121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>צביקי רנד - אם אשכחך קאבר</v>
+        <v>משה ברששת - יש בך הכל קאבר</v>
       </c>
       <c r="B122" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C122" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409107&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-08</v>
@@ -7500,16 +7428,22 @@
       <c r="X122" t="str">
         <v/>
       </c>
+      <c r="Y122" t="str">
+        <v/>
+      </c>
+      <c r="Z122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+        <v>אורי אוחיון - לב שבור קאבר</v>
       </c>
       <c r="B123" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C123" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409106&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-08</v>
@@ -7574,16 +7508,22 @@
       <c r="X123" t="str">
         <v/>
       </c>
+      <c r="Y123" t="str">
+        <v/>
+      </c>
+      <c r="Z123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>נתי שקד - אמן קאבר</v>
+        <v>אבישי רווה - דברי אליי קאבר</v>
       </c>
       <c r="B124" t="str">
-        <v>2025-12-26</v>
+        <v>2026-01-08</v>
       </c>
       <c r="C124" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409105&amp;sid=5acd1503d29ec141a863e4ec58385006</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-08</v>
@@ -7648,10 +7588,2596 @@
       <c r="X124" t="str">
         <v/>
       </c>
+      <c r="Y124" t="str">
+        <v/>
+      </c>
+      <c r="Z124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>אלין לינהרד - המבט בעינייך קאבר</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="C125" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409097&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v/>
+      </c>
+      <c r="T125" t="str">
+        <v/>
+      </c>
+      <c r="U125" t="str">
+        <v/>
+      </c>
+      <c r="V125" t="str">
+        <v/>
+      </c>
+      <c r="W125" t="str">
+        <v/>
+      </c>
+      <c r="X125" t="str">
+        <v/>
+      </c>
+      <c r="Y125" t="str">
+        <v/>
+      </c>
+      <c r="Z125" t="str">
+        <v/>
+      </c>
+      <c r="AA125" t="str">
+        <v/>
+      </c>
+      <c r="AB125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>שליו חנן - כל הדרך הביתה קאבר</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C126" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409034&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D126" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+      <c r="T126" t="str">
+        <v/>
+      </c>
+      <c r="U126" t="str">
+        <v/>
+      </c>
+      <c r="V126" t="str">
+        <v/>
+      </c>
+      <c r="W126" t="str">
+        <v/>
+      </c>
+      <c r="X126" t="str">
+        <v/>
+      </c>
+      <c r="Y126" t="str">
+        <v/>
+      </c>
+      <c r="Z126" t="str">
+        <v/>
+      </c>
+      <c r="AA126" t="str">
+        <v/>
+      </c>
+      <c r="AB126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>שי עזאני - גאולה</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C127" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409033&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D127" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127" t="str">
+        <v/>
+      </c>
+      <c r="V127" t="str">
+        <v/>
+      </c>
+      <c r="W127" t="str">
+        <v/>
+      </c>
+      <c r="X127" t="str">
+        <v/>
+      </c>
+      <c r="Y127" t="str">
+        <v/>
+      </c>
+      <c r="Z127" t="str">
+        <v/>
+      </c>
+      <c r="AA127" t="str">
+        <v/>
+      </c>
+      <c r="AB127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>נועם דדון - את כבר לא איתי קאבר</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C128" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409032&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+      <c r="U128" t="str">
+        <v/>
+      </c>
+      <c r="V128" t="str">
+        <v/>
+      </c>
+      <c r="W128" t="str">
+        <v/>
+      </c>
+      <c r="X128" t="str">
+        <v/>
+      </c>
+      <c r="Y128" t="str">
+        <v/>
+      </c>
+      <c r="Z128" t="str">
+        <v/>
+      </c>
+      <c r="AA128" t="str">
+        <v/>
+      </c>
+      <c r="AB128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>יאיר יראי - נתת לי הכל קאבר</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C129" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409031&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D129" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129" t="str">
+        <v/>
+      </c>
+      <c r="V129" t="str">
+        <v/>
+      </c>
+      <c r="W129" t="str">
+        <v/>
+      </c>
+      <c r="X129" t="str">
+        <v/>
+      </c>
+      <c r="Y129" t="str">
+        <v/>
+      </c>
+      <c r="Z129" t="str">
+        <v/>
+      </c>
+      <c r="AA129" t="str">
+        <v/>
+      </c>
+      <c r="AB129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>הרב נתנאל אלעזרוב - תמיד אוהב אותי קאבר</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C130" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409030&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D130" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+      <c r="U130" t="str">
+        <v/>
+      </c>
+      <c r="V130" t="str">
+        <v/>
+      </c>
+      <c r="W130" t="str">
+        <v/>
+      </c>
+      <c r="X130" t="str">
+        <v/>
+      </c>
+      <c r="Y130" t="str">
+        <v/>
+      </c>
+      <c r="Z130" t="str">
+        <v/>
+      </c>
+      <c r="AA130" t="str">
+        <v/>
+      </c>
+      <c r="AB130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>אלון מיכאל - אני בא אלייך קאבר</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C131" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409029&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D131" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v/>
+      </c>
+      <c r="T131" t="str">
+        <v/>
+      </c>
+      <c r="U131" t="str">
+        <v/>
+      </c>
+      <c r="V131" t="str">
+        <v/>
+      </c>
+      <c r="W131" t="str">
+        <v/>
+      </c>
+      <c r="X131" t="str">
+        <v/>
+      </c>
+      <c r="Y131" t="str">
+        <v/>
+      </c>
+      <c r="Z131" t="str">
+        <v/>
+      </c>
+      <c r="AA131" t="str">
+        <v/>
+      </c>
+      <c r="AB131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>אבישי עוזיאל - שני ילדים בבית</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C132" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409028&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D132" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+      <c r="T132" t="str">
+        <v/>
+      </c>
+      <c r="U132" t="str">
+        <v/>
+      </c>
+      <c r="V132" t="str">
+        <v/>
+      </c>
+      <c r="W132" t="str">
+        <v/>
+      </c>
+      <c r="X132" t="str">
+        <v/>
+      </c>
+      <c r="Y132" t="str">
+        <v/>
+      </c>
+      <c r="Z132" t="str">
+        <v/>
+      </c>
+      <c r="AA132" t="str">
+        <v/>
+      </c>
+      <c r="AB132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>אבישי עוזיאל - שאריות מעצמי קאבר</v>
+      </c>
+      <c r="B133" t="str">
+        <v>2026-01-02</v>
+      </c>
+      <c r="C133" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409027&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D133" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+      <c r="U133" t="str">
+        <v/>
+      </c>
+      <c r="V133" t="str">
+        <v/>
+      </c>
+      <c r="W133" t="str">
+        <v/>
+      </c>
+      <c r="X133" t="str">
+        <v/>
+      </c>
+      <c r="Y133" t="str">
+        <v/>
+      </c>
+      <c r="Z133" t="str">
+        <v/>
+      </c>
+      <c r="AA133" t="str">
+        <v/>
+      </c>
+      <c r="AB133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>שני אוחיון - על כל אלה קאבר</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C134" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408986&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D134" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
+      <c r="V134" t="str">
+        <v/>
+      </c>
+      <c r="W134" t="str">
+        <v/>
+      </c>
+      <c r="X134" t="str">
+        <v/>
+      </c>
+      <c r="Y134" t="str">
+        <v/>
+      </c>
+      <c r="Z134" t="str">
+        <v/>
+      </c>
+      <c r="AA134" t="str">
+        <v/>
+      </c>
+      <c r="AB134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>שיר דוד גדסי - שלווה בארמונותיך &amp; ניגונים</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C135" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408985&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D135" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
+        <v/>
+      </c>
+      <c r="V135" t="str">
+        <v/>
+      </c>
+      <c r="W135" t="str">
+        <v/>
+      </c>
+      <c r="X135" t="str">
+        <v/>
+      </c>
+      <c r="Y135" t="str">
+        <v/>
+      </c>
+      <c r="Z135" t="str">
+        <v/>
+      </c>
+      <c r="AA135" t="str">
+        <v/>
+      </c>
+      <c r="AB135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>עדי עייש - אהובי קאבר</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C136" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408984&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D136" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v/>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+      <c r="U136" t="str">
+        <v/>
+      </c>
+      <c r="V136" t="str">
+        <v/>
+      </c>
+      <c r="W136" t="str">
+        <v/>
+      </c>
+      <c r="X136" t="str">
+        <v/>
+      </c>
+      <c r="Y136" t="str">
+        <v/>
+      </c>
+      <c r="Z136" t="str">
+        <v/>
+      </c>
+      <c r="AA136" t="str">
+        <v/>
+      </c>
+      <c r="AB136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>נועם דדון - הו מרגנית קאבר</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C137" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408983&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D137" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137" t="str">
+        <v/>
+      </c>
+      <c r="V137" t="str">
+        <v/>
+      </c>
+      <c r="W137" t="str">
+        <v/>
+      </c>
+      <c r="X137" t="str">
+        <v/>
+      </c>
+      <c r="Y137" t="str">
+        <v/>
+      </c>
+      <c r="Z137" t="str">
+        <v/>
+      </c>
+      <c r="AA137" t="str">
+        <v/>
+      </c>
+      <c r="AB137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>משה לדני - בואי בשלום קאבר</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C138" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408982&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D138" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138" t="str">
+        <v/>
+      </c>
+      <c r="V138" t="str">
+        <v/>
+      </c>
+      <c r="W138" t="str">
+        <v/>
+      </c>
+      <c r="X138" t="str">
+        <v/>
+      </c>
+      <c r="Y138" t="str">
+        <v/>
+      </c>
+      <c r="Z138" t="str">
+        <v/>
+      </c>
+      <c r="AA138" t="str">
+        <v/>
+      </c>
+      <c r="AB138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>ברק אוגלבו - מחרוזת שקטים 2025 קאבר</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C139" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408981&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D139" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
+      <c r="V139" t="str">
+        <v/>
+      </c>
+      <c r="W139" t="str">
+        <v/>
+      </c>
+      <c r="X139" t="str">
+        <v/>
+      </c>
+      <c r="Y139" t="str">
+        <v/>
+      </c>
+      <c r="Z139" t="str">
+        <v/>
+      </c>
+      <c r="AA139" t="str">
+        <v/>
+      </c>
+      <c r="AB139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>אלכס - שובי לביתך קאבר</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C140" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408980&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D140" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+      <c r="U140" t="str">
+        <v/>
+      </c>
+      <c r="V140" t="str">
+        <v/>
+      </c>
+      <c r="W140" t="str">
+        <v/>
+      </c>
+      <c r="X140" t="str">
+        <v/>
+      </c>
+      <c r="Y140" t="str">
+        <v/>
+      </c>
+      <c r="Z140" t="str">
+        <v/>
+      </c>
+      <c r="AA140" t="str">
+        <v/>
+      </c>
+      <c r="AB140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>אילאי ברדה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C141" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408979&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D141" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v/>
+      </c>
+      <c r="T141" t="str">
+        <v/>
+      </c>
+      <c r="U141" t="str">
+        <v/>
+      </c>
+      <c r="V141" t="str">
+        <v/>
+      </c>
+      <c r="W141" t="str">
+        <v/>
+      </c>
+      <c r="X141" t="str">
+        <v/>
+      </c>
+      <c r="Y141" t="str">
+        <v/>
+      </c>
+      <c r="Z141" t="str">
+        <v/>
+      </c>
+      <c r="AA141" t="str">
+        <v/>
+      </c>
+      <c r="AB141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>אורין כולב - כל מה שאני רוצה קאבר</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C142" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408978&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D142" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v/>
+      </c>
+      <c r="T142" t="str">
+        <v/>
+      </c>
+      <c r="U142" t="str">
+        <v/>
+      </c>
+      <c r="V142" t="str">
+        <v/>
+      </c>
+      <c r="W142" t="str">
+        <v/>
+      </c>
+      <c r="X142" t="str">
+        <v/>
+      </c>
+      <c r="Y142" t="str">
+        <v/>
+      </c>
+      <c r="Z142" t="str">
+        <v/>
+      </c>
+      <c r="AA142" t="str">
+        <v/>
+      </c>
+      <c r="AB142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>אהרון כהן - פרק אחר קאבר</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C143" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408977&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D143" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v/>
+      </c>
+      <c r="T143" t="str">
+        <v/>
+      </c>
+      <c r="U143" t="str">
+        <v/>
+      </c>
+      <c r="V143" t="str">
+        <v/>
+      </c>
+      <c r="W143" t="str">
+        <v/>
+      </c>
+      <c r="X143" t="str">
+        <v/>
+      </c>
+      <c r="Y143" t="str">
+        <v/>
+      </c>
+      <c r="Z143" t="str">
+        <v/>
+      </c>
+      <c r="AA143" t="str">
+        <v/>
+      </c>
+      <c r="AB143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>אהרון כהן - נשבע קאבר</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C144" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408976&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D144" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v/>
+      </c>
+      <c r="T144" t="str">
+        <v/>
+      </c>
+      <c r="U144" t="str">
+        <v/>
+      </c>
+      <c r="V144" t="str">
+        <v/>
+      </c>
+      <c r="W144" t="str">
+        <v/>
+      </c>
+      <c r="X144" t="str">
+        <v/>
+      </c>
+      <c r="Y144" t="str">
+        <v/>
+      </c>
+      <c r="Z144" t="str">
+        <v/>
+      </c>
+      <c r="AA144" t="str">
+        <v/>
+      </c>
+      <c r="AB144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>אהרון כהן - ממעמקים קאבר</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C145" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408975&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D145" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v/>
+      </c>
+      <c r="T145" t="str">
+        <v/>
+      </c>
+      <c r="U145" t="str">
+        <v/>
+      </c>
+      <c r="V145" t="str">
+        <v/>
+      </c>
+      <c r="W145" t="str">
+        <v/>
+      </c>
+      <c r="X145" t="str">
+        <v/>
+      </c>
+      <c r="Y145" t="str">
+        <v/>
+      </c>
+      <c r="Z145" t="str">
+        <v/>
+      </c>
+      <c r="AA145" t="str">
+        <v/>
+      </c>
+      <c r="AB145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>אהרון כהן - יסמין קאבר</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C146" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408974&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D146" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E146" t="str">
+        <v/>
+      </c>
+      <c r="F146" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
+        <v/>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v/>
+      </c>
+      <c r="T146" t="str">
+        <v/>
+      </c>
+      <c r="U146" t="str">
+        <v/>
+      </c>
+      <c r="V146" t="str">
+        <v/>
+      </c>
+      <c r="W146" t="str">
+        <v/>
+      </c>
+      <c r="X146" t="str">
+        <v/>
+      </c>
+      <c r="Y146" t="str">
+        <v/>
+      </c>
+      <c r="Z146" t="str">
+        <v/>
+      </c>
+      <c r="AA146" t="str">
+        <v/>
+      </c>
+      <c r="AB146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>אהרון כהן - הפרח בגני קאבר</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C147" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408973&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D147" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E147" t="str">
+        <v/>
+      </c>
+      <c r="F147" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v/>
+      </c>
+      <c r="T147" t="str">
+        <v/>
+      </c>
+      <c r="U147" t="str">
+        <v/>
+      </c>
+      <c r="V147" t="str">
+        <v/>
+      </c>
+      <c r="W147" t="str">
+        <v/>
+      </c>
+      <c r="X147" t="str">
+        <v/>
+      </c>
+      <c r="Y147" t="str">
+        <v/>
+      </c>
+      <c r="Z147" t="str">
+        <v/>
+      </c>
+      <c r="AA147" t="str">
+        <v/>
+      </c>
+      <c r="AB147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>אביאל - שפוי בשבילך קאבר</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2025-12-30</v>
+      </c>
+      <c r="C148" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408972&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D148" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E148" t="str">
+        <v/>
+      </c>
+      <c r="F148" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v/>
+      </c>
+      <c r="T148" t="str">
+        <v/>
+      </c>
+      <c r="U148" t="str">
+        <v/>
+      </c>
+      <c r="V148" t="str">
+        <v/>
+      </c>
+      <c r="W148" t="str">
+        <v/>
+      </c>
+      <c r="X148" t="str">
+        <v/>
+      </c>
+      <c r="Y148" t="str">
+        <v/>
+      </c>
+      <c r="Z148" t="str">
+        <v/>
+      </c>
+      <c r="AA148" t="str">
+        <v/>
+      </c>
+      <c r="AB148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>אוריאל לנקרי - באתי לגני קאבר</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C149" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408940&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D149" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E149" t="str">
+        <v/>
+      </c>
+      <c r="F149" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
+        <v/>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v/>
+      </c>
+      <c r="T149" t="str">
+        <v/>
+      </c>
+      <c r="U149" t="str">
+        <v/>
+      </c>
+      <c r="V149" t="str">
+        <v/>
+      </c>
+      <c r="W149" t="str">
+        <v/>
+      </c>
+      <c r="X149" t="str">
+        <v/>
+      </c>
+      <c r="Y149" t="str">
+        <v/>
+      </c>
+      <c r="Z149" t="str">
+        <v/>
+      </c>
+      <c r="AA149" t="str">
+        <v/>
+      </c>
+      <c r="AB149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>שליו לוסקי - מלך אחד לעולם קאבר</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C150" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408939&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D150" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v/>
+      </c>
+      <c r="T150" t="str">
+        <v/>
+      </c>
+      <c r="U150" t="str">
+        <v/>
+      </c>
+      <c r="V150" t="str">
+        <v/>
+      </c>
+      <c r="W150" t="str">
+        <v/>
+      </c>
+      <c r="X150" t="str">
+        <v/>
+      </c>
+      <c r="Y150" t="str">
+        <v/>
+      </c>
+      <c r="Z150" t="str">
+        <v/>
+      </c>
+      <c r="AA150" t="str">
+        <v/>
+      </c>
+      <c r="AB150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>רונן לוגסי - גודל הכאב קאבר</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C151" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408938&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D151" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E151" t="str">
+        <v/>
+      </c>
+      <c r="F151" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v/>
+      </c>
+      <c r="T151" t="str">
+        <v/>
+      </c>
+      <c r="U151" t="str">
+        <v/>
+      </c>
+      <c r="V151" t="str">
+        <v/>
+      </c>
+      <c r="W151" t="str">
+        <v/>
+      </c>
+      <c r="X151" t="str">
+        <v/>
+      </c>
+      <c r="Y151" t="str">
+        <v/>
+      </c>
+      <c r="Z151" t="str">
+        <v/>
+      </c>
+      <c r="AA151" t="str">
+        <v/>
+      </c>
+      <c r="AB151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>צביקי רנד - אם אשכחך קאבר</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C152" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408937&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D152" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v/>
+      </c>
+      <c r="T152" t="str">
+        <v/>
+      </c>
+      <c r="U152" t="str">
+        <v/>
+      </c>
+      <c r="V152" t="str">
+        <v/>
+      </c>
+      <c r="W152" t="str">
+        <v/>
+      </c>
+      <c r="X152" t="str">
+        <v/>
+      </c>
+      <c r="Y152" t="str">
+        <v/>
+      </c>
+      <c r="Z152" t="str">
+        <v/>
+      </c>
+      <c r="AA152" t="str">
+        <v/>
+      </c>
+      <c r="AB152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>עמנואל זאודה &amp; משה זאודה - הזוהר לארגוב קאבר</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C153" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408936&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D153" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E153" t="str">
+        <v/>
+      </c>
+      <c r="F153" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
+        <v/>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v/>
+      </c>
+      <c r="T153" t="str">
+        <v/>
+      </c>
+      <c r="U153" t="str">
+        <v/>
+      </c>
+      <c r="V153" t="str">
+        <v/>
+      </c>
+      <c r="W153" t="str">
+        <v/>
+      </c>
+      <c r="X153" t="str">
+        <v/>
+      </c>
+      <c r="Y153" t="str">
+        <v/>
+      </c>
+      <c r="Z153" t="str">
+        <v/>
+      </c>
+      <c r="AA153" t="str">
+        <v/>
+      </c>
+      <c r="AB153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>נתי שקד - אמן קאבר</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2025-12-26</v>
+      </c>
+      <c r="C154" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=408935&amp;sid=64e6e3574a93ec12db122121669f0057</v>
+      </c>
+      <c r="D154" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="E154" t="str">
+        <v/>
+      </c>
+      <c r="F154" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
+        <v/>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
+      <c r="R154" t="str">
+        <v/>
+      </c>
+      <c r="S154" t="str">
+        <v/>
+      </c>
+      <c r="T154" t="str">
+        <v/>
+      </c>
+      <c r="U154" t="str">
+        <v/>
+      </c>
+      <c r="V154" t="str">
+        <v/>
+      </c>
+      <c r="W154" t="str">
+        <v/>
+      </c>
+      <c r="X154" t="str">
+        <v/>
+      </c>
+      <c r="Y154" t="str">
+        <v/>
+      </c>
+      <c r="Z154" t="str">
+        <v/>
+      </c>
+      <c r="AA154" t="str">
+        <v/>
+      </c>
+      <c r="AB154" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:O61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,10 +439,10 @@
         <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -474,10 +474,10 @@
         <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -509,10 +509,10 @@
         <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -544,10 +544,10 @@
         <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -579,10 +579,10 @@
         <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -614,10 +614,10 @@
         <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -649,10 +649,10 @@
         <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -684,10 +684,10 @@
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -719,10 +719,10 @@
         <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -754,10 +754,10 @@
         <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -789,10 +789,10 @@
         <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -824,10 +824,10 @@
         <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -859,10 +859,10 @@
         <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -894,10 +894,10 @@
         <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
@@ -929,10 +929,10 @@
         <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
@@ -964,10 +964,10 @@
         <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
@@ -999,10 +999,10 @@
         <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
@@ -1034,10 +1034,10 @@
         <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
@@ -1069,10 +1069,10 @@
         <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
@@ -1104,10 +1104,10 @@
         <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
@@ -1139,10 +1139,10 @@
         <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
@@ -1174,10 +1174,10 @@
         <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
@@ -1209,10 +1209,10 @@
         <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
@@ -1244,10 +1244,10 @@
         <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
@@ -1279,10 +1279,10 @@
         <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
@@ -1314,10 +1314,10 @@
         <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
@@ -1349,10 +1349,10 @@
         <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
@@ -1384,10 +1384,10 @@
         <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-16</v>
@@ -1419,10 +1419,10 @@
         <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-16</v>
@@ -1454,10 +1454,10 @@
         <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-16</v>
@@ -1484,9 +1484,1419 @@
         <v>משה סונה - הינך יפה קאבר</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C32" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C33" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C34" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C35" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C36" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C37" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C38" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C39" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C40" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C41" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C42" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C43" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C44" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C45" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C46" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C47" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C48" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C49" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C50" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C51" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C52" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C53" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C54" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C55" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C56" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C57" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C58" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C59" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C60" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C61" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:S91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -477,7 +477,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -512,7 +512,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -547,7 +547,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -582,7 +582,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -617,7 +617,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -652,7 +652,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -687,7 +687,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -722,7 +722,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -757,7 +757,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -792,7 +792,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -827,7 +827,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -862,7 +862,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -897,7 +897,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
@@ -932,7 +932,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
@@ -967,7 +967,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
@@ -1002,7 +1002,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
@@ -1037,7 +1037,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
@@ -1072,7 +1072,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
@@ -1107,7 +1107,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
@@ -1142,7 +1142,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
@@ -1177,7 +1177,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
@@ -1212,7 +1212,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
@@ -1247,7 +1247,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
@@ -1282,7 +1282,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
@@ -1317,7 +1317,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
@@ -1352,7 +1352,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
@@ -1387,7 +1387,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-16</v>
@@ -1422,7 +1422,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-16</v>
@@ -1457,7 +1457,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-16</v>
@@ -1489,10 +1489,10 @@
         <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-16</v>
@@ -1536,10 +1536,10 @@
         <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-16</v>
@@ -1583,10 +1583,10 @@
         <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-16</v>
@@ -1630,10 +1630,10 @@
         <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-16</v>
@@ -1677,10 +1677,10 @@
         <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-16</v>
@@ -1724,10 +1724,10 @@
         <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-16</v>
@@ -1771,10 +1771,10 @@
         <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-16</v>
@@ -1818,10 +1818,10 @@
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-16</v>
@@ -1865,10 +1865,10 @@
         <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-16</v>
@@ -1912,10 +1912,10 @@
         <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-16</v>
@@ -1959,10 +1959,10 @@
         <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-16</v>
@@ -2006,10 +2006,10 @@
         <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-16</v>
@@ -2053,10 +2053,10 @@
         <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-16</v>
@@ -2100,10 +2100,10 @@
         <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-16</v>
@@ -2147,10 +2147,10 @@
         <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-16</v>
@@ -2194,10 +2194,10 @@
         <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-16</v>
@@ -2241,10 +2241,10 @@
         <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-16</v>
@@ -2288,10 +2288,10 @@
         <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-16</v>
@@ -2335,10 +2335,10 @@
         <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-16</v>
@@ -2382,10 +2382,10 @@
         <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-16</v>
@@ -2429,10 +2429,10 @@
         <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-16</v>
@@ -2476,10 +2476,10 @@
         <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-16</v>
@@ -2523,10 +2523,10 @@
         <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-16</v>
@@ -2570,10 +2570,10 @@
         <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B55" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-16</v>
@@ -2617,10 +2617,10 @@
         <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B56" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-16</v>
@@ -2664,10 +2664,10 @@
         <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B57" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-16</v>
@@ -2711,10 +2711,10 @@
         <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B58" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-16</v>
@@ -2758,10 +2758,10 @@
         <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B59" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-16</v>
@@ -2805,10 +2805,10 @@
         <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B60" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-16</v>
@@ -2852,10 +2852,10 @@
         <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-16</v>
@@ -2894,9 +2894,1779 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C62" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C63" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C64" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C65" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C66" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C67" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C68" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C69" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C70" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C71" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C72" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C73" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C74" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C75" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C76" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C77" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C78" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C79" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C80" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C81" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C82" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C83" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C84" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C85" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C86" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C87" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C88" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C89" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C90" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C91" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S91"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S91"/>
+  <dimension ref="A1:W121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -477,7 +477,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -512,7 +512,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -547,7 +547,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -582,7 +582,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -617,7 +617,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -652,7 +652,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -687,7 +687,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -722,7 +722,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -757,7 +757,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -792,7 +792,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -827,7 +827,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -862,7 +862,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -897,7 +897,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
@@ -932,7 +932,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
@@ -967,7 +967,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
@@ -1002,7 +1002,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
@@ -1037,7 +1037,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
@@ -1072,7 +1072,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
@@ -1107,7 +1107,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
@@ -1142,7 +1142,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
@@ -1177,7 +1177,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
@@ -1212,7 +1212,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
@@ -1247,7 +1247,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
@@ -1282,7 +1282,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
@@ -1317,7 +1317,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
@@ -1352,7 +1352,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
@@ -1387,7 +1387,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-16</v>
@@ -1422,7 +1422,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-16</v>
@@ -1457,7 +1457,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-16</v>
@@ -1492,7 +1492,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-16</v>
@@ -1539,7 +1539,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-16</v>
@@ -1586,7 +1586,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-16</v>
@@ -1633,7 +1633,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-16</v>
@@ -1680,7 +1680,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-16</v>
@@ -1727,7 +1727,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-16</v>
@@ -1774,7 +1774,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-16</v>
@@ -1821,7 +1821,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-16</v>
@@ -1868,7 +1868,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-16</v>
@@ -1915,7 +1915,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-16</v>
@@ -1962,7 +1962,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-16</v>
@@ -2009,7 +2009,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-16</v>
@@ -2056,7 +2056,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-16</v>
@@ -2103,7 +2103,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-16</v>
@@ -2150,7 +2150,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-16</v>
@@ -2197,7 +2197,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-16</v>
@@ -2244,7 +2244,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-16</v>
@@ -2291,7 +2291,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-16</v>
@@ -2338,7 +2338,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-16</v>
@@ -2385,7 +2385,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-16</v>
@@ -2432,7 +2432,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-16</v>
@@ -2479,7 +2479,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-16</v>
@@ -2526,7 +2526,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-16</v>
@@ -2573,7 +2573,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-16</v>
@@ -2620,7 +2620,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-16</v>
@@ -2667,7 +2667,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-16</v>
@@ -2714,7 +2714,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-16</v>
@@ -2761,7 +2761,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-16</v>
@@ -2808,7 +2808,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-16</v>
@@ -2855,7 +2855,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-16</v>
@@ -2899,10 +2899,10 @@
         <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-16</v>
@@ -2958,10 +2958,10 @@
         <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B63" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-16</v>
@@ -3017,10 +3017,10 @@
         <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-16</v>
@@ -3076,10 +3076,10 @@
         <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B65" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-16</v>
@@ -3135,10 +3135,10 @@
         <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B66" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-16</v>
@@ -3194,10 +3194,10 @@
         <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B67" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-16</v>
@@ -3253,10 +3253,10 @@
         <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B68" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-16</v>
@@ -3312,10 +3312,10 @@
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B69" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-16</v>
@@ -3371,10 +3371,10 @@
         <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B70" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-16</v>
@@ -3430,10 +3430,10 @@
         <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B71" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-16</v>
@@ -3489,10 +3489,10 @@
         <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B72" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-16</v>
@@ -3548,10 +3548,10 @@
         <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B73" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-16</v>
@@ -3607,10 +3607,10 @@
         <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B74" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-16</v>
@@ -3666,10 +3666,10 @@
         <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B75" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-16</v>
@@ -3725,10 +3725,10 @@
         <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B76" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-16</v>
@@ -3784,10 +3784,10 @@
         <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B77" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-16</v>
@@ -3843,10 +3843,10 @@
         <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B78" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-16</v>
@@ -3902,10 +3902,10 @@
         <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B79" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-16</v>
@@ -3961,10 +3961,10 @@
         <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B80" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-16</v>
@@ -4020,10 +4020,10 @@
         <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B81" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-16</v>
@@ -4079,10 +4079,10 @@
         <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B82" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-16</v>
@@ -4138,10 +4138,10 @@
         <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B83" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-16</v>
@@ -4197,10 +4197,10 @@
         <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B84" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-16</v>
@@ -4256,10 +4256,10 @@
         <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B85" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-16</v>
@@ -4315,10 +4315,10 @@
         <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B86" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-16</v>
@@ -4374,10 +4374,10 @@
         <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B87" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-16</v>
@@ -4433,10 +4433,10 @@
         <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B88" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-16</v>
@@ -4492,10 +4492,10 @@
         <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B89" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-16</v>
@@ -4551,10 +4551,10 @@
         <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B90" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-16</v>
@@ -4610,10 +4610,10 @@
         <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B91" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-16</v>
@@ -4664,9 +4664,2139 @@
         <v/>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C92" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v/>
+      </c>
+      <c r="U92" t="str">
+        <v/>
+      </c>
+      <c r="V92" t="str">
+        <v/>
+      </c>
+      <c r="W92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C93" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+      <c r="T93" t="str">
+        <v/>
+      </c>
+      <c r="U93" t="str">
+        <v/>
+      </c>
+      <c r="V93" t="str">
+        <v/>
+      </c>
+      <c r="W93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C94" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <v/>
+      </c>
+      <c r="U94" t="str">
+        <v/>
+      </c>
+      <c r="V94" t="str">
+        <v/>
+      </c>
+      <c r="W94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C95" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <v/>
+      </c>
+      <c r="U95" t="str">
+        <v/>
+      </c>
+      <c r="V95" t="str">
+        <v/>
+      </c>
+      <c r="W95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C96" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <v/>
+      </c>
+      <c r="U96" t="str">
+        <v/>
+      </c>
+      <c r="V96" t="str">
+        <v/>
+      </c>
+      <c r="W96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C97" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+      <c r="T97" t="str">
+        <v/>
+      </c>
+      <c r="U97" t="str">
+        <v/>
+      </c>
+      <c r="V97" t="str">
+        <v/>
+      </c>
+      <c r="W97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C98" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+      <c r="U98" t="str">
+        <v/>
+      </c>
+      <c r="V98" t="str">
+        <v/>
+      </c>
+      <c r="W98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C99" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+      <c r="U99" t="str">
+        <v/>
+      </c>
+      <c r="V99" t="str">
+        <v/>
+      </c>
+      <c r="W99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C100" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+      <c r="U100" t="str">
+        <v/>
+      </c>
+      <c r="V100" t="str">
+        <v/>
+      </c>
+      <c r="W100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C101" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+      <c r="U101" t="str">
+        <v/>
+      </c>
+      <c r="V101" t="str">
+        <v/>
+      </c>
+      <c r="W101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C102" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102" t="str">
+        <v/>
+      </c>
+      <c r="V102" t="str">
+        <v/>
+      </c>
+      <c r="W102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C103" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+      <c r="U103" t="str">
+        <v/>
+      </c>
+      <c r="V103" t="str">
+        <v/>
+      </c>
+      <c r="W103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C104" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+      <c r="U104" t="str">
+        <v/>
+      </c>
+      <c r="V104" t="str">
+        <v/>
+      </c>
+      <c r="W104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C105" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+      <c r="U105" t="str">
+        <v/>
+      </c>
+      <c r="V105" t="str">
+        <v/>
+      </c>
+      <c r="W105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C106" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+      <c r="U106" t="str">
+        <v/>
+      </c>
+      <c r="V106" t="str">
+        <v/>
+      </c>
+      <c r="W106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C107" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+      <c r="U107" t="str">
+        <v/>
+      </c>
+      <c r="V107" t="str">
+        <v/>
+      </c>
+      <c r="W107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C108" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+      <c r="U108" t="str">
+        <v/>
+      </c>
+      <c r="V108" t="str">
+        <v/>
+      </c>
+      <c r="W108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C109" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+      <c r="U109" t="str">
+        <v/>
+      </c>
+      <c r="V109" t="str">
+        <v/>
+      </c>
+      <c r="W109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C110" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+      <c r="U110" t="str">
+        <v/>
+      </c>
+      <c r="V110" t="str">
+        <v/>
+      </c>
+      <c r="W110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C111" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+      <c r="U111" t="str">
+        <v/>
+      </c>
+      <c r="V111" t="str">
+        <v/>
+      </c>
+      <c r="W111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C112" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+      <c r="U112" t="str">
+        <v/>
+      </c>
+      <c r="V112" t="str">
+        <v/>
+      </c>
+      <c r="W112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C113" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+      <c r="U113" t="str">
+        <v/>
+      </c>
+      <c r="V113" t="str">
+        <v/>
+      </c>
+      <c r="W113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C114" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+      <c r="U114" t="str">
+        <v/>
+      </c>
+      <c r="V114" t="str">
+        <v/>
+      </c>
+      <c r="W114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C115" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+      <c r="U115" t="str">
+        <v/>
+      </c>
+      <c r="V115" t="str">
+        <v/>
+      </c>
+      <c r="W115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C116" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v/>
+      </c>
+      <c r="T116" t="str">
+        <v/>
+      </c>
+      <c r="U116" t="str">
+        <v/>
+      </c>
+      <c r="V116" t="str">
+        <v/>
+      </c>
+      <c r="W116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C117" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D117" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+      <c r="T117" t="str">
+        <v/>
+      </c>
+      <c r="U117" t="str">
+        <v/>
+      </c>
+      <c r="V117" t="str">
+        <v/>
+      </c>
+      <c r="W117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C118" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+      <c r="T118" t="str">
+        <v/>
+      </c>
+      <c r="U118" t="str">
+        <v/>
+      </c>
+      <c r="V118" t="str">
+        <v/>
+      </c>
+      <c r="W118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C119" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D119" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119" t="str">
+        <v/>
+      </c>
+      <c r="V119" t="str">
+        <v/>
+      </c>
+      <c r="W119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C120" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120" t="str">
+        <v/>
+      </c>
+      <c r="V120" t="str">
+        <v/>
+      </c>
+      <c r="W120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C121" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v/>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+      <c r="U121" t="str">
+        <v/>
+      </c>
+      <c r="V121" t="str">
+        <v/>
+      </c>
+      <c r="W121" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W121"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W121"/>
+  <dimension ref="A1:AA151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -477,7 +477,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -512,7 +512,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -547,7 +547,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -582,7 +582,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -617,7 +617,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -652,7 +652,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -687,7 +687,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -722,7 +722,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -757,7 +757,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -792,7 +792,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -827,7 +827,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -862,7 +862,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -897,7 +897,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
@@ -932,7 +932,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
@@ -967,7 +967,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
@@ -1002,7 +1002,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
@@ -1037,7 +1037,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
@@ -1072,7 +1072,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
@@ -1107,7 +1107,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
@@ -1142,7 +1142,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
@@ -1177,7 +1177,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
@@ -1212,7 +1212,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
@@ -1247,7 +1247,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
@@ -1282,7 +1282,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
@@ -1317,7 +1317,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
@@ -1352,7 +1352,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
@@ -1387,7 +1387,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-16</v>
@@ -1422,7 +1422,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-16</v>
@@ -1457,7 +1457,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-16</v>
@@ -1492,7 +1492,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-16</v>
@@ -1539,7 +1539,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-16</v>
@@ -1586,7 +1586,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-16</v>
@@ -1633,7 +1633,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-16</v>
@@ -1680,7 +1680,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-16</v>
@@ -1727,7 +1727,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-16</v>
@@ -1774,7 +1774,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-16</v>
@@ -1821,7 +1821,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-16</v>
@@ -1868,7 +1868,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-16</v>
@@ -1915,7 +1915,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-16</v>
@@ -1962,7 +1962,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-16</v>
@@ -2009,7 +2009,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-16</v>
@@ -2056,7 +2056,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-16</v>
@@ -2103,7 +2103,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-16</v>
@@ -2150,7 +2150,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-16</v>
@@ -2197,7 +2197,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-16</v>
@@ -2244,7 +2244,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-16</v>
@@ -2291,7 +2291,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-16</v>
@@ -2338,7 +2338,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-16</v>
@@ -2385,7 +2385,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-16</v>
@@ -2432,7 +2432,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-16</v>
@@ -2479,7 +2479,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-16</v>
@@ -2526,7 +2526,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-16</v>
@@ -2573,7 +2573,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-16</v>
@@ -2620,7 +2620,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-16</v>
@@ -2667,7 +2667,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-16</v>
@@ -2714,7 +2714,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-16</v>
@@ -2761,7 +2761,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-16</v>
@@ -2808,7 +2808,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-16</v>
@@ -2855,7 +2855,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-16</v>
@@ -2902,7 +2902,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-16</v>
@@ -2961,7 +2961,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-16</v>
@@ -3020,7 +3020,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-16</v>
@@ -3079,7 +3079,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-16</v>
@@ -3138,7 +3138,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-16</v>
@@ -3197,7 +3197,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-16</v>
@@ -3256,7 +3256,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-16</v>
@@ -3315,7 +3315,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-16</v>
@@ -3374,7 +3374,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-16</v>
@@ -3433,7 +3433,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-16</v>
@@ -3492,7 +3492,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-16</v>
@@ -3551,7 +3551,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-16</v>
@@ -3610,7 +3610,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-16</v>
@@ -3669,7 +3669,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-16</v>
@@ -3728,7 +3728,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-16</v>
@@ -3787,7 +3787,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-16</v>
@@ -3846,7 +3846,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-16</v>
@@ -3905,7 +3905,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-16</v>
@@ -3964,7 +3964,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-16</v>
@@ -4023,7 +4023,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-16</v>
@@ -4082,7 +4082,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-16</v>
@@ -4141,7 +4141,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-16</v>
@@ -4200,7 +4200,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-16</v>
@@ -4259,7 +4259,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-16</v>
@@ -4318,7 +4318,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-16</v>
@@ -4377,7 +4377,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-16</v>
@@ -4436,7 +4436,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-16</v>
@@ -4495,7 +4495,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-16</v>
@@ -4554,7 +4554,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-16</v>
@@ -4613,7 +4613,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-16</v>
@@ -4669,10 +4669,10 @@
         <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B92" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-16</v>
@@ -4740,10 +4740,10 @@
         <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B93" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-16</v>
@@ -4811,10 +4811,10 @@
         <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B94" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-16</v>
@@ -4882,10 +4882,10 @@
         <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B95" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-16</v>
@@ -4953,10 +4953,10 @@
         <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B96" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-16</v>
@@ -5024,10 +5024,10 @@
         <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B97" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C97" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-16</v>
@@ -5095,10 +5095,10 @@
         <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B98" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C98" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-16</v>
@@ -5166,10 +5166,10 @@
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B99" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C99" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-16</v>
@@ -5237,10 +5237,10 @@
         <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B100" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C100" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-16</v>
@@ -5308,10 +5308,10 @@
         <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B101" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C101" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-16</v>
@@ -5379,10 +5379,10 @@
         <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B102" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C102" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-16</v>
@@ -5450,10 +5450,10 @@
         <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B103" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C103" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-16</v>
@@ -5521,10 +5521,10 @@
         <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B104" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C104" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-16</v>
@@ -5592,10 +5592,10 @@
         <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B105" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C105" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-16</v>
@@ -5663,10 +5663,10 @@
         <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B106" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C106" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-16</v>
@@ -5734,10 +5734,10 @@
         <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B107" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C107" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-16</v>
@@ -5805,10 +5805,10 @@
         <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B108" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C108" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-16</v>
@@ -5876,10 +5876,10 @@
         <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B109" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C109" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-16</v>
@@ -5947,10 +5947,10 @@
         <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B110" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C110" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-16</v>
@@ -6018,10 +6018,10 @@
         <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B111" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C111" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-16</v>
@@ -6089,10 +6089,10 @@
         <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B112" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C112" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-16</v>
@@ -6160,10 +6160,10 @@
         <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B113" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C113" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-16</v>
@@ -6231,10 +6231,10 @@
         <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B114" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C114" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-16</v>
@@ -6302,10 +6302,10 @@
         <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B115" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C115" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-16</v>
@@ -6373,10 +6373,10 @@
         <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B116" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C116" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-16</v>
@@ -6444,10 +6444,10 @@
         <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B117" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C117" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-16</v>
@@ -6515,10 +6515,10 @@
         <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B118" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C118" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-16</v>
@@ -6586,10 +6586,10 @@
         <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B119" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C119" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-16</v>
@@ -6657,10 +6657,10 @@
         <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B120" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C120" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-16</v>
@@ -6728,10 +6728,10 @@
         <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B121" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C121" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-16</v>
@@ -6794,9 +6794,2499 @@
         <v/>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C122" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v/>
+      </c>
+      <c r="T122" t="str">
+        <v/>
+      </c>
+      <c r="U122" t="str">
+        <v/>
+      </c>
+      <c r="V122" t="str">
+        <v/>
+      </c>
+      <c r="W122" t="str">
+        <v/>
+      </c>
+      <c r="X122" t="str">
+        <v/>
+      </c>
+      <c r="Y122" t="str">
+        <v/>
+      </c>
+      <c r="Z122" t="str">
+        <v/>
+      </c>
+      <c r="AA122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C123" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+      <c r="T123" t="str">
+        <v/>
+      </c>
+      <c r="U123" t="str">
+        <v/>
+      </c>
+      <c r="V123" t="str">
+        <v/>
+      </c>
+      <c r="W123" t="str">
+        <v/>
+      </c>
+      <c r="X123" t="str">
+        <v/>
+      </c>
+      <c r="Y123" t="str">
+        <v/>
+      </c>
+      <c r="Z123" t="str">
+        <v/>
+      </c>
+      <c r="AA123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C124" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+      <c r="U124" t="str">
+        <v/>
+      </c>
+      <c r="V124" t="str">
+        <v/>
+      </c>
+      <c r="W124" t="str">
+        <v/>
+      </c>
+      <c r="X124" t="str">
+        <v/>
+      </c>
+      <c r="Y124" t="str">
+        <v/>
+      </c>
+      <c r="Z124" t="str">
+        <v/>
+      </c>
+      <c r="AA124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C125" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v/>
+      </c>
+      <c r="T125" t="str">
+        <v/>
+      </c>
+      <c r="U125" t="str">
+        <v/>
+      </c>
+      <c r="V125" t="str">
+        <v/>
+      </c>
+      <c r="W125" t="str">
+        <v/>
+      </c>
+      <c r="X125" t="str">
+        <v/>
+      </c>
+      <c r="Y125" t="str">
+        <v/>
+      </c>
+      <c r="Z125" t="str">
+        <v/>
+      </c>
+      <c r="AA125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C126" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D126" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+      <c r="T126" t="str">
+        <v/>
+      </c>
+      <c r="U126" t="str">
+        <v/>
+      </c>
+      <c r="V126" t="str">
+        <v/>
+      </c>
+      <c r="W126" t="str">
+        <v/>
+      </c>
+      <c r="X126" t="str">
+        <v/>
+      </c>
+      <c r="Y126" t="str">
+        <v/>
+      </c>
+      <c r="Z126" t="str">
+        <v/>
+      </c>
+      <c r="AA126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C127" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D127" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127" t="str">
+        <v/>
+      </c>
+      <c r="V127" t="str">
+        <v/>
+      </c>
+      <c r="W127" t="str">
+        <v/>
+      </c>
+      <c r="X127" t="str">
+        <v/>
+      </c>
+      <c r="Y127" t="str">
+        <v/>
+      </c>
+      <c r="Z127" t="str">
+        <v/>
+      </c>
+      <c r="AA127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C128" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+      <c r="U128" t="str">
+        <v/>
+      </c>
+      <c r="V128" t="str">
+        <v/>
+      </c>
+      <c r="W128" t="str">
+        <v/>
+      </c>
+      <c r="X128" t="str">
+        <v/>
+      </c>
+      <c r="Y128" t="str">
+        <v/>
+      </c>
+      <c r="Z128" t="str">
+        <v/>
+      </c>
+      <c r="AA128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C129" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D129" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129" t="str">
+        <v/>
+      </c>
+      <c r="V129" t="str">
+        <v/>
+      </c>
+      <c r="W129" t="str">
+        <v/>
+      </c>
+      <c r="X129" t="str">
+        <v/>
+      </c>
+      <c r="Y129" t="str">
+        <v/>
+      </c>
+      <c r="Z129" t="str">
+        <v/>
+      </c>
+      <c r="AA129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C130" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D130" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+      <c r="U130" t="str">
+        <v/>
+      </c>
+      <c r="V130" t="str">
+        <v/>
+      </c>
+      <c r="W130" t="str">
+        <v/>
+      </c>
+      <c r="X130" t="str">
+        <v/>
+      </c>
+      <c r="Y130" t="str">
+        <v/>
+      </c>
+      <c r="Z130" t="str">
+        <v/>
+      </c>
+      <c r="AA130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C131" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D131" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v/>
+      </c>
+      <c r="T131" t="str">
+        <v/>
+      </c>
+      <c r="U131" t="str">
+        <v/>
+      </c>
+      <c r="V131" t="str">
+        <v/>
+      </c>
+      <c r="W131" t="str">
+        <v/>
+      </c>
+      <c r="X131" t="str">
+        <v/>
+      </c>
+      <c r="Y131" t="str">
+        <v/>
+      </c>
+      <c r="Z131" t="str">
+        <v/>
+      </c>
+      <c r="AA131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C132" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D132" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+      <c r="T132" t="str">
+        <v/>
+      </c>
+      <c r="U132" t="str">
+        <v/>
+      </c>
+      <c r="V132" t="str">
+        <v/>
+      </c>
+      <c r="W132" t="str">
+        <v/>
+      </c>
+      <c r="X132" t="str">
+        <v/>
+      </c>
+      <c r="Y132" t="str">
+        <v/>
+      </c>
+      <c r="Z132" t="str">
+        <v/>
+      </c>
+      <c r="AA132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="B133" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C133" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D133" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+      <c r="U133" t="str">
+        <v/>
+      </c>
+      <c r="V133" t="str">
+        <v/>
+      </c>
+      <c r="W133" t="str">
+        <v/>
+      </c>
+      <c r="X133" t="str">
+        <v/>
+      </c>
+      <c r="Y133" t="str">
+        <v/>
+      </c>
+      <c r="Z133" t="str">
+        <v/>
+      </c>
+      <c r="AA133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C134" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D134" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
+      <c r="V134" t="str">
+        <v/>
+      </c>
+      <c r="W134" t="str">
+        <v/>
+      </c>
+      <c r="X134" t="str">
+        <v/>
+      </c>
+      <c r="Y134" t="str">
+        <v/>
+      </c>
+      <c r="Z134" t="str">
+        <v/>
+      </c>
+      <c r="AA134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C135" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D135" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
+        <v/>
+      </c>
+      <c r="V135" t="str">
+        <v/>
+      </c>
+      <c r="W135" t="str">
+        <v/>
+      </c>
+      <c r="X135" t="str">
+        <v/>
+      </c>
+      <c r="Y135" t="str">
+        <v/>
+      </c>
+      <c r="Z135" t="str">
+        <v/>
+      </c>
+      <c r="AA135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C136" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D136" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v/>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+      <c r="U136" t="str">
+        <v/>
+      </c>
+      <c r="V136" t="str">
+        <v/>
+      </c>
+      <c r="W136" t="str">
+        <v/>
+      </c>
+      <c r="X136" t="str">
+        <v/>
+      </c>
+      <c r="Y136" t="str">
+        <v/>
+      </c>
+      <c r="Z136" t="str">
+        <v/>
+      </c>
+      <c r="AA136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C137" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D137" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137" t="str">
+        <v/>
+      </c>
+      <c r="V137" t="str">
+        <v/>
+      </c>
+      <c r="W137" t="str">
+        <v/>
+      </c>
+      <c r="X137" t="str">
+        <v/>
+      </c>
+      <c r="Y137" t="str">
+        <v/>
+      </c>
+      <c r="Z137" t="str">
+        <v/>
+      </c>
+      <c r="AA137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C138" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D138" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138" t="str">
+        <v/>
+      </c>
+      <c r="V138" t="str">
+        <v/>
+      </c>
+      <c r="W138" t="str">
+        <v/>
+      </c>
+      <c r="X138" t="str">
+        <v/>
+      </c>
+      <c r="Y138" t="str">
+        <v/>
+      </c>
+      <c r="Z138" t="str">
+        <v/>
+      </c>
+      <c r="AA138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C139" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D139" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
+      <c r="V139" t="str">
+        <v/>
+      </c>
+      <c r="W139" t="str">
+        <v/>
+      </c>
+      <c r="X139" t="str">
+        <v/>
+      </c>
+      <c r="Y139" t="str">
+        <v/>
+      </c>
+      <c r="Z139" t="str">
+        <v/>
+      </c>
+      <c r="AA139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C140" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D140" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" t="str">
+        <v/>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+      <c r="U140" t="str">
+        <v/>
+      </c>
+      <c r="V140" t="str">
+        <v/>
+      </c>
+      <c r="W140" t="str">
+        <v/>
+      </c>
+      <c r="X140" t="str">
+        <v/>
+      </c>
+      <c r="Y140" t="str">
+        <v/>
+      </c>
+      <c r="Z140" t="str">
+        <v/>
+      </c>
+      <c r="AA140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C141" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D141" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v/>
+      </c>
+      <c r="T141" t="str">
+        <v/>
+      </c>
+      <c r="U141" t="str">
+        <v/>
+      </c>
+      <c r="V141" t="str">
+        <v/>
+      </c>
+      <c r="W141" t="str">
+        <v/>
+      </c>
+      <c r="X141" t="str">
+        <v/>
+      </c>
+      <c r="Y141" t="str">
+        <v/>
+      </c>
+      <c r="Z141" t="str">
+        <v/>
+      </c>
+      <c r="AA141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C142" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D142" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v/>
+      </c>
+      <c r="T142" t="str">
+        <v/>
+      </c>
+      <c r="U142" t="str">
+        <v/>
+      </c>
+      <c r="V142" t="str">
+        <v/>
+      </c>
+      <c r="W142" t="str">
+        <v/>
+      </c>
+      <c r="X142" t="str">
+        <v/>
+      </c>
+      <c r="Y142" t="str">
+        <v/>
+      </c>
+      <c r="Z142" t="str">
+        <v/>
+      </c>
+      <c r="AA142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C143" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D143" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v/>
+      </c>
+      <c r="T143" t="str">
+        <v/>
+      </c>
+      <c r="U143" t="str">
+        <v/>
+      </c>
+      <c r="V143" t="str">
+        <v/>
+      </c>
+      <c r="W143" t="str">
+        <v/>
+      </c>
+      <c r="X143" t="str">
+        <v/>
+      </c>
+      <c r="Y143" t="str">
+        <v/>
+      </c>
+      <c r="Z143" t="str">
+        <v/>
+      </c>
+      <c r="AA143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C144" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D144" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v/>
+      </c>
+      <c r="T144" t="str">
+        <v/>
+      </c>
+      <c r="U144" t="str">
+        <v/>
+      </c>
+      <c r="V144" t="str">
+        <v/>
+      </c>
+      <c r="W144" t="str">
+        <v/>
+      </c>
+      <c r="X144" t="str">
+        <v/>
+      </c>
+      <c r="Y144" t="str">
+        <v/>
+      </c>
+      <c r="Z144" t="str">
+        <v/>
+      </c>
+      <c r="AA144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C145" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D145" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v/>
+      </c>
+      <c r="T145" t="str">
+        <v/>
+      </c>
+      <c r="U145" t="str">
+        <v/>
+      </c>
+      <c r="V145" t="str">
+        <v/>
+      </c>
+      <c r="W145" t="str">
+        <v/>
+      </c>
+      <c r="X145" t="str">
+        <v/>
+      </c>
+      <c r="Y145" t="str">
+        <v/>
+      </c>
+      <c r="Z145" t="str">
+        <v/>
+      </c>
+      <c r="AA145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C146" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D146" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E146" t="str">
+        <v/>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v/>
+      </c>
+      <c r="T146" t="str">
+        <v/>
+      </c>
+      <c r="U146" t="str">
+        <v/>
+      </c>
+      <c r="V146" t="str">
+        <v/>
+      </c>
+      <c r="W146" t="str">
+        <v/>
+      </c>
+      <c r="X146" t="str">
+        <v/>
+      </c>
+      <c r="Y146" t="str">
+        <v/>
+      </c>
+      <c r="Z146" t="str">
+        <v/>
+      </c>
+      <c r="AA146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C147" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D147" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E147" t="str">
+        <v/>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v/>
+      </c>
+      <c r="T147" t="str">
+        <v/>
+      </c>
+      <c r="U147" t="str">
+        <v/>
+      </c>
+      <c r="V147" t="str">
+        <v/>
+      </c>
+      <c r="W147" t="str">
+        <v/>
+      </c>
+      <c r="X147" t="str">
+        <v/>
+      </c>
+      <c r="Y147" t="str">
+        <v/>
+      </c>
+      <c r="Z147" t="str">
+        <v/>
+      </c>
+      <c r="AA147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C148" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D148" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E148" t="str">
+        <v/>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v/>
+      </c>
+      <c r="T148" t="str">
+        <v/>
+      </c>
+      <c r="U148" t="str">
+        <v/>
+      </c>
+      <c r="V148" t="str">
+        <v/>
+      </c>
+      <c r="W148" t="str">
+        <v/>
+      </c>
+      <c r="X148" t="str">
+        <v/>
+      </c>
+      <c r="Y148" t="str">
+        <v/>
+      </c>
+      <c r="Z148" t="str">
+        <v/>
+      </c>
+      <c r="AA148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C149" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D149" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E149" t="str">
+        <v/>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v/>
+      </c>
+      <c r="T149" t="str">
+        <v/>
+      </c>
+      <c r="U149" t="str">
+        <v/>
+      </c>
+      <c r="V149" t="str">
+        <v/>
+      </c>
+      <c r="W149" t="str">
+        <v/>
+      </c>
+      <c r="X149" t="str">
+        <v/>
+      </c>
+      <c r="Y149" t="str">
+        <v/>
+      </c>
+      <c r="Z149" t="str">
+        <v/>
+      </c>
+      <c r="AA149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C150" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D150" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v/>
+      </c>
+      <c r="T150" t="str">
+        <v/>
+      </c>
+      <c r="U150" t="str">
+        <v/>
+      </c>
+      <c r="V150" t="str">
+        <v/>
+      </c>
+      <c r="W150" t="str">
+        <v/>
+      </c>
+      <c r="X150" t="str">
+        <v/>
+      </c>
+      <c r="Y150" t="str">
+        <v/>
+      </c>
+      <c r="Z150" t="str">
+        <v/>
+      </c>
+      <c r="AA150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C151" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D151" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E151" t="str">
+        <v/>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v/>
+      </c>
+      <c r="T151" t="str">
+        <v/>
+      </c>
+      <c r="U151" t="str">
+        <v/>
+      </c>
+      <c r="V151" t="str">
+        <v/>
+      </c>
+      <c r="W151" t="str">
+        <v/>
+      </c>
+      <c r="X151" t="str">
+        <v/>
+      </c>
+      <c r="Y151" t="str">
+        <v/>
+      </c>
+      <c r="Z151" t="str">
+        <v/>
+      </c>
+      <c r="AA151" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA151"/>
+  <dimension ref="A1:AE181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-16</v>
@@ -477,7 +477,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-16</v>
@@ -512,7 +512,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-16</v>
@@ -547,7 +547,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-16</v>
@@ -582,7 +582,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-16</v>
@@ -617,7 +617,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-16</v>
@@ -652,7 +652,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-16</v>
@@ -687,7 +687,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-16</v>
@@ -722,7 +722,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-16</v>
@@ -757,7 +757,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-16</v>
@@ -792,7 +792,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-16</v>
@@ -827,7 +827,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-16</v>
@@ -862,7 +862,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-16</v>
@@ -897,7 +897,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-16</v>
@@ -932,7 +932,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-16</v>
@@ -967,7 +967,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-16</v>
@@ -1002,7 +1002,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-16</v>
@@ -1037,7 +1037,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-16</v>
@@ -1072,7 +1072,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-16</v>
@@ -1107,7 +1107,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-16</v>
@@ -1142,7 +1142,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-16</v>
@@ -1177,7 +1177,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-16</v>
@@ -1212,7 +1212,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-16</v>
@@ -1247,7 +1247,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-16</v>
@@ -1282,7 +1282,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-16</v>
@@ -1317,7 +1317,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-16</v>
@@ -1352,7 +1352,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-16</v>
@@ -1387,7 +1387,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-16</v>
@@ -1422,7 +1422,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-16</v>
@@ -1457,7 +1457,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-16</v>
@@ -1492,7 +1492,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-16</v>
@@ -1539,7 +1539,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-16</v>
@@ -1586,7 +1586,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-16</v>
@@ -1633,7 +1633,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-16</v>
@@ -1680,7 +1680,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-16</v>
@@ -1727,7 +1727,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-16</v>
@@ -1774,7 +1774,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-16</v>
@@ -1821,7 +1821,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-16</v>
@@ -1868,7 +1868,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-16</v>
@@ -1915,7 +1915,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-16</v>
@@ -1962,7 +1962,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-16</v>
@@ -2009,7 +2009,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-16</v>
@@ -2056,7 +2056,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-16</v>
@@ -2103,7 +2103,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-16</v>
@@ -2150,7 +2150,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-16</v>
@@ -2197,7 +2197,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-16</v>
@@ -2244,7 +2244,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-16</v>
@@ -2291,7 +2291,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-16</v>
@@ -2338,7 +2338,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-16</v>
@@ -2385,7 +2385,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-16</v>
@@ -2432,7 +2432,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-16</v>
@@ -2479,7 +2479,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-16</v>
@@ -2526,7 +2526,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-16</v>
@@ -2573,7 +2573,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-16</v>
@@ -2620,7 +2620,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-16</v>
@@ -2667,7 +2667,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-16</v>
@@ -2714,7 +2714,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-16</v>
@@ -2761,7 +2761,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-16</v>
@@ -2808,7 +2808,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-16</v>
@@ -2855,7 +2855,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-16</v>
@@ -2902,7 +2902,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-16</v>
@@ -2961,7 +2961,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-16</v>
@@ -3020,7 +3020,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-16</v>
@@ -3079,7 +3079,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-16</v>
@@ -3138,7 +3138,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-16</v>
@@ -3197,7 +3197,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-16</v>
@@ -3256,7 +3256,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-16</v>
@@ -3315,7 +3315,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-16</v>
@@ -3374,7 +3374,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-16</v>
@@ -3433,7 +3433,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-16</v>
@@ -3492,7 +3492,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-16</v>
@@ -3551,7 +3551,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-16</v>
@@ -3610,7 +3610,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-16</v>
@@ -3669,7 +3669,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-16</v>
@@ -3728,7 +3728,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-16</v>
@@ -3787,7 +3787,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-16</v>
@@ -3846,7 +3846,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-16</v>
@@ -3905,7 +3905,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-16</v>
@@ -3964,7 +3964,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-16</v>
@@ -4023,7 +4023,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-16</v>
@@ -4082,7 +4082,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-16</v>
@@ -4141,7 +4141,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-16</v>
@@ -4200,7 +4200,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-16</v>
@@ -4259,7 +4259,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-16</v>
@@ -4318,7 +4318,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-16</v>
@@ -4377,7 +4377,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-16</v>
@@ -4436,7 +4436,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-16</v>
@@ -4495,7 +4495,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-16</v>
@@ -4554,7 +4554,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-16</v>
@@ -4613,7 +4613,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-16</v>
@@ -4672,7 +4672,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-16</v>
@@ -4743,7 +4743,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-16</v>
@@ -4814,7 +4814,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-16</v>
@@ -4885,7 +4885,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-16</v>
@@ -4956,7 +4956,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-16</v>
@@ -5027,7 +5027,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C97" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-16</v>
@@ -5098,7 +5098,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C98" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-16</v>
@@ -5169,7 +5169,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C99" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-16</v>
@@ -5240,7 +5240,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C100" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-16</v>
@@ -5311,7 +5311,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C101" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-16</v>
@@ -5382,7 +5382,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C102" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-16</v>
@@ -5453,7 +5453,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C103" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-16</v>
@@ -5524,7 +5524,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C104" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-16</v>
@@ -5595,7 +5595,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C105" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-16</v>
@@ -5666,7 +5666,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C106" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-16</v>
@@ -5737,7 +5737,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C107" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-16</v>
@@ -5808,7 +5808,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C108" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-16</v>
@@ -5879,7 +5879,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C109" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-16</v>
@@ -5950,7 +5950,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C110" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-16</v>
@@ -6021,7 +6021,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C111" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-16</v>
@@ -6092,7 +6092,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C112" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-16</v>
@@ -6163,7 +6163,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C113" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-16</v>
@@ -6234,7 +6234,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C114" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-16</v>
@@ -6305,7 +6305,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C115" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-16</v>
@@ -6376,7 +6376,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C116" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-16</v>
@@ -6447,7 +6447,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C117" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-16</v>
@@ -6518,7 +6518,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C118" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-16</v>
@@ -6589,7 +6589,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C119" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-16</v>
@@ -6660,7 +6660,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C120" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-16</v>
@@ -6731,7 +6731,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C121" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-16</v>
@@ -6799,10 +6799,10 @@
         <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B122" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C122" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-16</v>
@@ -6882,10 +6882,10 @@
         <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B123" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C123" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-16</v>
@@ -6965,10 +6965,10 @@
         <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B124" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C124" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-16</v>
@@ -7048,10 +7048,10 @@
         <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B125" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C125" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-16</v>
@@ -7131,10 +7131,10 @@
         <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B126" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C126" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-16</v>
@@ -7214,10 +7214,10 @@
         <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B127" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C127" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-16</v>
@@ -7297,10 +7297,10 @@
         <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B128" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C128" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-16</v>
@@ -7380,10 +7380,10 @@
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B129" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C129" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-16</v>
@@ -7463,10 +7463,10 @@
         <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B130" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C130" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-16</v>
@@ -7546,10 +7546,10 @@
         <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B131" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C131" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-16</v>
@@ -7629,10 +7629,10 @@
         <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B132" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C132" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-16</v>
@@ -7712,10 +7712,10 @@
         <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B133" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C133" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-16</v>
@@ -7795,10 +7795,10 @@
         <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B134" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C134" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-16</v>
@@ -7878,10 +7878,10 @@
         <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B135" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C135" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-16</v>
@@ -7961,10 +7961,10 @@
         <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B136" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C136" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-16</v>
@@ -8044,10 +8044,10 @@
         <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B137" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C137" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-16</v>
@@ -8127,10 +8127,10 @@
         <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B138" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C138" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-16</v>
@@ -8210,10 +8210,10 @@
         <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B139" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C139" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-16</v>
@@ -8293,10 +8293,10 @@
         <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B140" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C140" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-16</v>
@@ -8376,10 +8376,10 @@
         <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B141" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C141" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-16</v>
@@ -8459,10 +8459,10 @@
         <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B142" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C142" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-16</v>
@@ -8542,10 +8542,10 @@
         <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B143" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C143" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-16</v>
@@ -8625,10 +8625,10 @@
         <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B144" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C144" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-16</v>
@@ -8708,10 +8708,10 @@
         <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B145" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C145" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-16</v>
@@ -8791,10 +8791,10 @@
         <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B146" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C146" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-16</v>
@@ -8874,10 +8874,10 @@
         <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B147" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C147" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-16</v>
@@ -8957,10 +8957,10 @@
         <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B148" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C148" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-16</v>
@@ -9040,10 +9040,10 @@
         <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B149" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C149" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-16</v>
@@ -9123,10 +9123,10 @@
         <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B150" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C150" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-16</v>
@@ -9206,10 +9206,10 @@
         <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B151" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C151" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-16</v>
@@ -9284,9 +9284,2859 @@
         <v/>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C152" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D152" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v/>
+      </c>
+      <c r="T152" t="str">
+        <v/>
+      </c>
+      <c r="U152" t="str">
+        <v/>
+      </c>
+      <c r="V152" t="str">
+        <v/>
+      </c>
+      <c r="W152" t="str">
+        <v/>
+      </c>
+      <c r="X152" t="str">
+        <v/>
+      </c>
+      <c r="Y152" t="str">
+        <v/>
+      </c>
+      <c r="Z152" t="str">
+        <v/>
+      </c>
+      <c r="AA152" t="str">
+        <v/>
+      </c>
+      <c r="AB152" t="str">
+        <v/>
+      </c>
+      <c r="AC152" t="str">
+        <v/>
+      </c>
+      <c r="AD152" t="str">
+        <v/>
+      </c>
+      <c r="AE152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C153" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D153" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E153" t="str">
+        <v/>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v/>
+      </c>
+      <c r="T153" t="str">
+        <v/>
+      </c>
+      <c r="U153" t="str">
+        <v/>
+      </c>
+      <c r="V153" t="str">
+        <v/>
+      </c>
+      <c r="W153" t="str">
+        <v/>
+      </c>
+      <c r="X153" t="str">
+        <v/>
+      </c>
+      <c r="Y153" t="str">
+        <v/>
+      </c>
+      <c r="Z153" t="str">
+        <v/>
+      </c>
+      <c r="AA153" t="str">
+        <v/>
+      </c>
+      <c r="AB153" t="str">
+        <v/>
+      </c>
+      <c r="AC153" t="str">
+        <v/>
+      </c>
+      <c r="AD153" t="str">
+        <v/>
+      </c>
+      <c r="AE153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C154" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D154" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E154" t="str">
+        <v/>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
+      <c r="R154" t="str">
+        <v/>
+      </c>
+      <c r="S154" t="str">
+        <v/>
+      </c>
+      <c r="T154" t="str">
+        <v/>
+      </c>
+      <c r="U154" t="str">
+        <v/>
+      </c>
+      <c r="V154" t="str">
+        <v/>
+      </c>
+      <c r="W154" t="str">
+        <v/>
+      </c>
+      <c r="X154" t="str">
+        <v/>
+      </c>
+      <c r="Y154" t="str">
+        <v/>
+      </c>
+      <c r="Z154" t="str">
+        <v/>
+      </c>
+      <c r="AA154" t="str">
+        <v/>
+      </c>
+      <c r="AB154" t="str">
+        <v/>
+      </c>
+      <c r="AC154" t="str">
+        <v/>
+      </c>
+      <c r="AD154" t="str">
+        <v/>
+      </c>
+      <c r="AE154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="B155" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C155" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D155" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E155" t="str">
+        <v/>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
+      <c r="R155" t="str">
+        <v/>
+      </c>
+      <c r="S155" t="str">
+        <v/>
+      </c>
+      <c r="T155" t="str">
+        <v/>
+      </c>
+      <c r="U155" t="str">
+        <v/>
+      </c>
+      <c r="V155" t="str">
+        <v/>
+      </c>
+      <c r="W155" t="str">
+        <v/>
+      </c>
+      <c r="X155" t="str">
+        <v/>
+      </c>
+      <c r="Y155" t="str">
+        <v/>
+      </c>
+      <c r="Z155" t="str">
+        <v/>
+      </c>
+      <c r="AA155" t="str">
+        <v/>
+      </c>
+      <c r="AB155" t="str">
+        <v/>
+      </c>
+      <c r="AC155" t="str">
+        <v/>
+      </c>
+      <c r="AD155" t="str">
+        <v/>
+      </c>
+      <c r="AE155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="B156" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C156" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D156" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E156" t="str">
+        <v/>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v/>
+      </c>
+      <c r="K156" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
+      <c r="R156" t="str">
+        <v/>
+      </c>
+      <c r="S156" t="str">
+        <v/>
+      </c>
+      <c r="T156" t="str">
+        <v/>
+      </c>
+      <c r="U156" t="str">
+        <v/>
+      </c>
+      <c r="V156" t="str">
+        <v/>
+      </c>
+      <c r="W156" t="str">
+        <v/>
+      </c>
+      <c r="X156" t="str">
+        <v/>
+      </c>
+      <c r="Y156" t="str">
+        <v/>
+      </c>
+      <c r="Z156" t="str">
+        <v/>
+      </c>
+      <c r="AA156" t="str">
+        <v/>
+      </c>
+      <c r="AB156" t="str">
+        <v/>
+      </c>
+      <c r="AC156" t="str">
+        <v/>
+      </c>
+      <c r="AD156" t="str">
+        <v/>
+      </c>
+      <c r="AE156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="B157" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C157" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D157" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E157" t="str">
+        <v/>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
+        <v/>
+      </c>
+      <c r="T157" t="str">
+        <v/>
+      </c>
+      <c r="U157" t="str">
+        <v/>
+      </c>
+      <c r="V157" t="str">
+        <v/>
+      </c>
+      <c r="W157" t="str">
+        <v/>
+      </c>
+      <c r="X157" t="str">
+        <v/>
+      </c>
+      <c r="Y157" t="str">
+        <v/>
+      </c>
+      <c r="Z157" t="str">
+        <v/>
+      </c>
+      <c r="AA157" t="str">
+        <v/>
+      </c>
+      <c r="AB157" t="str">
+        <v/>
+      </c>
+      <c r="AC157" t="str">
+        <v/>
+      </c>
+      <c r="AD157" t="str">
+        <v/>
+      </c>
+      <c r="AE157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="B158" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C158" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D158" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v/>
+      </c>
+      <c r="K158" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
+      <c r="R158" t="str">
+        <v/>
+      </c>
+      <c r="S158" t="str">
+        <v/>
+      </c>
+      <c r="T158" t="str">
+        <v/>
+      </c>
+      <c r="U158" t="str">
+        <v/>
+      </c>
+      <c r="V158" t="str">
+        <v/>
+      </c>
+      <c r="W158" t="str">
+        <v/>
+      </c>
+      <c r="X158" t="str">
+        <v/>
+      </c>
+      <c r="Y158" t="str">
+        <v/>
+      </c>
+      <c r="Z158" t="str">
+        <v/>
+      </c>
+      <c r="AA158" t="str">
+        <v/>
+      </c>
+      <c r="AB158" t="str">
+        <v/>
+      </c>
+      <c r="AC158" t="str">
+        <v/>
+      </c>
+      <c r="AD158" t="str">
+        <v/>
+      </c>
+      <c r="AE158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="B159" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C159" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D159" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E159" t="str">
+        <v/>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v/>
+      </c>
+      <c r="K159" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
+      <c r="R159" t="str">
+        <v/>
+      </c>
+      <c r="S159" t="str">
+        <v/>
+      </c>
+      <c r="T159" t="str">
+        <v/>
+      </c>
+      <c r="U159" t="str">
+        <v/>
+      </c>
+      <c r="V159" t="str">
+        <v/>
+      </c>
+      <c r="W159" t="str">
+        <v/>
+      </c>
+      <c r="X159" t="str">
+        <v/>
+      </c>
+      <c r="Y159" t="str">
+        <v/>
+      </c>
+      <c r="Z159" t="str">
+        <v/>
+      </c>
+      <c r="AA159" t="str">
+        <v/>
+      </c>
+      <c r="AB159" t="str">
+        <v/>
+      </c>
+      <c r="AC159" t="str">
+        <v/>
+      </c>
+      <c r="AD159" t="str">
+        <v/>
+      </c>
+      <c r="AE159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C160" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D160" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E160" t="str">
+        <v/>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v/>
+      </c>
+      <c r="K160" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
+      <c r="R160" t="str">
+        <v/>
+      </c>
+      <c r="S160" t="str">
+        <v/>
+      </c>
+      <c r="T160" t="str">
+        <v/>
+      </c>
+      <c r="U160" t="str">
+        <v/>
+      </c>
+      <c r="V160" t="str">
+        <v/>
+      </c>
+      <c r="W160" t="str">
+        <v/>
+      </c>
+      <c r="X160" t="str">
+        <v/>
+      </c>
+      <c r="Y160" t="str">
+        <v/>
+      </c>
+      <c r="Z160" t="str">
+        <v/>
+      </c>
+      <c r="AA160" t="str">
+        <v/>
+      </c>
+      <c r="AB160" t="str">
+        <v/>
+      </c>
+      <c r="AC160" t="str">
+        <v/>
+      </c>
+      <c r="AD160" t="str">
+        <v/>
+      </c>
+      <c r="AE160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C161" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D161" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E161" t="str">
+        <v/>
+      </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161" t="str">
+        <v/>
+      </c>
+      <c r="K161" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
+      <c r="R161" t="str">
+        <v/>
+      </c>
+      <c r="S161" t="str">
+        <v/>
+      </c>
+      <c r="T161" t="str">
+        <v/>
+      </c>
+      <c r="U161" t="str">
+        <v/>
+      </c>
+      <c r="V161" t="str">
+        <v/>
+      </c>
+      <c r="W161" t="str">
+        <v/>
+      </c>
+      <c r="X161" t="str">
+        <v/>
+      </c>
+      <c r="Y161" t="str">
+        <v/>
+      </c>
+      <c r="Z161" t="str">
+        <v/>
+      </c>
+      <c r="AA161" t="str">
+        <v/>
+      </c>
+      <c r="AB161" t="str">
+        <v/>
+      </c>
+      <c r="AC161" t="str">
+        <v/>
+      </c>
+      <c r="AD161" t="str">
+        <v/>
+      </c>
+      <c r="AE161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C162" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D162" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E162" t="str">
+        <v/>
+      </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v/>
+      </c>
+      <c r="K162" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
+      <c r="R162" t="str">
+        <v/>
+      </c>
+      <c r="S162" t="str">
+        <v/>
+      </c>
+      <c r="T162" t="str">
+        <v/>
+      </c>
+      <c r="U162" t="str">
+        <v/>
+      </c>
+      <c r="V162" t="str">
+        <v/>
+      </c>
+      <c r="W162" t="str">
+        <v/>
+      </c>
+      <c r="X162" t="str">
+        <v/>
+      </c>
+      <c r="Y162" t="str">
+        <v/>
+      </c>
+      <c r="Z162" t="str">
+        <v/>
+      </c>
+      <c r="AA162" t="str">
+        <v/>
+      </c>
+      <c r="AB162" t="str">
+        <v/>
+      </c>
+      <c r="AC162" t="str">
+        <v/>
+      </c>
+      <c r="AD162" t="str">
+        <v/>
+      </c>
+      <c r="AE162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C163" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D163" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E163" t="str">
+        <v/>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
+      <c r="V163" t="str">
+        <v/>
+      </c>
+      <c r="W163" t="str">
+        <v/>
+      </c>
+      <c r="X163" t="str">
+        <v/>
+      </c>
+      <c r="Y163" t="str">
+        <v/>
+      </c>
+      <c r="Z163" t="str">
+        <v/>
+      </c>
+      <c r="AA163" t="str">
+        <v/>
+      </c>
+      <c r="AB163" t="str">
+        <v/>
+      </c>
+      <c r="AC163" t="str">
+        <v/>
+      </c>
+      <c r="AD163" t="str">
+        <v/>
+      </c>
+      <c r="AE163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C164" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D164" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" t="str">
+        <v/>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+      <c r="U164" t="str">
+        <v/>
+      </c>
+      <c r="V164" t="str">
+        <v/>
+      </c>
+      <c r="W164" t="str">
+        <v/>
+      </c>
+      <c r="X164" t="str">
+        <v/>
+      </c>
+      <c r="Y164" t="str">
+        <v/>
+      </c>
+      <c r="Z164" t="str">
+        <v/>
+      </c>
+      <c r="AA164" t="str">
+        <v/>
+      </c>
+      <c r="AB164" t="str">
+        <v/>
+      </c>
+      <c r="AC164" t="str">
+        <v/>
+      </c>
+      <c r="AD164" t="str">
+        <v/>
+      </c>
+      <c r="AE164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C165" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D165" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+      <c r="R165" t="str">
+        <v/>
+      </c>
+      <c r="S165" t="str">
+        <v/>
+      </c>
+      <c r="T165" t="str">
+        <v/>
+      </c>
+      <c r="U165" t="str">
+        <v/>
+      </c>
+      <c r="V165" t="str">
+        <v/>
+      </c>
+      <c r="W165" t="str">
+        <v/>
+      </c>
+      <c r="X165" t="str">
+        <v/>
+      </c>
+      <c r="Y165" t="str">
+        <v/>
+      </c>
+      <c r="Z165" t="str">
+        <v/>
+      </c>
+      <c r="AA165" t="str">
+        <v/>
+      </c>
+      <c r="AB165" t="str">
+        <v/>
+      </c>
+      <c r="AC165" t="str">
+        <v/>
+      </c>
+      <c r="AD165" t="str">
+        <v/>
+      </c>
+      <c r="AE165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C166" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D166" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
+      <c r="R166" t="str">
+        <v/>
+      </c>
+      <c r="S166" t="str">
+        <v/>
+      </c>
+      <c r="T166" t="str">
+        <v/>
+      </c>
+      <c r="U166" t="str">
+        <v/>
+      </c>
+      <c r="V166" t="str">
+        <v/>
+      </c>
+      <c r="W166" t="str">
+        <v/>
+      </c>
+      <c r="X166" t="str">
+        <v/>
+      </c>
+      <c r="Y166" t="str">
+        <v/>
+      </c>
+      <c r="Z166" t="str">
+        <v/>
+      </c>
+      <c r="AA166" t="str">
+        <v/>
+      </c>
+      <c r="AB166" t="str">
+        <v/>
+      </c>
+      <c r="AC166" t="str">
+        <v/>
+      </c>
+      <c r="AD166" t="str">
+        <v/>
+      </c>
+      <c r="AE166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C167" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D167" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E167" t="str">
+        <v/>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
+      <c r="K167" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
+      <c r="R167" t="str">
+        <v/>
+      </c>
+      <c r="S167" t="str">
+        <v/>
+      </c>
+      <c r="T167" t="str">
+        <v/>
+      </c>
+      <c r="U167" t="str">
+        <v/>
+      </c>
+      <c r="V167" t="str">
+        <v/>
+      </c>
+      <c r="W167" t="str">
+        <v/>
+      </c>
+      <c r="X167" t="str">
+        <v/>
+      </c>
+      <c r="Y167" t="str">
+        <v/>
+      </c>
+      <c r="Z167" t="str">
+        <v/>
+      </c>
+      <c r="AA167" t="str">
+        <v/>
+      </c>
+      <c r="AB167" t="str">
+        <v/>
+      </c>
+      <c r="AC167" t="str">
+        <v/>
+      </c>
+      <c r="AD167" t="str">
+        <v/>
+      </c>
+      <c r="AE167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C168" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D168" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" t="str">
+        <v/>
+      </c>
+      <c r="S168" t="str">
+        <v/>
+      </c>
+      <c r="T168" t="str">
+        <v/>
+      </c>
+      <c r="U168" t="str">
+        <v/>
+      </c>
+      <c r="V168" t="str">
+        <v/>
+      </c>
+      <c r="W168" t="str">
+        <v/>
+      </c>
+      <c r="X168" t="str">
+        <v/>
+      </c>
+      <c r="Y168" t="str">
+        <v/>
+      </c>
+      <c r="Z168" t="str">
+        <v/>
+      </c>
+      <c r="AA168" t="str">
+        <v/>
+      </c>
+      <c r="AB168" t="str">
+        <v/>
+      </c>
+      <c r="AC168" t="str">
+        <v/>
+      </c>
+      <c r="AD168" t="str">
+        <v/>
+      </c>
+      <c r="AE168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C169" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D169" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
+      <c r="K169" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+      <c r="R169" t="str">
+        <v/>
+      </c>
+      <c r="S169" t="str">
+        <v/>
+      </c>
+      <c r="T169" t="str">
+        <v/>
+      </c>
+      <c r="U169" t="str">
+        <v/>
+      </c>
+      <c r="V169" t="str">
+        <v/>
+      </c>
+      <c r="W169" t="str">
+        <v/>
+      </c>
+      <c r="X169" t="str">
+        <v/>
+      </c>
+      <c r="Y169" t="str">
+        <v/>
+      </c>
+      <c r="Z169" t="str">
+        <v/>
+      </c>
+      <c r="AA169" t="str">
+        <v/>
+      </c>
+      <c r="AB169" t="str">
+        <v/>
+      </c>
+      <c r="AC169" t="str">
+        <v/>
+      </c>
+      <c r="AD169" t="str">
+        <v/>
+      </c>
+      <c r="AE169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C170" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D170" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E170" t="str">
+        <v/>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
+      <c r="K170" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+      <c r="R170" t="str">
+        <v/>
+      </c>
+      <c r="S170" t="str">
+        <v/>
+      </c>
+      <c r="T170" t="str">
+        <v/>
+      </c>
+      <c r="U170" t="str">
+        <v/>
+      </c>
+      <c r="V170" t="str">
+        <v/>
+      </c>
+      <c r="W170" t="str">
+        <v/>
+      </c>
+      <c r="X170" t="str">
+        <v/>
+      </c>
+      <c r="Y170" t="str">
+        <v/>
+      </c>
+      <c r="Z170" t="str">
+        <v/>
+      </c>
+      <c r="AA170" t="str">
+        <v/>
+      </c>
+      <c r="AB170" t="str">
+        <v/>
+      </c>
+      <c r="AC170" t="str">
+        <v/>
+      </c>
+      <c r="AD170" t="str">
+        <v/>
+      </c>
+      <c r="AE170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C171" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D171" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v/>
+      </c>
+      <c r="S171" t="str">
+        <v/>
+      </c>
+      <c r="T171" t="str">
+        <v/>
+      </c>
+      <c r="U171" t="str">
+        <v/>
+      </c>
+      <c r="V171" t="str">
+        <v/>
+      </c>
+      <c r="W171" t="str">
+        <v/>
+      </c>
+      <c r="X171" t="str">
+        <v/>
+      </c>
+      <c r="Y171" t="str">
+        <v/>
+      </c>
+      <c r="Z171" t="str">
+        <v/>
+      </c>
+      <c r="AA171" t="str">
+        <v/>
+      </c>
+      <c r="AB171" t="str">
+        <v/>
+      </c>
+      <c r="AC171" t="str">
+        <v/>
+      </c>
+      <c r="AD171" t="str">
+        <v/>
+      </c>
+      <c r="AE171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C172" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D172" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E172" t="str">
+        <v/>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
+      <c r="K172" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+      <c r="R172" t="str">
+        <v/>
+      </c>
+      <c r="S172" t="str">
+        <v/>
+      </c>
+      <c r="T172" t="str">
+        <v/>
+      </c>
+      <c r="U172" t="str">
+        <v/>
+      </c>
+      <c r="V172" t="str">
+        <v/>
+      </c>
+      <c r="W172" t="str">
+        <v/>
+      </c>
+      <c r="X172" t="str">
+        <v/>
+      </c>
+      <c r="Y172" t="str">
+        <v/>
+      </c>
+      <c r="Z172" t="str">
+        <v/>
+      </c>
+      <c r="AA172" t="str">
+        <v/>
+      </c>
+      <c r="AB172" t="str">
+        <v/>
+      </c>
+      <c r="AC172" t="str">
+        <v/>
+      </c>
+      <c r="AD172" t="str">
+        <v/>
+      </c>
+      <c r="AE172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="B173" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C173" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D173" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+      <c r="T173" t="str">
+        <v/>
+      </c>
+      <c r="U173" t="str">
+        <v/>
+      </c>
+      <c r="V173" t="str">
+        <v/>
+      </c>
+      <c r="W173" t="str">
+        <v/>
+      </c>
+      <c r="X173" t="str">
+        <v/>
+      </c>
+      <c r="Y173" t="str">
+        <v/>
+      </c>
+      <c r="Z173" t="str">
+        <v/>
+      </c>
+      <c r="AA173" t="str">
+        <v/>
+      </c>
+      <c r="AB173" t="str">
+        <v/>
+      </c>
+      <c r="AC173" t="str">
+        <v/>
+      </c>
+      <c r="AD173" t="str">
+        <v/>
+      </c>
+      <c r="AE173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="B174" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C174" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D174" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E174" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+      <c r="R174" t="str">
+        <v/>
+      </c>
+      <c r="S174" t="str">
+        <v/>
+      </c>
+      <c r="T174" t="str">
+        <v/>
+      </c>
+      <c r="U174" t="str">
+        <v/>
+      </c>
+      <c r="V174" t="str">
+        <v/>
+      </c>
+      <c r="W174" t="str">
+        <v/>
+      </c>
+      <c r="X174" t="str">
+        <v/>
+      </c>
+      <c r="Y174" t="str">
+        <v/>
+      </c>
+      <c r="Z174" t="str">
+        <v/>
+      </c>
+      <c r="AA174" t="str">
+        <v/>
+      </c>
+      <c r="AB174" t="str">
+        <v/>
+      </c>
+      <c r="AC174" t="str">
+        <v/>
+      </c>
+      <c r="AD174" t="str">
+        <v/>
+      </c>
+      <c r="AE174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="B175" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C175" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D175" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
+      <c r="K175" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+      <c r="R175" t="str">
+        <v/>
+      </c>
+      <c r="S175" t="str">
+        <v/>
+      </c>
+      <c r="T175" t="str">
+        <v/>
+      </c>
+      <c r="U175" t="str">
+        <v/>
+      </c>
+      <c r="V175" t="str">
+        <v/>
+      </c>
+      <c r="W175" t="str">
+        <v/>
+      </c>
+      <c r="X175" t="str">
+        <v/>
+      </c>
+      <c r="Y175" t="str">
+        <v/>
+      </c>
+      <c r="Z175" t="str">
+        <v/>
+      </c>
+      <c r="AA175" t="str">
+        <v/>
+      </c>
+      <c r="AB175" t="str">
+        <v/>
+      </c>
+      <c r="AC175" t="str">
+        <v/>
+      </c>
+      <c r="AD175" t="str">
+        <v/>
+      </c>
+      <c r="AE175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="B176" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C176" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D176" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" t="str">
+        <v/>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+      <c r="T176" t="str">
+        <v/>
+      </c>
+      <c r="U176" t="str">
+        <v/>
+      </c>
+      <c r="V176" t="str">
+        <v/>
+      </c>
+      <c r="W176" t="str">
+        <v/>
+      </c>
+      <c r="X176" t="str">
+        <v/>
+      </c>
+      <c r="Y176" t="str">
+        <v/>
+      </c>
+      <c r="Z176" t="str">
+        <v/>
+      </c>
+      <c r="AA176" t="str">
+        <v/>
+      </c>
+      <c r="AB176" t="str">
+        <v/>
+      </c>
+      <c r="AC176" t="str">
+        <v/>
+      </c>
+      <c r="AD176" t="str">
+        <v/>
+      </c>
+      <c r="AE176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="B177" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C177" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D177" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E177" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+      <c r="R177" t="str">
+        <v/>
+      </c>
+      <c r="S177" t="str">
+        <v/>
+      </c>
+      <c r="T177" t="str">
+        <v/>
+      </c>
+      <c r="U177" t="str">
+        <v/>
+      </c>
+      <c r="V177" t="str">
+        <v/>
+      </c>
+      <c r="W177" t="str">
+        <v/>
+      </c>
+      <c r="X177" t="str">
+        <v/>
+      </c>
+      <c r="Y177" t="str">
+        <v/>
+      </c>
+      <c r="Z177" t="str">
+        <v/>
+      </c>
+      <c r="AA177" t="str">
+        <v/>
+      </c>
+      <c r="AB177" t="str">
+        <v/>
+      </c>
+      <c r="AC177" t="str">
+        <v/>
+      </c>
+      <c r="AD177" t="str">
+        <v/>
+      </c>
+      <c r="AE177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="B178" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C178" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D178" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E178" t="str">
+        <v/>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" t="str">
+        <v/>
+      </c>
+      <c r="S178" t="str">
+        <v/>
+      </c>
+      <c r="T178" t="str">
+        <v/>
+      </c>
+      <c r="U178" t="str">
+        <v/>
+      </c>
+      <c r="V178" t="str">
+        <v/>
+      </c>
+      <c r="W178" t="str">
+        <v/>
+      </c>
+      <c r="X178" t="str">
+        <v/>
+      </c>
+      <c r="Y178" t="str">
+        <v/>
+      </c>
+      <c r="Z178" t="str">
+        <v/>
+      </c>
+      <c r="AA178" t="str">
+        <v/>
+      </c>
+      <c r="AB178" t="str">
+        <v/>
+      </c>
+      <c r="AC178" t="str">
+        <v/>
+      </c>
+      <c r="AD178" t="str">
+        <v/>
+      </c>
+      <c r="AE178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="B179" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C179" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D179" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E179" t="str">
+        <v/>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+      <c r="T179" t="str">
+        <v/>
+      </c>
+      <c r="U179" t="str">
+        <v/>
+      </c>
+      <c r="V179" t="str">
+        <v/>
+      </c>
+      <c r="W179" t="str">
+        <v/>
+      </c>
+      <c r="X179" t="str">
+        <v/>
+      </c>
+      <c r="Y179" t="str">
+        <v/>
+      </c>
+      <c r="Z179" t="str">
+        <v/>
+      </c>
+      <c r="AA179" t="str">
+        <v/>
+      </c>
+      <c r="AB179" t="str">
+        <v/>
+      </c>
+      <c r="AC179" t="str">
+        <v/>
+      </c>
+      <c r="AD179" t="str">
+        <v/>
+      </c>
+      <c r="AE179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="B180" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C180" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D180" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E180" t="str">
+        <v/>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
+      <c r="K180" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" t="str">
+        <v/>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+      <c r="T180" t="str">
+        <v/>
+      </c>
+      <c r="U180" t="str">
+        <v/>
+      </c>
+      <c r="V180" t="str">
+        <v/>
+      </c>
+      <c r="W180" t="str">
+        <v/>
+      </c>
+      <c r="X180" t="str">
+        <v/>
+      </c>
+      <c r="Y180" t="str">
+        <v/>
+      </c>
+      <c r="Z180" t="str">
+        <v/>
+      </c>
+      <c r="AA180" t="str">
+        <v/>
+      </c>
+      <c r="AB180" t="str">
+        <v/>
+      </c>
+      <c r="AC180" t="str">
+        <v/>
+      </c>
+      <c r="AD180" t="str">
+        <v/>
+      </c>
+      <c r="AE180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C181" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D181" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E181" t="str">
+        <v/>
+      </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+      <c r="T181" t="str">
+        <v/>
+      </c>
+      <c r="U181" t="str">
+        <v/>
+      </c>
+      <c r="V181" t="str">
+        <v/>
+      </c>
+      <c r="W181" t="str">
+        <v/>
+      </c>
+      <c r="X181" t="str">
+        <v/>
+      </c>
+      <c r="Y181" t="str">
+        <v/>
+      </c>
+      <c r="Z181" t="str">
+        <v/>
+      </c>
+      <c r="AA181" t="str">
+        <v/>
+      </c>
+      <c r="AB181" t="str">
+        <v/>
+      </c>
+      <c r="AC181" t="str">
+        <v/>
+      </c>
+      <c r="AD181" t="str">
+        <v/>
+      </c>
+      <c r="AE181" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE181"/>
+  <dimension ref="A1:AI211"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
       <c r="B2" t="str">
         <v>16 | ינואר</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -466,21 +466,21 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר</v>
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
       <c r="B3" t="str">
         <v>16 | ינואר</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -501,21 +501,21 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר</v>
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מידד טסה - עוף מוזר קאבר</v>
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
       <c r="B4" t="str">
         <v>16 | ינואר</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -536,21 +536,21 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>מידד טסה - עוף מוזר קאבר</v>
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
       <c r="B5" t="str">
         <v>16 | ינואר</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -571,21 +571,21 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
       <c r="B6" t="str">
         <v>16 | ינואר</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -606,21 +606,21 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל חן - אל תלכי קאבר</v>
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
       <c r="B7" t="str">
         <v>16 | ינואר</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -641,21 +641,21 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>דניאל חן - אל תלכי קאבר</v>
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>איימי - אהבה רעילה קאבר</v>
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
       <c r="B8" t="str">
         <v>16 | ינואר</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -676,21 +676,21 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>איימי - אהבה רעילה קאבר</v>
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
       <c r="B9" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -711,21 +711,21 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
       <c r="B10" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -746,21 +746,21 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>שני פונה - דרך חדשה קאבר</v>
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
       </c>
       <c r="B11" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -781,21 +781,21 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>פארידה - Darixdim Cover</v>
+        <v>פארידה - Darixdim Cover להורדה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
       <c r="B12" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -816,21 +816,21 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+        <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
       <c r="B13" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -851,21 +851,21 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+        <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
       <c r="B14" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -886,21 +886,21 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+        <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
       <c r="B15" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -921,21 +921,21 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>לירוי בר זוהר - אבא קאבר</v>
+        <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
       <c r="B16" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -956,21 +956,21 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+        <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
       <c r="B17" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -991,21 +991,21 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+        <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
       <c r="B18" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1026,21 +1026,21 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+        <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
       <c r="B19" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1061,21 +1061,21 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>ברטין - שביל האושר קאבר</v>
+        <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
       </c>
       <c r="B20" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1096,21 +1096,21 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+        <v>אריאל קנדאבי - גולה סנגם קאבר להורדה</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
       </c>
       <c r="B21" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1131,21 +1131,21 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>אלירן עטר - את קאבר</v>
+        <v>אלירן עטר - את קאבר להורדה</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
       </c>
       <c r="B22" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1166,21 +1166,21 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>אליקיר - מזל קאבר</v>
+        <v>אליקיר - מזל קאבר להורדה</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
       </c>
       <c r="B23" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1201,21 +1201,21 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+        <v>אליאור נונה - תספר לי איך למעלה קאבר להורדה</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
       </c>
       <c r="B24" t="str">
         <v>13 | ינואר</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1236,21 +1236,21 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר להורדה</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
       </c>
       <c r="B25" t="str">
         <v>08 | ינואר</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1271,21 +1271,21 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>דניאל פרטוש - רוח ים קאבר</v>
+        <v>דניאל פרטוש - רוח ים קאבר להורדה</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
       </c>
       <c r="B26" t="str">
         <v>08 | ינואר</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1306,21 +1306,21 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+        <v>אביחי טהיא - מהפכה של שמחה קאבר להורדה</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
       </c>
       <c r="B27" t="str">
         <v>08 | ינואר</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1341,21 +1341,21 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>תאי חבאני - חלום מתוק קאבר</v>
+        <v>תאי חבאני - חלום מתוק קאבר להורדה</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
       </c>
       <c r="B28" t="str">
         <v>08 | ינואר</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1376,21 +1376,21 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>רם נעים - מלכת היופי שלי קאבר</v>
+        <v>רם נעים - מלכת היופי שלי קאבר להורדה</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
       </c>
       <c r="B29" t="str">
         <v>08 | ינואר</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1411,21 +1411,21 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+        <v>רביד בדיאן - רולקס וקסקט קאבר להורדה</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
       </c>
       <c r="B30" t="str">
         <v>08 | ינואר</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1446,21 +1446,21 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>עוז גנון - שיר למעלות קאבר</v>
+        <v>עוז גנון - שיר למעלות קאבר להורדה</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
       </c>
       <c r="B31" t="str">
         <v>08 | ינואר</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=f849545385436f6c0eb6b6d8a2c81e05</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-16</v>
+        <v>2026-01-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1481,7 +1481,7 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>משה סונה - הינך יפה קאבר</v>
+        <v>משה סונה - הינך יפה קאבר להורדה</v>
       </c>
     </row>
     <row r="32">
@@ -1492,7 +1492,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C32" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-16</v>
@@ -1539,7 +1539,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C33" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-16</v>
@@ -1586,7 +1586,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C34" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-16</v>
@@ -1633,7 +1633,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C35" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-16</v>
@@ -1680,7 +1680,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C36" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-16</v>
@@ -1727,7 +1727,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C37" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-16</v>
@@ -1774,7 +1774,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C38" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-16</v>
@@ -1821,7 +1821,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C39" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-16</v>
@@ -1868,7 +1868,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C40" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-16</v>
@@ -1915,7 +1915,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C41" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-16</v>
@@ -1962,7 +1962,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C42" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-16</v>
@@ -2009,7 +2009,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C43" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-16</v>
@@ -2056,7 +2056,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C44" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-16</v>
@@ -2103,7 +2103,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C45" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-16</v>
@@ -2150,7 +2150,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C46" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-16</v>
@@ -2197,7 +2197,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C47" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-16</v>
@@ -2244,7 +2244,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C48" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-16</v>
@@ -2291,7 +2291,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C49" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-16</v>
@@ -2338,7 +2338,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C50" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-16</v>
@@ -2385,7 +2385,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C51" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-16</v>
@@ -2432,7 +2432,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C52" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-16</v>
@@ -2479,7 +2479,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C53" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-16</v>
@@ -2526,7 +2526,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C54" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-16</v>
@@ -2573,7 +2573,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C55" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-16</v>
@@ -2620,7 +2620,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C56" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-16</v>
@@ -2667,7 +2667,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C57" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-16</v>
@@ -2714,7 +2714,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C58" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-16</v>
@@ -2761,7 +2761,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C59" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-16</v>
@@ -2808,7 +2808,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C60" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-16</v>
@@ -2855,7 +2855,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C61" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=d7e98add09ea81d836f919544317df1e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ea7f2a24774a132d400fa9491406d8b1</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-16</v>
@@ -2902,7 +2902,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C62" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-16</v>
@@ -2961,7 +2961,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C63" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-16</v>
@@ -3020,7 +3020,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C64" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-16</v>
@@ -3079,7 +3079,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C65" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-16</v>
@@ -3138,7 +3138,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C66" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-16</v>
@@ -3197,7 +3197,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C67" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-16</v>
@@ -3256,7 +3256,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C68" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-16</v>
@@ -3315,7 +3315,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C69" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-16</v>
@@ -3374,7 +3374,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C70" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-16</v>
@@ -3433,7 +3433,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C71" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-16</v>
@@ -3492,7 +3492,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C72" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-16</v>
@@ -3551,7 +3551,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C73" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-16</v>
@@ -3610,7 +3610,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C74" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-16</v>
@@ -3669,7 +3669,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C75" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-16</v>
@@ -3728,7 +3728,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C76" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-16</v>
@@ -3787,7 +3787,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C77" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-16</v>
@@ -3846,7 +3846,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C78" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-16</v>
@@ -3905,7 +3905,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C79" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-16</v>
@@ -3964,7 +3964,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C80" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-16</v>
@@ -4023,7 +4023,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C81" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-16</v>
@@ -4082,7 +4082,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C82" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-16</v>
@@ -4141,7 +4141,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C83" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-16</v>
@@ -4200,7 +4200,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C84" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-16</v>
@@ -4259,7 +4259,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C85" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-16</v>
@@ -4318,7 +4318,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C86" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-16</v>
@@ -4377,7 +4377,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C87" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-16</v>
@@ -4436,7 +4436,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C88" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-16</v>
@@ -4495,7 +4495,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C89" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-16</v>
@@ -4554,7 +4554,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C90" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-16</v>
@@ -4613,7 +4613,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C91" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ae1713637a044856914f8759cd9b9479</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=d7e98add09ea81d836f919544317df1e</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-16</v>
@@ -4672,7 +4672,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C92" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-16</v>
@@ -4743,7 +4743,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C93" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-16</v>
@@ -4814,7 +4814,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C94" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-16</v>
@@ -4885,7 +4885,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C95" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-16</v>
@@ -4956,7 +4956,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C96" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-16</v>
@@ -5027,7 +5027,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C97" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-16</v>
@@ -5098,7 +5098,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C98" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-16</v>
@@ -5169,7 +5169,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C99" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-16</v>
@@ -5240,7 +5240,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C100" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-16</v>
@@ -5311,7 +5311,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C101" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-16</v>
@@ -5382,7 +5382,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C102" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-16</v>
@@ -5453,7 +5453,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C103" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-16</v>
@@ -5524,7 +5524,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C104" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-16</v>
@@ -5595,7 +5595,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C105" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-16</v>
@@ -5666,7 +5666,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C106" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-16</v>
@@ -5737,7 +5737,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C107" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-16</v>
@@ -5808,7 +5808,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C108" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-16</v>
@@ -5879,7 +5879,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C109" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-16</v>
@@ -5950,7 +5950,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C110" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-16</v>
@@ -6021,7 +6021,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C111" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-16</v>
@@ -6092,7 +6092,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C112" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-16</v>
@@ -6163,7 +6163,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C113" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-16</v>
@@ -6234,7 +6234,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C114" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-16</v>
@@ -6305,7 +6305,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C115" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-16</v>
@@ -6376,7 +6376,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C116" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-16</v>
@@ -6447,7 +6447,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C117" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-16</v>
@@ -6518,7 +6518,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C118" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-16</v>
@@ -6589,7 +6589,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C119" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-16</v>
@@ -6660,7 +6660,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C120" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-16</v>
@@ -6731,7 +6731,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C121" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=ae1713637a044856914f8759cd9b9479</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-16</v>
@@ -6802,7 +6802,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C122" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-16</v>
@@ -6885,7 +6885,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C123" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-16</v>
@@ -6968,7 +6968,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C124" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-16</v>
@@ -7051,7 +7051,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C125" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-16</v>
@@ -7134,7 +7134,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C126" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-16</v>
@@ -7217,7 +7217,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C127" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-16</v>
@@ -7300,7 +7300,7 @@
         <v>16 | ינואר</v>
       </c>
       <c r="C128" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-16</v>
@@ -7383,7 +7383,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C129" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-16</v>
@@ -7466,7 +7466,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C130" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-16</v>
@@ -7549,7 +7549,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C131" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-16</v>
@@ -7632,7 +7632,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C132" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-16</v>
@@ -7715,7 +7715,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C133" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-16</v>
@@ -7798,7 +7798,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C134" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-16</v>
@@ -7881,7 +7881,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C135" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-16</v>
@@ -7964,7 +7964,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C136" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-16</v>
@@ -8047,7 +8047,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C137" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-16</v>
@@ -8130,7 +8130,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C138" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-16</v>
@@ -8213,7 +8213,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C139" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-16</v>
@@ -8296,7 +8296,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C140" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-16</v>
@@ -8379,7 +8379,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C141" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-16</v>
@@ -8462,7 +8462,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C142" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-16</v>
@@ -8545,7 +8545,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C143" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-16</v>
@@ -8628,7 +8628,7 @@
         <v>13 | ינואר</v>
       </c>
       <c r="C144" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-16</v>
@@ -8711,7 +8711,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C145" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-16</v>
@@ -8794,7 +8794,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C146" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-16</v>
@@ -8877,7 +8877,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C147" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-16</v>
@@ -8960,7 +8960,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C148" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-16</v>
@@ -9043,7 +9043,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C149" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-16</v>
@@ -9126,7 +9126,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C150" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-16</v>
@@ -9209,7 +9209,7 @@
         <v>08 | ינואר</v>
       </c>
       <c r="C151" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=b1be9c27797c337391ca6ac657f7214b</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-16</v>
@@ -9289,10 +9289,10 @@
         <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B152" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C152" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-16</v>
@@ -9384,10 +9384,10 @@
         <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B153" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C153" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-16</v>
@@ -9479,10 +9479,10 @@
         <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B154" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C154" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-16</v>
@@ -9574,10 +9574,10 @@
         <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B155" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C155" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-16</v>
@@ -9669,10 +9669,10 @@
         <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B156" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C156" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-16</v>
@@ -9764,10 +9764,10 @@
         <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B157" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C157" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-16</v>
@@ -9859,10 +9859,10 @@
         <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B158" t="str">
-        <v>2026-01-16</v>
+        <v>16 | ינואר</v>
       </c>
       <c r="C158" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-16</v>
@@ -9954,10 +9954,10 @@
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B159" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C159" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-16</v>
@@ -10049,10 +10049,10 @@
         <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B160" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C160" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-16</v>
@@ -10144,10 +10144,10 @@
         <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B161" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C161" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-16</v>
@@ -10239,10 +10239,10 @@
         <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
       </c>
       <c r="B162" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C162" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-16</v>
@@ -10334,10 +10334,10 @@
         <v>נתנאל נגר - כל יום שעובר קאבר</v>
       </c>
       <c r="B163" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C163" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-16</v>
@@ -10429,10 +10429,10 @@
         <v>נאור מתתיהו - תמיד שמח קאבר</v>
       </c>
       <c r="B164" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C164" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-16</v>
@@ -10524,10 +10524,10 @@
         <v>לירוי בר זוהר - אבא קאבר</v>
       </c>
       <c r="B165" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C165" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-16</v>
@@ -10619,10 +10619,10 @@
         <v>ליאן אברהם - כשאת עצובה קאבר</v>
       </c>
       <c r="B166" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C166" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-16</v>
@@ -10714,10 +10714,10 @@
         <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
       </c>
       <c r="B167" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C167" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-16</v>
@@ -10809,10 +10809,10 @@
         <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B168" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C168" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-16</v>
@@ -10904,10 +10904,10 @@
         <v>ברטין - שביל האושר קאבר</v>
       </c>
       <c r="B169" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C169" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-16</v>
@@ -10999,10 +10999,10 @@
         <v>אריאל קנדאבי - גולה סנגם קאבר</v>
       </c>
       <c r="B170" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C170" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-16</v>
@@ -11094,10 +11094,10 @@
         <v>אלירן עטר - את קאבר</v>
       </c>
       <c r="B171" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C171" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-16</v>
@@ -11189,10 +11189,10 @@
         <v>אליקיר - מזל קאבר</v>
       </c>
       <c r="B172" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C172" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-16</v>
@@ -11284,10 +11284,10 @@
         <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
       </c>
       <c r="B173" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C173" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-16</v>
@@ -11379,10 +11379,10 @@
         <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
       </c>
       <c r="B174" t="str">
-        <v>2026-01-13</v>
+        <v>13 | ינואר</v>
       </c>
       <c r="C174" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-16</v>
@@ -11474,10 +11474,10 @@
         <v>דניאל פרטוש - רוח ים קאבר</v>
       </c>
       <c r="B175" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C175" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-16</v>
@@ -11569,10 +11569,10 @@
         <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
       </c>
       <c r="B176" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C176" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-16</v>
@@ -11664,10 +11664,10 @@
         <v>תאי חבאני - חלום מתוק קאבר</v>
       </c>
       <c r="B177" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C177" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-16</v>
@@ -11759,10 +11759,10 @@
         <v>רם נעים - מלכת היופי שלי קאבר</v>
       </c>
       <c r="B178" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C178" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-16</v>
@@ -11854,10 +11854,10 @@
         <v>רביד בדיאן - רולקס וקסקט קאבר</v>
       </c>
       <c r="B179" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C179" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-16</v>
@@ -11949,10 +11949,10 @@
         <v>עוז גנון - שיר למעלות קאבר</v>
       </c>
       <c r="B180" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C180" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-16</v>
@@ -12044,10 +12044,10 @@
         <v>משה סונה - הינך יפה קאבר</v>
       </c>
       <c r="B181" t="str">
-        <v>2026-01-08</v>
+        <v>08 | ינואר</v>
       </c>
       <c r="C181" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=9fad7b9a61e7c0c286d9a12adea5e812</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-16</v>
@@ -12134,9 +12134,3219 @@
         <v/>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="B182" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C182" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D182" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E182" t="str">
+        <v/>
+      </c>
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
+      <c r="K182" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
+      </c>
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
+        <v/>
+      </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+      <c r="R182" t="str">
+        <v/>
+      </c>
+      <c r="S182" t="str">
+        <v/>
+      </c>
+      <c r="T182" t="str">
+        <v/>
+      </c>
+      <c r="U182" t="str">
+        <v/>
+      </c>
+      <c r="V182" t="str">
+        <v/>
+      </c>
+      <c r="W182" t="str">
+        <v/>
+      </c>
+      <c r="X182" t="str">
+        <v/>
+      </c>
+      <c r="Y182" t="str">
+        <v/>
+      </c>
+      <c r="Z182" t="str">
+        <v/>
+      </c>
+      <c r="AA182" t="str">
+        <v/>
+      </c>
+      <c r="AB182" t="str">
+        <v/>
+      </c>
+      <c r="AC182" t="str">
+        <v/>
+      </c>
+      <c r="AD182" t="str">
+        <v/>
+      </c>
+      <c r="AE182" t="str">
+        <v/>
+      </c>
+      <c r="AF182" t="str">
+        <v/>
+      </c>
+      <c r="AG182" t="str">
+        <v/>
+      </c>
+      <c r="AH182" t="str">
+        <v/>
+      </c>
+      <c r="AI182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C183" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D183" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E183" t="str">
+        <v/>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v/>
+      </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+      <c r="R183" t="str">
+        <v/>
+      </c>
+      <c r="S183" t="str">
+        <v/>
+      </c>
+      <c r="T183" t="str">
+        <v/>
+      </c>
+      <c r="U183" t="str">
+        <v/>
+      </c>
+      <c r="V183" t="str">
+        <v/>
+      </c>
+      <c r="W183" t="str">
+        <v/>
+      </c>
+      <c r="X183" t="str">
+        <v/>
+      </c>
+      <c r="Y183" t="str">
+        <v/>
+      </c>
+      <c r="Z183" t="str">
+        <v/>
+      </c>
+      <c r="AA183" t="str">
+        <v/>
+      </c>
+      <c r="AB183" t="str">
+        <v/>
+      </c>
+      <c r="AC183" t="str">
+        <v/>
+      </c>
+      <c r="AD183" t="str">
+        <v/>
+      </c>
+      <c r="AE183" t="str">
+        <v/>
+      </c>
+      <c r="AF183" t="str">
+        <v/>
+      </c>
+      <c r="AG183" t="str">
+        <v/>
+      </c>
+      <c r="AH183" t="str">
+        <v/>
+      </c>
+      <c r="AI183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="B184" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C184" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D184" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E184" t="str">
+        <v/>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v>מידד טסה - עוף מוזר קאבר</v>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+      <c r="T184" t="str">
+        <v/>
+      </c>
+      <c r="U184" t="str">
+        <v/>
+      </c>
+      <c r="V184" t="str">
+        <v/>
+      </c>
+      <c r="W184" t="str">
+        <v/>
+      </c>
+      <c r="X184" t="str">
+        <v/>
+      </c>
+      <c r="Y184" t="str">
+        <v/>
+      </c>
+      <c r="Z184" t="str">
+        <v/>
+      </c>
+      <c r="AA184" t="str">
+        <v/>
+      </c>
+      <c r="AB184" t="str">
+        <v/>
+      </c>
+      <c r="AC184" t="str">
+        <v/>
+      </c>
+      <c r="AD184" t="str">
+        <v/>
+      </c>
+      <c r="AE184" t="str">
+        <v/>
+      </c>
+      <c r="AF184" t="str">
+        <v/>
+      </c>
+      <c r="AG184" t="str">
+        <v/>
+      </c>
+      <c r="AH184" t="str">
+        <v/>
+      </c>
+      <c r="AI184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="B185" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C185" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D185" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E185" t="str">
+        <v/>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
+        <v/>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+      <c r="T185" t="str">
+        <v/>
+      </c>
+      <c r="U185" t="str">
+        <v/>
+      </c>
+      <c r="V185" t="str">
+        <v/>
+      </c>
+      <c r="W185" t="str">
+        <v/>
+      </c>
+      <c r="X185" t="str">
+        <v/>
+      </c>
+      <c r="Y185" t="str">
+        <v/>
+      </c>
+      <c r="Z185" t="str">
+        <v/>
+      </c>
+      <c r="AA185" t="str">
+        <v/>
+      </c>
+      <c r="AB185" t="str">
+        <v/>
+      </c>
+      <c r="AC185" t="str">
+        <v/>
+      </c>
+      <c r="AD185" t="str">
+        <v/>
+      </c>
+      <c r="AE185" t="str">
+        <v/>
+      </c>
+      <c r="AF185" t="str">
+        <v/>
+      </c>
+      <c r="AG185" t="str">
+        <v/>
+      </c>
+      <c r="AH185" t="str">
+        <v/>
+      </c>
+      <c r="AI185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="B186" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C186" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D186" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E186" t="str">
+        <v/>
+      </c>
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+      <c r="T186" t="str">
+        <v/>
+      </c>
+      <c r="U186" t="str">
+        <v/>
+      </c>
+      <c r="V186" t="str">
+        <v/>
+      </c>
+      <c r="W186" t="str">
+        <v/>
+      </c>
+      <c r="X186" t="str">
+        <v/>
+      </c>
+      <c r="Y186" t="str">
+        <v/>
+      </c>
+      <c r="Z186" t="str">
+        <v/>
+      </c>
+      <c r="AA186" t="str">
+        <v/>
+      </c>
+      <c r="AB186" t="str">
+        <v/>
+      </c>
+      <c r="AC186" t="str">
+        <v/>
+      </c>
+      <c r="AD186" t="str">
+        <v/>
+      </c>
+      <c r="AE186" t="str">
+        <v/>
+      </c>
+      <c r="AF186" t="str">
+        <v/>
+      </c>
+      <c r="AG186" t="str">
+        <v/>
+      </c>
+      <c r="AH186" t="str">
+        <v/>
+      </c>
+      <c r="AI186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="B187" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C187" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D187" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E187" t="str">
+        <v/>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
+        <v>דניאל חן - אל תלכי קאבר</v>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+      <c r="R187" t="str">
+        <v/>
+      </c>
+      <c r="S187" t="str">
+        <v/>
+      </c>
+      <c r="T187" t="str">
+        <v/>
+      </c>
+      <c r="U187" t="str">
+        <v/>
+      </c>
+      <c r="V187" t="str">
+        <v/>
+      </c>
+      <c r="W187" t="str">
+        <v/>
+      </c>
+      <c r="X187" t="str">
+        <v/>
+      </c>
+      <c r="Y187" t="str">
+        <v/>
+      </c>
+      <c r="Z187" t="str">
+        <v/>
+      </c>
+      <c r="AA187" t="str">
+        <v/>
+      </c>
+      <c r="AB187" t="str">
+        <v/>
+      </c>
+      <c r="AC187" t="str">
+        <v/>
+      </c>
+      <c r="AD187" t="str">
+        <v/>
+      </c>
+      <c r="AE187" t="str">
+        <v/>
+      </c>
+      <c r="AF187" t="str">
+        <v/>
+      </c>
+      <c r="AG187" t="str">
+        <v/>
+      </c>
+      <c r="AH187" t="str">
+        <v/>
+      </c>
+      <c r="AI187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="B188" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C188" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D188" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E188" t="str">
+        <v/>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
+      <c r="K188" t="str">
+        <v>איימי - אהבה רעילה קאבר</v>
+      </c>
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
+        <v/>
+      </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+      <c r="R188" t="str">
+        <v/>
+      </c>
+      <c r="S188" t="str">
+        <v/>
+      </c>
+      <c r="T188" t="str">
+        <v/>
+      </c>
+      <c r="U188" t="str">
+        <v/>
+      </c>
+      <c r="V188" t="str">
+        <v/>
+      </c>
+      <c r="W188" t="str">
+        <v/>
+      </c>
+      <c r="X188" t="str">
+        <v/>
+      </c>
+      <c r="Y188" t="str">
+        <v/>
+      </c>
+      <c r="Z188" t="str">
+        <v/>
+      </c>
+      <c r="AA188" t="str">
+        <v/>
+      </c>
+      <c r="AB188" t="str">
+        <v/>
+      </c>
+      <c r="AC188" t="str">
+        <v/>
+      </c>
+      <c r="AD188" t="str">
+        <v/>
+      </c>
+      <c r="AE188" t="str">
+        <v/>
+      </c>
+      <c r="AF188" t="str">
+        <v/>
+      </c>
+      <c r="AG188" t="str">
+        <v/>
+      </c>
+      <c r="AH188" t="str">
+        <v/>
+      </c>
+      <c r="AI188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="B189" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C189" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D189" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
+      <c r="K189" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
+      </c>
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
+      <c r="R189" t="str">
+        <v/>
+      </c>
+      <c r="S189" t="str">
+        <v/>
+      </c>
+      <c r="T189" t="str">
+        <v/>
+      </c>
+      <c r="U189" t="str">
+        <v/>
+      </c>
+      <c r="V189" t="str">
+        <v/>
+      </c>
+      <c r="W189" t="str">
+        <v/>
+      </c>
+      <c r="X189" t="str">
+        <v/>
+      </c>
+      <c r="Y189" t="str">
+        <v/>
+      </c>
+      <c r="Z189" t="str">
+        <v/>
+      </c>
+      <c r="AA189" t="str">
+        <v/>
+      </c>
+      <c r="AB189" t="str">
+        <v/>
+      </c>
+      <c r="AC189" t="str">
+        <v/>
+      </c>
+      <c r="AD189" t="str">
+        <v/>
+      </c>
+      <c r="AE189" t="str">
+        <v/>
+      </c>
+      <c r="AF189" t="str">
+        <v/>
+      </c>
+      <c r="AG189" t="str">
+        <v/>
+      </c>
+      <c r="AH189" t="str">
+        <v/>
+      </c>
+      <c r="AI189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="B190" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C190" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D190" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
+        <v>שני פונה - דרך חדשה קאבר</v>
+      </c>
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+      <c r="R190" t="str">
+        <v/>
+      </c>
+      <c r="S190" t="str">
+        <v/>
+      </c>
+      <c r="T190" t="str">
+        <v/>
+      </c>
+      <c r="U190" t="str">
+        <v/>
+      </c>
+      <c r="V190" t="str">
+        <v/>
+      </c>
+      <c r="W190" t="str">
+        <v/>
+      </c>
+      <c r="X190" t="str">
+        <v/>
+      </c>
+      <c r="Y190" t="str">
+        <v/>
+      </c>
+      <c r="Z190" t="str">
+        <v/>
+      </c>
+      <c r="AA190" t="str">
+        <v/>
+      </c>
+      <c r="AB190" t="str">
+        <v/>
+      </c>
+      <c r="AC190" t="str">
+        <v/>
+      </c>
+      <c r="AD190" t="str">
+        <v/>
+      </c>
+      <c r="AE190" t="str">
+        <v/>
+      </c>
+      <c r="AF190" t="str">
+        <v/>
+      </c>
+      <c r="AG190" t="str">
+        <v/>
+      </c>
+      <c r="AH190" t="str">
+        <v/>
+      </c>
+      <c r="AI190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="B191" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C191" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D191" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
+      <c r="K191" t="str">
+        <v>פארידה - Darixdim Cover</v>
+      </c>
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+      <c r="R191" t="str">
+        <v/>
+      </c>
+      <c r="S191" t="str">
+        <v/>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v/>
+      </c>
+      <c r="V191" t="str">
+        <v/>
+      </c>
+      <c r="W191" t="str">
+        <v/>
+      </c>
+      <c r="X191" t="str">
+        <v/>
+      </c>
+      <c r="Y191" t="str">
+        <v/>
+      </c>
+      <c r="Z191" t="str">
+        <v/>
+      </c>
+      <c r="AA191" t="str">
+        <v/>
+      </c>
+      <c r="AB191" t="str">
+        <v/>
+      </c>
+      <c r="AC191" t="str">
+        <v/>
+      </c>
+      <c r="AD191" t="str">
+        <v/>
+      </c>
+      <c r="AE191" t="str">
+        <v/>
+      </c>
+      <c r="AF191" t="str">
+        <v/>
+      </c>
+      <c r="AG191" t="str">
+        <v/>
+      </c>
+      <c r="AH191" t="str">
+        <v/>
+      </c>
+      <c r="AI191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="B192" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C192" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D192" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E192" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v>עומרי פרחן - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
+        <v/>
+      </c>
+      <c r="T192" t="str">
+        <v/>
+      </c>
+      <c r="U192" t="str">
+        <v/>
+      </c>
+      <c r="V192" t="str">
+        <v/>
+      </c>
+      <c r="W192" t="str">
+        <v/>
+      </c>
+      <c r="X192" t="str">
+        <v/>
+      </c>
+      <c r="Y192" t="str">
+        <v/>
+      </c>
+      <c r="Z192" t="str">
+        <v/>
+      </c>
+      <c r="AA192" t="str">
+        <v/>
+      </c>
+      <c r="AB192" t="str">
+        <v/>
+      </c>
+      <c r="AC192" t="str">
+        <v/>
+      </c>
+      <c r="AD192" t="str">
+        <v/>
+      </c>
+      <c r="AE192" t="str">
+        <v/>
+      </c>
+      <c r="AF192" t="str">
+        <v/>
+      </c>
+      <c r="AG192" t="str">
+        <v/>
+      </c>
+      <c r="AH192" t="str">
+        <v/>
+      </c>
+      <c r="AI192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="B193" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C193" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v/>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v>נתנאל נגר - כל יום שעובר קאבר</v>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+      <c r="R193" t="str">
+        <v/>
+      </c>
+      <c r="S193" t="str">
+        <v/>
+      </c>
+      <c r="T193" t="str">
+        <v/>
+      </c>
+      <c r="U193" t="str">
+        <v/>
+      </c>
+      <c r="V193" t="str">
+        <v/>
+      </c>
+      <c r="W193" t="str">
+        <v/>
+      </c>
+      <c r="X193" t="str">
+        <v/>
+      </c>
+      <c r="Y193" t="str">
+        <v/>
+      </c>
+      <c r="Z193" t="str">
+        <v/>
+      </c>
+      <c r="AA193" t="str">
+        <v/>
+      </c>
+      <c r="AB193" t="str">
+        <v/>
+      </c>
+      <c r="AC193" t="str">
+        <v/>
+      </c>
+      <c r="AD193" t="str">
+        <v/>
+      </c>
+      <c r="AE193" t="str">
+        <v/>
+      </c>
+      <c r="AF193" t="str">
+        <v/>
+      </c>
+      <c r="AG193" t="str">
+        <v/>
+      </c>
+      <c r="AH193" t="str">
+        <v/>
+      </c>
+      <c r="AI193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="B194" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C194" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v>נאור מתתיהו - תמיד שמח קאבר</v>
+      </c>
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
+        <v/>
+      </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
+      <c r="R194" t="str">
+        <v/>
+      </c>
+      <c r="S194" t="str">
+        <v/>
+      </c>
+      <c r="T194" t="str">
+        <v/>
+      </c>
+      <c r="U194" t="str">
+        <v/>
+      </c>
+      <c r="V194" t="str">
+        <v/>
+      </c>
+      <c r="W194" t="str">
+        <v/>
+      </c>
+      <c r="X194" t="str">
+        <v/>
+      </c>
+      <c r="Y194" t="str">
+        <v/>
+      </c>
+      <c r="Z194" t="str">
+        <v/>
+      </c>
+      <c r="AA194" t="str">
+        <v/>
+      </c>
+      <c r="AB194" t="str">
+        <v/>
+      </c>
+      <c r="AC194" t="str">
+        <v/>
+      </c>
+      <c r="AD194" t="str">
+        <v/>
+      </c>
+      <c r="AE194" t="str">
+        <v/>
+      </c>
+      <c r="AF194" t="str">
+        <v/>
+      </c>
+      <c r="AG194" t="str">
+        <v/>
+      </c>
+      <c r="AH194" t="str">
+        <v/>
+      </c>
+      <c r="AI194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="B195" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C195" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v>לירוי בר זוהר - אבא קאבר</v>
+      </c>
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
+        <v/>
+      </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
+      <c r="R195" t="str">
+        <v/>
+      </c>
+      <c r="S195" t="str">
+        <v/>
+      </c>
+      <c r="T195" t="str">
+        <v/>
+      </c>
+      <c r="U195" t="str">
+        <v/>
+      </c>
+      <c r="V195" t="str">
+        <v/>
+      </c>
+      <c r="W195" t="str">
+        <v/>
+      </c>
+      <c r="X195" t="str">
+        <v/>
+      </c>
+      <c r="Y195" t="str">
+        <v/>
+      </c>
+      <c r="Z195" t="str">
+        <v/>
+      </c>
+      <c r="AA195" t="str">
+        <v/>
+      </c>
+      <c r="AB195" t="str">
+        <v/>
+      </c>
+      <c r="AC195" t="str">
+        <v/>
+      </c>
+      <c r="AD195" t="str">
+        <v/>
+      </c>
+      <c r="AE195" t="str">
+        <v/>
+      </c>
+      <c r="AF195" t="str">
+        <v/>
+      </c>
+      <c r="AG195" t="str">
+        <v/>
+      </c>
+      <c r="AH195" t="str">
+        <v/>
+      </c>
+      <c r="AI195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="B196" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C196" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
+      <c r="K196" t="str">
+        <v>ליאן אברהם - כשאת עצובה קאבר</v>
+      </c>
+      <c r="L196" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str">
+        <v/>
+      </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
+      <c r="R196" t="str">
+        <v/>
+      </c>
+      <c r="S196" t="str">
+        <v/>
+      </c>
+      <c r="T196" t="str">
+        <v/>
+      </c>
+      <c r="U196" t="str">
+        <v/>
+      </c>
+      <c r="V196" t="str">
+        <v/>
+      </c>
+      <c r="W196" t="str">
+        <v/>
+      </c>
+      <c r="X196" t="str">
+        <v/>
+      </c>
+      <c r="Y196" t="str">
+        <v/>
+      </c>
+      <c r="Z196" t="str">
+        <v/>
+      </c>
+      <c r="AA196" t="str">
+        <v/>
+      </c>
+      <c r="AB196" t="str">
+        <v/>
+      </c>
+      <c r="AC196" t="str">
+        <v/>
+      </c>
+      <c r="AD196" t="str">
+        <v/>
+      </c>
+      <c r="AE196" t="str">
+        <v/>
+      </c>
+      <c r="AF196" t="str">
+        <v/>
+      </c>
+      <c r="AG196" t="str">
+        <v/>
+      </c>
+      <c r="AH196" t="str">
+        <v/>
+      </c>
+      <c r="AI196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C197" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197" t="str">
+        <v/>
+      </c>
+      <c r="K197" t="str">
+        <v>יאיר יראי - תופס לך את הדמעות קאבר</v>
+      </c>
+      <c r="L197" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str">
+        <v/>
+      </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
+      <c r="R197" t="str">
+        <v/>
+      </c>
+      <c r="S197" t="str">
+        <v/>
+      </c>
+      <c r="T197" t="str">
+        <v/>
+      </c>
+      <c r="U197" t="str">
+        <v/>
+      </c>
+      <c r="V197" t="str">
+        <v/>
+      </c>
+      <c r="W197" t="str">
+        <v/>
+      </c>
+      <c r="X197" t="str">
+        <v/>
+      </c>
+      <c r="Y197" t="str">
+        <v/>
+      </c>
+      <c r="Z197" t="str">
+        <v/>
+      </c>
+      <c r="AA197" t="str">
+        <v/>
+      </c>
+      <c r="AB197" t="str">
+        <v/>
+      </c>
+      <c r="AC197" t="str">
+        <v/>
+      </c>
+      <c r="AD197" t="str">
+        <v/>
+      </c>
+      <c r="AE197" t="str">
+        <v/>
+      </c>
+      <c r="AF197" t="str">
+        <v/>
+      </c>
+      <c r="AG197" t="str">
+        <v/>
+      </c>
+      <c r="AH197" t="str">
+        <v/>
+      </c>
+      <c r="AI197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="B198" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C198" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
+      <c r="J198" t="str">
+        <v/>
+      </c>
+      <c r="K198" t="str">
+        <v>ברק לוי - לאהוב אותך כל יום קאבר</v>
+      </c>
+      <c r="L198" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str">
+        <v/>
+      </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
+      <c r="R198" t="str">
+        <v/>
+      </c>
+      <c r="S198" t="str">
+        <v/>
+      </c>
+      <c r="T198" t="str">
+        <v/>
+      </c>
+      <c r="U198" t="str">
+        <v/>
+      </c>
+      <c r="V198" t="str">
+        <v/>
+      </c>
+      <c r="W198" t="str">
+        <v/>
+      </c>
+      <c r="X198" t="str">
+        <v/>
+      </c>
+      <c r="Y198" t="str">
+        <v/>
+      </c>
+      <c r="Z198" t="str">
+        <v/>
+      </c>
+      <c r="AA198" t="str">
+        <v/>
+      </c>
+      <c r="AB198" t="str">
+        <v/>
+      </c>
+      <c r="AC198" t="str">
+        <v/>
+      </c>
+      <c r="AD198" t="str">
+        <v/>
+      </c>
+      <c r="AE198" t="str">
+        <v/>
+      </c>
+      <c r="AF198" t="str">
+        <v/>
+      </c>
+      <c r="AG198" t="str">
+        <v/>
+      </c>
+      <c r="AH198" t="str">
+        <v/>
+      </c>
+      <c r="AI198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="B199" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C199" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199" t="str">
+        <v/>
+      </c>
+      <c r="K199" t="str">
+        <v>ברטין - שביל האושר קאבר</v>
+      </c>
+      <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
+        <v/>
+      </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
+      <c r="R199" t="str">
+        <v/>
+      </c>
+      <c r="S199" t="str">
+        <v/>
+      </c>
+      <c r="T199" t="str">
+        <v/>
+      </c>
+      <c r="U199" t="str">
+        <v/>
+      </c>
+      <c r="V199" t="str">
+        <v/>
+      </c>
+      <c r="W199" t="str">
+        <v/>
+      </c>
+      <c r="X199" t="str">
+        <v/>
+      </c>
+      <c r="Y199" t="str">
+        <v/>
+      </c>
+      <c r="Z199" t="str">
+        <v/>
+      </c>
+      <c r="AA199" t="str">
+        <v/>
+      </c>
+      <c r="AB199" t="str">
+        <v/>
+      </c>
+      <c r="AC199" t="str">
+        <v/>
+      </c>
+      <c r="AD199" t="str">
+        <v/>
+      </c>
+      <c r="AE199" t="str">
+        <v/>
+      </c>
+      <c r="AF199" t="str">
+        <v/>
+      </c>
+      <c r="AG199" t="str">
+        <v/>
+      </c>
+      <c r="AH199" t="str">
+        <v/>
+      </c>
+      <c r="AI199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="B200" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C200" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409177&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
+      <c r="K200" t="str">
+        <v>אריאל קנדאבי - גולה סנגם קאבר</v>
+      </c>
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str">
+        <v/>
+      </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
+      <c r="R200" t="str">
+        <v/>
+      </c>
+      <c r="S200" t="str">
+        <v/>
+      </c>
+      <c r="T200" t="str">
+        <v/>
+      </c>
+      <c r="U200" t="str">
+        <v/>
+      </c>
+      <c r="V200" t="str">
+        <v/>
+      </c>
+      <c r="W200" t="str">
+        <v/>
+      </c>
+      <c r="X200" t="str">
+        <v/>
+      </c>
+      <c r="Y200" t="str">
+        <v/>
+      </c>
+      <c r="Z200" t="str">
+        <v/>
+      </c>
+      <c r="AA200" t="str">
+        <v/>
+      </c>
+      <c r="AB200" t="str">
+        <v/>
+      </c>
+      <c r="AC200" t="str">
+        <v/>
+      </c>
+      <c r="AD200" t="str">
+        <v/>
+      </c>
+      <c r="AE200" t="str">
+        <v/>
+      </c>
+      <c r="AF200" t="str">
+        <v/>
+      </c>
+      <c r="AG200" t="str">
+        <v/>
+      </c>
+      <c r="AH200" t="str">
+        <v/>
+      </c>
+      <c r="AI200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="B201" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C201" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409176&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201" t="str">
+        <v/>
+      </c>
+      <c r="K201" t="str">
+        <v>אלירן עטר - את קאבר</v>
+      </c>
+      <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
+        <v/>
+      </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
+      <c r="R201" t="str">
+        <v/>
+      </c>
+      <c r="S201" t="str">
+        <v/>
+      </c>
+      <c r="T201" t="str">
+        <v/>
+      </c>
+      <c r="U201" t="str">
+        <v/>
+      </c>
+      <c r="V201" t="str">
+        <v/>
+      </c>
+      <c r="W201" t="str">
+        <v/>
+      </c>
+      <c r="X201" t="str">
+        <v/>
+      </c>
+      <c r="Y201" t="str">
+        <v/>
+      </c>
+      <c r="Z201" t="str">
+        <v/>
+      </c>
+      <c r="AA201" t="str">
+        <v/>
+      </c>
+      <c r="AB201" t="str">
+        <v/>
+      </c>
+      <c r="AC201" t="str">
+        <v/>
+      </c>
+      <c r="AD201" t="str">
+        <v/>
+      </c>
+      <c r="AE201" t="str">
+        <v/>
+      </c>
+      <c r="AF201" t="str">
+        <v/>
+      </c>
+      <c r="AG201" t="str">
+        <v/>
+      </c>
+      <c r="AH201" t="str">
+        <v/>
+      </c>
+      <c r="AI201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="B202" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C202" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409175&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
+      <c r="K202" t="str">
+        <v>אליקיר - מזל קאבר</v>
+      </c>
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
+      <c r="R202" t="str">
+        <v/>
+      </c>
+      <c r="S202" t="str">
+        <v/>
+      </c>
+      <c r="T202" t="str">
+        <v/>
+      </c>
+      <c r="U202" t="str">
+        <v/>
+      </c>
+      <c r="V202" t="str">
+        <v/>
+      </c>
+      <c r="W202" t="str">
+        <v/>
+      </c>
+      <c r="X202" t="str">
+        <v/>
+      </c>
+      <c r="Y202" t="str">
+        <v/>
+      </c>
+      <c r="Z202" t="str">
+        <v/>
+      </c>
+      <c r="AA202" t="str">
+        <v/>
+      </c>
+      <c r="AB202" t="str">
+        <v/>
+      </c>
+      <c r="AC202" t="str">
+        <v/>
+      </c>
+      <c r="AD202" t="str">
+        <v/>
+      </c>
+      <c r="AE202" t="str">
+        <v/>
+      </c>
+      <c r="AF202" t="str">
+        <v/>
+      </c>
+      <c r="AG202" t="str">
+        <v/>
+      </c>
+      <c r="AH202" t="str">
+        <v/>
+      </c>
+      <c r="AI202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="B203" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C203" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409174&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
+      <c r="K203" t="str">
+        <v>אליאור נונה - תספר לי איך למעלה קאבר</v>
+      </c>
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
+        <v/>
+      </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
+      <c r="R203" t="str">
+        <v/>
+      </c>
+      <c r="S203" t="str">
+        <v/>
+      </c>
+      <c r="T203" t="str">
+        <v/>
+      </c>
+      <c r="U203" t="str">
+        <v/>
+      </c>
+      <c r="V203" t="str">
+        <v/>
+      </c>
+      <c r="W203" t="str">
+        <v/>
+      </c>
+      <c r="X203" t="str">
+        <v/>
+      </c>
+      <c r="Y203" t="str">
+        <v/>
+      </c>
+      <c r="Z203" t="str">
+        <v/>
+      </c>
+      <c r="AA203" t="str">
+        <v/>
+      </c>
+      <c r="AB203" t="str">
+        <v/>
+      </c>
+      <c r="AC203" t="str">
+        <v/>
+      </c>
+      <c r="AD203" t="str">
+        <v/>
+      </c>
+      <c r="AE203" t="str">
+        <v/>
+      </c>
+      <c r="AF203" t="str">
+        <v/>
+      </c>
+      <c r="AG203" t="str">
+        <v/>
+      </c>
+      <c r="AH203" t="str">
+        <v/>
+      </c>
+      <c r="AI203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="B204" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C204" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409173&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
+      <c r="K204" t="str">
+        <v>איתמר שיר - בקרוב זה ישתנה קאבר</v>
+      </c>
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str">
+        <v/>
+      </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
+      <c r="R204" t="str">
+        <v/>
+      </c>
+      <c r="S204" t="str">
+        <v/>
+      </c>
+      <c r="T204" t="str">
+        <v/>
+      </c>
+      <c r="U204" t="str">
+        <v/>
+      </c>
+      <c r="V204" t="str">
+        <v/>
+      </c>
+      <c r="W204" t="str">
+        <v/>
+      </c>
+      <c r="X204" t="str">
+        <v/>
+      </c>
+      <c r="Y204" t="str">
+        <v/>
+      </c>
+      <c r="Z204" t="str">
+        <v/>
+      </c>
+      <c r="AA204" t="str">
+        <v/>
+      </c>
+      <c r="AB204" t="str">
+        <v/>
+      </c>
+      <c r="AC204" t="str">
+        <v/>
+      </c>
+      <c r="AD204" t="str">
+        <v/>
+      </c>
+      <c r="AE204" t="str">
+        <v/>
+      </c>
+      <c r="AF204" t="str">
+        <v/>
+      </c>
+      <c r="AG204" t="str">
+        <v/>
+      </c>
+      <c r="AH204" t="str">
+        <v/>
+      </c>
+      <c r="AI204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="B205" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C205" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409114&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
+      <c r="K205" t="str">
+        <v>דניאל פרטוש - רוח ים קאבר</v>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v/>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+      <c r="R205" t="str">
+        <v/>
+      </c>
+      <c r="S205" t="str">
+        <v/>
+      </c>
+      <c r="T205" t="str">
+        <v/>
+      </c>
+      <c r="U205" t="str">
+        <v/>
+      </c>
+      <c r="V205" t="str">
+        <v/>
+      </c>
+      <c r="W205" t="str">
+        <v/>
+      </c>
+      <c r="X205" t="str">
+        <v/>
+      </c>
+      <c r="Y205" t="str">
+        <v/>
+      </c>
+      <c r="Z205" t="str">
+        <v/>
+      </c>
+      <c r="AA205" t="str">
+        <v/>
+      </c>
+      <c r="AB205" t="str">
+        <v/>
+      </c>
+      <c r="AC205" t="str">
+        <v/>
+      </c>
+      <c r="AD205" t="str">
+        <v/>
+      </c>
+      <c r="AE205" t="str">
+        <v/>
+      </c>
+      <c r="AF205" t="str">
+        <v/>
+      </c>
+      <c r="AG205" t="str">
+        <v/>
+      </c>
+      <c r="AH205" t="str">
+        <v/>
+      </c>
+      <c r="AI205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="B206" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C206" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409113&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
+      <c r="K206" t="str">
+        <v>אביחי טהיא - מהפכה של שמחה קאבר</v>
+      </c>
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
+        <v/>
+      </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
+      <c r="R206" t="str">
+        <v/>
+      </c>
+      <c r="S206" t="str">
+        <v/>
+      </c>
+      <c r="T206" t="str">
+        <v/>
+      </c>
+      <c r="U206" t="str">
+        <v/>
+      </c>
+      <c r="V206" t="str">
+        <v/>
+      </c>
+      <c r="W206" t="str">
+        <v/>
+      </c>
+      <c r="X206" t="str">
+        <v/>
+      </c>
+      <c r="Y206" t="str">
+        <v/>
+      </c>
+      <c r="Z206" t="str">
+        <v/>
+      </c>
+      <c r="AA206" t="str">
+        <v/>
+      </c>
+      <c r="AB206" t="str">
+        <v/>
+      </c>
+      <c r="AC206" t="str">
+        <v/>
+      </c>
+      <c r="AD206" t="str">
+        <v/>
+      </c>
+      <c r="AE206" t="str">
+        <v/>
+      </c>
+      <c r="AF206" t="str">
+        <v/>
+      </c>
+      <c r="AG206" t="str">
+        <v/>
+      </c>
+      <c r="AH206" t="str">
+        <v/>
+      </c>
+      <c r="AI206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="B207" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C207" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409112&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
+      <c r="K207" t="str">
+        <v>תאי חבאני - חלום מתוק קאבר</v>
+      </c>
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
+        <v/>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+      <c r="R207" t="str">
+        <v/>
+      </c>
+      <c r="S207" t="str">
+        <v/>
+      </c>
+      <c r="T207" t="str">
+        <v/>
+      </c>
+      <c r="U207" t="str">
+        <v/>
+      </c>
+      <c r="V207" t="str">
+        <v/>
+      </c>
+      <c r="W207" t="str">
+        <v/>
+      </c>
+      <c r="X207" t="str">
+        <v/>
+      </c>
+      <c r="Y207" t="str">
+        <v/>
+      </c>
+      <c r="Z207" t="str">
+        <v/>
+      </c>
+      <c r="AA207" t="str">
+        <v/>
+      </c>
+      <c r="AB207" t="str">
+        <v/>
+      </c>
+      <c r="AC207" t="str">
+        <v/>
+      </c>
+      <c r="AD207" t="str">
+        <v/>
+      </c>
+      <c r="AE207" t="str">
+        <v/>
+      </c>
+      <c r="AF207" t="str">
+        <v/>
+      </c>
+      <c r="AG207" t="str">
+        <v/>
+      </c>
+      <c r="AH207" t="str">
+        <v/>
+      </c>
+      <c r="AI207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="B208" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C208" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409111&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I208" t="str">
+        <v/>
+      </c>
+      <c r="J208" t="str">
+        <v/>
+      </c>
+      <c r="K208" t="str">
+        <v>רם נעים - מלכת היופי שלי קאבר</v>
+      </c>
+      <c r="L208" t="str">
+        <v/>
+      </c>
+      <c r="M208" t="str">
+        <v/>
+      </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
+      <c r="R208" t="str">
+        <v/>
+      </c>
+      <c r="S208" t="str">
+        <v/>
+      </c>
+      <c r="T208" t="str">
+        <v/>
+      </c>
+      <c r="U208" t="str">
+        <v/>
+      </c>
+      <c r="V208" t="str">
+        <v/>
+      </c>
+      <c r="W208" t="str">
+        <v/>
+      </c>
+      <c r="X208" t="str">
+        <v/>
+      </c>
+      <c r="Y208" t="str">
+        <v/>
+      </c>
+      <c r="Z208" t="str">
+        <v/>
+      </c>
+      <c r="AA208" t="str">
+        <v/>
+      </c>
+      <c r="AB208" t="str">
+        <v/>
+      </c>
+      <c r="AC208" t="str">
+        <v/>
+      </c>
+      <c r="AD208" t="str">
+        <v/>
+      </c>
+      <c r="AE208" t="str">
+        <v/>
+      </c>
+      <c r="AF208" t="str">
+        <v/>
+      </c>
+      <c r="AG208" t="str">
+        <v/>
+      </c>
+      <c r="AH208" t="str">
+        <v/>
+      </c>
+      <c r="AI208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="B209" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C209" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409110&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
+      <c r="J209" t="str">
+        <v/>
+      </c>
+      <c r="K209" t="str">
+        <v>רביד בדיאן - רולקס וקסקט קאבר</v>
+      </c>
+      <c r="L209" t="str">
+        <v/>
+      </c>
+      <c r="M209" t="str">
+        <v/>
+      </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
+      <c r="R209" t="str">
+        <v/>
+      </c>
+      <c r="S209" t="str">
+        <v/>
+      </c>
+      <c r="T209" t="str">
+        <v/>
+      </c>
+      <c r="U209" t="str">
+        <v/>
+      </c>
+      <c r="V209" t="str">
+        <v/>
+      </c>
+      <c r="W209" t="str">
+        <v/>
+      </c>
+      <c r="X209" t="str">
+        <v/>
+      </c>
+      <c r="Y209" t="str">
+        <v/>
+      </c>
+      <c r="Z209" t="str">
+        <v/>
+      </c>
+      <c r="AA209" t="str">
+        <v/>
+      </c>
+      <c r="AB209" t="str">
+        <v/>
+      </c>
+      <c r="AC209" t="str">
+        <v/>
+      </c>
+      <c r="AD209" t="str">
+        <v/>
+      </c>
+      <c r="AE209" t="str">
+        <v/>
+      </c>
+      <c r="AF209" t="str">
+        <v/>
+      </c>
+      <c r="AG209" t="str">
+        <v/>
+      </c>
+      <c r="AH209" t="str">
+        <v/>
+      </c>
+      <c r="AI209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="B210" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C210" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409109&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
+      <c r="J210" t="str">
+        <v/>
+      </c>
+      <c r="K210" t="str">
+        <v>עוז גנון - שיר למעלות קאבר</v>
+      </c>
+      <c r="L210" t="str">
+        <v/>
+      </c>
+      <c r="M210" t="str">
+        <v/>
+      </c>
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v/>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
+      <c r="R210" t="str">
+        <v/>
+      </c>
+      <c r="S210" t="str">
+        <v/>
+      </c>
+      <c r="T210" t="str">
+        <v/>
+      </c>
+      <c r="U210" t="str">
+        <v/>
+      </c>
+      <c r="V210" t="str">
+        <v/>
+      </c>
+      <c r="W210" t="str">
+        <v/>
+      </c>
+      <c r="X210" t="str">
+        <v/>
+      </c>
+      <c r="Y210" t="str">
+        <v/>
+      </c>
+      <c r="Z210" t="str">
+        <v/>
+      </c>
+      <c r="AA210" t="str">
+        <v/>
+      </c>
+      <c r="AB210" t="str">
+        <v/>
+      </c>
+      <c r="AC210" t="str">
+        <v/>
+      </c>
+      <c r="AD210" t="str">
+        <v/>
+      </c>
+      <c r="AE210" t="str">
+        <v/>
+      </c>
+      <c r="AF210" t="str">
+        <v/>
+      </c>
+      <c r="AG210" t="str">
+        <v/>
+      </c>
+      <c r="AH210" t="str">
+        <v/>
+      </c>
+      <c r="AI210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="B211" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C211" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409108&amp;sid=851e07a19b18637a493280e7d70f9d8b</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" t="str">
+        <v/>
+      </c>
+      <c r="K211" t="str">
+        <v>משה סונה - הינך יפה קאבר</v>
+      </c>
+      <c r="L211" t="str">
+        <v/>
+      </c>
+      <c r="M211" t="str">
+        <v/>
+      </c>
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
+      <c r="R211" t="str">
+        <v/>
+      </c>
+      <c r="S211" t="str">
+        <v/>
+      </c>
+      <c r="T211" t="str">
+        <v/>
+      </c>
+      <c r="U211" t="str">
+        <v/>
+      </c>
+      <c r="V211" t="str">
+        <v/>
+      </c>
+      <c r="W211" t="str">
+        <v/>
+      </c>
+      <c r="X211" t="str">
+        <v/>
+      </c>
+      <c r="Y211" t="str">
+        <v/>
+      </c>
+      <c r="Z211" t="str">
+        <v/>
+      </c>
+      <c r="AA211" t="str">
+        <v/>
+      </c>
+      <c r="AB211" t="str">
+        <v/>
+      </c>
+      <c r="AC211" t="str">
+        <v/>
+      </c>
+      <c r="AD211" t="str">
+        <v/>
+      </c>
+      <c r="AE211" t="str">
+        <v/>
+      </c>
+      <c r="AF211" t="str">
+        <v/>
+      </c>
+      <c r="AG211" t="str">
+        <v/>
+      </c>
+      <c r="AH211" t="str">
+        <v/>
+      </c>
+      <c r="AI211" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI211"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -442,7 +442,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
@@ -457,15 +457,18 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
       </c>
     </row>
@@ -477,7 +480,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
@@ -492,15 +495,18 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
       </c>
     </row>
@@ -512,7 +518,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -527,15 +533,18 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
       </c>
     </row>
@@ -547,7 +556,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
@@ -562,15 +571,18 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>קובי בוקעי - Like The End Cover להורדה</v>
       </c>
     </row>
@@ -582,7 +594,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -597,15 +609,18 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>קארין עמוס - תפילות קאבר להורדה</v>
       </c>
     </row>
@@ -617,7 +632,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -632,15 +647,18 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
       </c>
     </row>
@@ -652,7 +670,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -667,15 +685,18 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>נועם דדון - הקסם השחור קאבר להורדה</v>
       </c>
     </row>
@@ -687,7 +708,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -702,15 +723,18 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
       </c>
     </row>
@@ -722,7 +746,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
@@ -737,15 +761,18 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
       </c>
     </row>
@@ -757,7 +784,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
@@ -772,15 +799,18 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
       </c>
     </row>
@@ -792,7 +822,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -807,15 +837,18 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>ברטין - Seni Dusundum Cover להורדה</v>
       </c>
     </row>
@@ -827,7 +860,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
@@ -842,15 +875,18 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
       </c>
     </row>
@@ -862,7 +898,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -877,15 +913,18 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
     </row>
@@ -897,7 +936,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
@@ -912,15 +951,18 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
     </row>
@@ -932,7 +974,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-22</v>
@@ -947,15 +989,18 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
     </row>
@@ -967,7 +1012,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-22</v>
@@ -982,15 +1027,18 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
     </row>
@@ -1002,7 +1050,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-22</v>
@@ -1017,15 +1065,18 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
     </row>
@@ -1037,7 +1088,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-22</v>
@@ -1052,15 +1103,18 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
     </row>
@@ -1072,7 +1126,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-22</v>
@@ -1087,15 +1141,18 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
     </row>
@@ -1107,7 +1164,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-22</v>
@@ -1122,15 +1179,18 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
     </row>
@@ -1142,7 +1202,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-22</v>
@@ -1157,15 +1217,18 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
     </row>
@@ -1177,7 +1240,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-22</v>
@@ -1192,15 +1255,18 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>פארידה - Darixdim Cover להורדה</v>
       </c>
     </row>
@@ -1212,7 +1278,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-22</v>
@@ -1227,15 +1293,18 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
     </row>
@@ -1247,7 +1316,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-22</v>
@@ -1262,15 +1331,18 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
     </row>
@@ -1282,7 +1354,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-22</v>
@@ -1297,15 +1369,18 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
     </row>
@@ -1317,7 +1392,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-22</v>
@@ -1332,15 +1407,18 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
     </row>
@@ -1352,7 +1430,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-22</v>
@@ -1367,15 +1445,18 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
     </row>
@@ -1387,7 +1468,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-22</v>
@@ -1402,15 +1483,18 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
     </row>
@@ -1422,7 +1506,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-22</v>
@@ -1437,15 +1521,18 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J30" t="str">
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
     </row>
@@ -1457,7 +1544,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-22</v>
@@ -1472,21 +1559,24 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -480,7 +480,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -518,7 +518,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -556,7 +556,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -594,7 +594,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -632,7 +632,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -670,7 +670,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -708,7 +708,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -738,9 +738,845 @@
         <v>אבירם ברמי - איפה את קאבר להורדה</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>קובי בוקעי - Like The End Cover להורדה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>קובי בוקעי - Like The End Cover להורדה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>קארין עמוס - תפילות קאבר להורדה</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>קארין עמוס - תפילות קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ברטין - Seni Dusundum Cover להורדה</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>ברטין - Seni Dusundum Cover להורדה</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C25" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C26" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C27" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C28" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C29" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C30" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>פארידה - Darixdim Cover להורדה</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C31" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>פארידה - Darixdim Cover להורדה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון ביטון - תפילות קאבר להורדה</v>
+        <v>שמעון ביטון - תפילות קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון ביטון - תפילות קאבר להורדה</v>
+        <v>שמעון ביטון - תפילות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
+        <v>נריה עובדיה - ילדה של אב קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
+        <v>נריה עובדיה - ילדה של אב קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
+        <v>נועם דדון - זר של נרקיסים קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
+        <v>נועם דדון - זר של נרקיסים קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
+        <v>יהונתן נחמיאס - מאשאפ חופות 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
+        <v>יהונתן נחמיאס - מאשאפ חופות 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
+        <v>חנוך שובל - עולם בשני צבעים קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
+        <v>חנוך שובל - עולם בשני צבעים קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>חן גז - אהבה חולה קאבר להורדה</v>
+        <v>חן גז - אהבה חולה קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>חן גז - אהבה חולה קאבר להורדה</v>
+        <v>חן גז - אהבה חולה קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
+        <v>אוריאל שלום - אשת חיל שלי קאבר</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
+        <v>אוריאל שלום - אשת חיל שלי קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבירם ברמי - איפה את קאבר להורדה</v>
+        <v>אבירם ברמי - איפה את קאבר</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבירם ברמי - איפה את קאבר להורדה</v>
+        <v>אבירם ברמי - איפה את קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+        <v>רון חטיבי - גודל הכאב קאבר</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+        <v>רון חטיבי - גודל הכאב קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>קובי בוקעי - Like The End Cover להורדה</v>
+        <v>קובי בוקעי - Like The End Cover</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>קובי בוקעי - Like The End Cover להורדה</v>
+        <v>קובי בוקעי - Like The End Cover</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>קארין עמוס - תפילות קאבר להורדה</v>
+        <v>קארין עמוס - תפילות קאבר</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>קארין עמוס - תפילות קאבר להורדה</v>
+        <v>קארין עמוס - תפילות קאבר</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+        <v>עילאי גניש - מצייר אותך קאבר</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+        <v>עילאי גניש - מצייר אותך קאבר</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+        <v>נועם דדון - הקסם השחור קאבר</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+        <v>נועם דדון - הקסם השחור קאבר</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+        <v>מתנאל סבח - עד יום מותי קאבר</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+        <v>מתנאל סבח - עד יום מותי קאבר</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+        <v>ליה נחום - בסיבוב הבא קאבר</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+        <v>ליה נחום - בסיבוב הבא קאבר</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+        <v>ליאל גוטמן - אצלנו בגן קאבר</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+        <v>ליאל גוטמן - אצלנו בגן קאבר</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ברטין - Seni Dusundum Cover להורדה</v>
+        <v>ברטין - Seni Dusundum Cover</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>ברטין - Seni Dusundum Cover להורדה</v>
+        <v>ברטין - Seni Dusundum Cover</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+        <v>אביחי טהיא - שביל האושר קאבר</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+        <v>אביחי טהיא - שביל האושר קאבר</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>איימי - אהבה רעילה קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B28" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>איימי - אהבה רעילה קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B29" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B30" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B31" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1571,7 +1571,7 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -442,7 +442,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-24</v>
@@ -480,7 +480,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-24</v>
@@ -518,7 +518,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-24</v>
@@ -556,7 +556,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-24</v>
@@ -594,7 +594,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-24</v>
@@ -632,7 +632,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-24</v>
@@ -670,7 +670,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-24</v>
@@ -708,7 +708,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-24</v>
@@ -746,7 +746,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-24</v>
@@ -784,7 +784,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-24</v>
@@ -822,7 +822,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-24</v>
@@ -860,7 +860,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-24</v>
@@ -898,7 +898,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-24</v>
@@ -936,7 +936,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-24</v>
@@ -974,7 +974,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-24</v>
@@ -1012,7 +1012,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-24</v>
@@ -1050,7 +1050,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-24</v>
@@ -1088,7 +1088,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-24</v>
@@ -1126,7 +1126,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-24</v>
@@ -1164,7 +1164,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-24</v>
@@ -1202,7 +1202,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-24</v>
@@ -1240,7 +1240,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-24</v>
@@ -1278,7 +1278,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-24</v>
@@ -1316,7 +1316,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-24</v>
@@ -1354,7 +1354,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-24</v>
@@ -1392,7 +1392,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-24</v>
@@ -1430,7 +1430,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-24</v>
@@ -1468,7 +1468,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-24</v>
@@ -1506,7 +1506,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-24</v>
@@ -1544,7 +1544,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-24</v>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עילאי בודאני - תמיד שמח &amp; ציפור זרה קאבר</v>
+        <v>בן חן - Napiyosun Mesela Cover</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409362&amp;sid=c435c2a5a44d5ce4653fe25328d0c6bc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409387&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עילאי בודאני - תמיד שמח &amp; ציפור זרה קאבר</v>
+        <v>בן חן - Napiyosun Mesela Cover</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409386&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409385&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן חן - Napiyosun Mesela Cover</v>
+        <v>רועי יעקב - גיבור של אמא קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409387&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409399&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-28</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן חן - Napiyosun Mesela Cover</v>
+        <v>רועי יעקב - גיבור של אמא קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+        <v>קובי בוקעי - Daydreaming Cover</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-28</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409386&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409398&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-28</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+        <v>קובי בוקעי - Daydreaming Cover</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
+        <v>נחמן סבג - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-28</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409385&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409397&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-28</v>
@@ -545,12 +545,354 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
+        <v>נחמן סבג - אל תעזוב אותי קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מתנאל סבח - כשאחר קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409396&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מתנאל סבח - כשאחר קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאי רובין - עד מחר קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409395&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאי רובין - עד מחר קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יוסף כהן - ירח בננה קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409394&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יוסף כהן - ירח בננה קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יגאל עדי - הבטחות שווא קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409393&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יגאל עדי - הבטחות שווא קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יאיר יראי - תמיד שמח קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409392&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יאיר יראי - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>טל ועקנין &amp; העבריים מדימונה - לכל אחד יש קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409391&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>טל ועקנין &amp; העבריים מדימונה - לכל אחד יש קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>חנוך שובל &amp; עילאי אלול - תמיד שמח קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409390&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>חנוך שובל &amp; עילאי אלול - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חיים איפרגן - לא כמו פעם קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409389&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חיים איפרגן - לא כמו פעם קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>גל וקנין - הנך יפה קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409388&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>גל וקנין - הנך יפה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי יעקב - גיבור של אמא קאבר</v>
+        <v>מאיר בן הרוש - קח אוויר קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409399&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409466&amp;sid=f414d17277694758434992880ac90efb</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רועי יעקב - גיבור של אמא קאבר</v>
+        <v>מאיר בן הרוש - קח אוויר קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קובי בוקעי - Daydreaming Cover</v>
+        <v>הנסיך מהמזרח - הבוגדת קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409398&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409465&amp;sid=f414d17277694758434992880ac90efb</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קובי בוקעי - Daydreaming Cover</v>
+        <v>הנסיך מהמזרח - הבוגדת קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נחמן סבג - אל תעזוב אותי קאבר</v>
+        <v>בן גורן - האישה הכי יפה בעולם קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409397&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409464&amp;sid=f414d17277694758434992880ac90efb</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נחמן סבג - אל תעזוב אותי קאבר</v>
+        <v>בן גורן - האישה הכי יפה בעולם קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מתנאל סבח - כשאחר קאבר</v>
+        <v>אלרום יעקב - אני ואת קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409396&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409463&amp;sid=f414d17277694758434992880ac90efb</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מתנאל סבח - כשאחר קאבר</v>
+        <v>אלרום יעקב - אני ואת קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מאי רובין - עד מחר קאבר</v>
+        <v>אלמוג טויטו - עת דודים כלה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409395&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409462&amp;sid=f414d17277694758434992880ac90efb</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מאי רובין - עד מחר קאבר</v>
+        <v>אלמוג טויטו - עת דודים כלה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יוסף כהן - ירח בננה קאבר</v>
+        <v>אבישי עוזיאל - השנה החדשה שלי קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409394&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409461&amp;sid=f414d17277694758434992880ac90efb</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-28</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,240 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יוסף כהן - ירח בננה קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>יגאל עדי - הבטחות שווא קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409393&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>יגאל עדי - הבטחות שווא קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>יאיר יראי - תמיד שמח קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409392&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>יאיר יראי - תמיד שמח קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>טל ועקנין &amp; העבריים מדימונה - לכל אחד יש קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409391&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>טל ועקנין &amp; העבריים מדימונה - לכל אחד יש קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>חנוך שובל &amp; עילאי אלול - תמיד שמח קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409390&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>חנוך שובל &amp; עילאי אלול - תמיד שמח קאבר</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>חיים איפרגן - לא כמו פעם קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409389&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>חיים איפרגן - לא כמו פעם קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>גל וקנין - הנך יפה קאבר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409388&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-01-28</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>גל וקנין - הנך יפה קאבר</v>
+        <v>אבישי עוזיאל - השנה החדשה שלי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאיר בן הרוש - קח אוויר קאבר</v>
+        <v>נועה שירי - אבא גדול קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409466&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409473&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאיר בן הרוש - קח אוויר קאבר</v>
+        <v>נועה שירי - אבא גדול קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הנסיך מהמזרח - הבוגדת קאבר</v>
+        <v>רון אהרוני - מאוהב בגשם קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409465&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409472&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-03</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הנסיך מהמזרח - הבוגדת קאבר</v>
+        <v>רון אהרוני - מאוהב בגשם קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>בן גורן - האישה הכי יפה בעולם קאבר</v>
+        <v>קורל אמויאל - אמא קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409464&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409471&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-03</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>בן גורן - האישה הכי יפה בעולם קאבר</v>
+        <v>קורל אמויאל - אמא קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אלרום יעקב - אני ואת קאבר</v>
+        <v>קובי צור - המחר קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409463&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409470&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-03</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אלרום יעקב - אני ואת קאבר</v>
+        <v>קובי צור - המחר קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אלמוג טויטו - עת דודים כלה קאבר</v>
+        <v>עקיבא בן חמו - ילדי קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409462&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409469&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-03</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אלמוג טויטו - עת דודים כלה קאבר</v>
+        <v>עקיבא בן חמו - ילדי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אבישי עוזיאל - השנה החדשה שלי קאבר</v>
+        <v>סהר לוי - גן עדן קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409461&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409468&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-03</v>
@@ -659,12 +659,50 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אבישי עוזיאל - השנה החדשה שלי קאבר</v>
+        <v>סהר לוי - גן עדן קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נועם צ'נרו - שקט קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409467&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נועם צ'נרו - שקט קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה שירי - אבא גדול קאבר</v>
+        <v>ירין אדרי - צעקות וקללות קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409473&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409475&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה שירי - אבא גדול קאבר</v>
+        <v>ירין אדרי - צעקות וקללות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון אהרוני - מאוהב בגשם קאבר</v>
+        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409472&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409474&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-03</v>
@@ -507,202 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון אהרוני - מאוהב בגשם קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>קורל אמויאל - אמא קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409471&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>קורל אמויאל - אמא קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>קובי צור - המחר קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409470&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>קובי צור - המחר קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>עקיבא בן חמו - ילדי קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409469&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>עקיבא בן חמו - ילדי קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>סהר לוי - גן עדן קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409468&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>סהר לוי - גן עדן קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נועם צ'נרו - שקט קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409467&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נועם צ'נרו - שקט קאבר</v>
+        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ירין אדרי - צעקות וקללות קאבר</v>
+        <v>טל בן מויאל - אהבה ברכב קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409475&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409476&amp;sid=85a43ebc12c9917d756b212c36ac93e5</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ירין אדרי - צעקות וקללות קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409474&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
+        <v>טל בן מויאל - אהבה ברכב קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>טל בן מויאל - אהבה ברכב קאבר</v>
+        <v>רויטל ממן - פנים מול פנים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409476&amp;sid=85a43ebc12c9917d756b212c36ac93e5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409522&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>טל בן מויאל - אהבה ברכב קאבר</v>
+        <v>רויטל ממן - פנים מול פנים קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>נתנאל ברק - הספסל השבור קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409521&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>נתנאל ברק - הספסל השבור קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נועם דדון - סיגל קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409520&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נועם דדון - סיגל קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נויה ערבה - גן עדן קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409519&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נויה ערבה - גן עדן קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאיר רובין - רחקי מכולם קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409518&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאיר רובין - רחקי מכולם קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409517&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דניאל דרחי - מדאם קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409516&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דניאל דרחי - מדאם קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דור כהן - מקלט לדמעותיי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409515&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דור כהן - מקלט לדמעותיי קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אודי דמארי - פשוט אנשים קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409514&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אודי דמארי - פשוט אנשים קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רויטל ממן - פנים מול פנים קאבר</v>
+        <v>חנוך שובל - אם את כבר הולכת קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409522&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409525&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רויטל ממן - פנים מול פנים קאבר</v>
+        <v>חנוך שובל - אם את כבר הולכת קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ברק - הספסל השבור קאבר</v>
+        <v>אליה ביתן - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409521&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409524&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ברק - הספסל השבור קאבר</v>
+        <v>אליה ביתן - אל תעזוב אותי קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם דדון - סיגל קאבר</v>
+        <v>אבישי עוזיאל - יש מבול קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409520&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409523&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,240 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם דדון - סיגל קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נויה ערבה - גן עדן קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409519&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נויה ערבה - גן עדן קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מאיר רובין - רחקי מכולם קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409518&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מאיר רובין - רחקי מכולם קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409517&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דניאל דרחי - מדאם קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409516&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דניאל דרחי - מדאם קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דור כהן - מקלט לדמעותיי קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409515&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דור כהן - מקלט לדמעותיי קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אודי דמארי - פשוט אנשים קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409514&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אודי דמארי - פשוט אנשים קאבר</v>
+        <v>אבישי עוזיאל - יש מבול קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חנוך שובל - אם את כבר הולכת קאבר</v>
+        <v>אליה אבוקרט - אמא יקרה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409525&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409575&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-15</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חנוך שובל - אם את כבר הולכת קאבר</v>
+        <v>אליה אבוקרט - אמא יקרה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אליה ביתן - אל תעזוב אותי קאבר</v>
+        <v>אופק המלאך - אין מילים איתך קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409524&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409574&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-15</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אליה ביתן - אל תעזוב אותי קאבר</v>
+        <v>אופק המלאך - אין מילים איתך קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אבישי עוזיאל - יש מבול קאבר</v>
+        <v>אופיר נגר - Aramam Cover</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409523&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409573&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-07</v>
+        <v>2026-02-15</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,12 +545,50 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אבישי עוזיאל - יש מבול קאבר</v>
+        <v>אופיר נגר - Aramam Cover</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409572&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אליה אבוקרט - אמא יקרה קאבר</v>
+        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409575&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409582&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-15</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אליה אבוקרט - אמא יקרה קאבר</v>
+        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אופק המלאך - אין מילים איתך קאבר</v>
+        <v>נאור בן דוד - כמו בימים קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409574&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409581&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-15</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אופק המלאך - אין מילים איתך קאבר</v>
+        <v>נאור בן דוד - כמו בימים קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אופיר נגר - Aramam Cover</v>
+        <v>ליאן אמסלם - יכולה לבד קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409573&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409580&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-15</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אופיר נגר - Aramam Cover</v>
+        <v>ליאן אמסלם - יכולה לבד קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
+        <v>הדר מעוז - גולה סאנגם קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409572&amp;sid=a8a5a1e57229330c535f7e1a7942dafa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409579&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-15</v>
@@ -583,12 +583,126 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אבישי עוזיאל - אין לי אותך קאבר</v>
+        <v>הדר מעוז - גולה סאנגם קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409578&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>דניאל בן משיח - ממעמקים קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409577&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>דניאל בן משיח - ממעמקים קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>בן ישכרוב - מזל קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409576&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>בן ישכרוב - מזל קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
+        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409582&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409588&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-15</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נגה ון-דר ולדה - מלכת הדור קאבר</v>
+        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נאור בן דוד - כמו בימים קאבר</v>
+        <v>תאי חבאני - הגולה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409581&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409587&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-15</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נאור בן דוד - כמו בימים קאבר</v>
+        <v>תאי חבאני - הגולה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאן אמסלם - יכולה לבד קאבר</v>
+        <v>שרון זריהן - רק איתך קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409580&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409586&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-15</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאן אמסלם - יכולה לבד קאבר</v>
+        <v>שרון זריהן - רק איתך קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הדר מעוז - גולה סאנגם קאבר</v>
+        <v>שילת ויצמן - הנך יפה קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409579&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409585&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-15</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>הדר מעוז - גולה סאנגם קאבר</v>
+        <v>שילת ויצמן - הנך יפה קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+        <v>שי חזן - חי איך שבא לי קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409578&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409584&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-15</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>דניאל חן - התמונות שבאלבום קאבר</v>
+        <v>שי חזן - חי איך שבא לי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל בן משיח - ממעמקים קאבר</v>
+        <v>צוריאל - הפרח בגני קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409577&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409583&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-15</v>
@@ -659,50 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דניאל בן משיח - ממעמקים קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>בן ישכרוב - מזל קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409576&amp;sid=d09027a3b24c8cd942795a30f95f3436</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>בן ישכרוב - מזל קאבר</v>
+        <v>צוריאל - הפרח בגני קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
+        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409588&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409596&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהל עזרא - רציתי לדבר איתך קאבר</v>
+        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תאי חבאני - הגולה קאבר</v>
+        <v>יהל עמר - עד סוף העולם קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409587&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409595&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תאי חבאני - הגולה קאבר</v>
+        <v>יהל עמר - עד סוף העולם קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שרון זריהן - רק איתך קאבר</v>
+        <v>יהל עמר - הנך יפה קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409586&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409594&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שרון זריהן - רק איתך קאבר</v>
+        <v>יהל עמר - הנך יפה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שילת ויצמן - הנך יפה קאבר</v>
+        <v>חנוך שובל - Aktar Cover</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409585&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409593&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שילת ויצמן - הנך יפה קאבר</v>
+        <v>חנוך שובל - Aktar Cover</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שי חזן - חי איך שבא לי קאבר</v>
+        <v>חגית ביטון חג'בי - Never Enough Cover</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409584&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409592&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שי חזן - חי איך שבא לי קאבר</v>
+        <v>חגית ביטון חג'בי - Never Enough Cover</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>צוריאל - הפרח בגני קאבר</v>
+        <v>הודיה לוי - יכולה לבד קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409583&amp;sid=1be5e63e81c8e2b5e975cab900ebe0ae</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409591&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,88 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>צוריאל - הפרח בגני קאבר</v>
+        <v>הודיה לוי - יכולה לבד קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409590&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409589&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
+        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409596&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409602&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל קונסטנטיני - כמה מתוק קאבר</v>
+        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהל עמר - עד סוף העולם קאבר</v>
+        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409595&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409601&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהל עמר - עד סוף העולם קאבר</v>
+        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יהל עמר - הנך יפה קאבר</v>
+        <v>שי שלום - שרק תחייך קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409594&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409600&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יהל עמר - הנך יפה קאבר</v>
+        <v>שי שלום - שרק תחייך קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>חנוך שובל - Aktar Cover</v>
+        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409593&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409599&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>חנוך שובל - Aktar Cover</v>
+        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חגית ביטון חג'בי - Never Enough Cover</v>
+        <v>מתן טולדנו - עינייך מספרות קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409592&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409598&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חגית ביטון חג'בי - Never Enough Cover</v>
+        <v>מתן טולדנו - עינייך מספרות קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הודיה לוי - יכולה לבד קאבר</v>
+        <v>ליעד - יום אהבה ראשון קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409591&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409597&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>הודיה לוי - יכולה לבד קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409590&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלרואי &amp; אביה - מגנט &amp; הייתי חוזרת קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409589&amp;sid=846b7ed9141fdd03f79af5d3710d71af</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אוריה בן שושן - אלוקיי תן שלום קאבר</v>
+        <v>ליעד - יום אהבה ראשון קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
+        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409602&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409603&amp;sid=aaf75d33e307b5a16fb4b3cf00589b10</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צביקי רנד &amp; יהודה רושגולד &amp; איציק עקשטיין - מיין הארץ קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409601&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שירה אורן - קצת משונה שלא נשארת קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שי שלום - שרק תחייך קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409600&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שי שלום - שרק תחייך קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409599&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עידו עמדור - תצאי לי מהראש קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מתן טולדנו - עינייך מספרות קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409598&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מתן טולדנו - עינייך מספרות קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ליעד - יום אהבה ראשון קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409597&amp;sid=d67bf896a4ea73f11a2df696159cf3c7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ליעד - יום אהבה ראשון קאבר</v>
+        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
+        <v>תאי חבאני - נשבעתי לך ילדה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409603&amp;sid=aaf75d33e307b5a16fb4b3cf00589b10</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409676&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמוליק טליאס &amp; טהר טליאס - כינורי קאבר</v>
+        <v>תאי חבאני - נשבעתי לך ילדה קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שלמה דעוס - היום קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409675&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שלמה דעוס - היום קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתנאל סורילוב - מאשאפ חשבונות שמיים &amp; ביחד איתי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409674&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתנאל סורילוב - מאשאפ חשבונות שמיים &amp; ביחד איתי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מאיר שטרית - תמאלי מעאק קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409673&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מאיר שטרית - תמאלי מעאק קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>זוהר אשירוב &amp; בתאל אדרי - תגידי קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409672&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>זוהר אשירוב &amp; בתאל אדרי - תגידי קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>הודיה שמואל - רוח ים קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409671&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>הודיה שמואל - רוח ים קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלון מיכאל - חבקי אותי קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409670&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלון מיכאל - חבקי אותי קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אחיה קובי &amp; שלומי אמסלם - לכה דודי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409669&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אחיה קובי &amp; שלומי אמסלם - לכה דודי קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אושר פלמן - בואי אמא קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409668&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אושר פלמן - בואי אמא קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אבנר הררי &amp; איתי הררי - בין הטוב והרע קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409667&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אבנר הררי &amp; איתי הררי - בין הטוב והרע קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבירם ברמי - תחזרי קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409666&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבירם ברמי - תחזרי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תאי חבאני - נשבעתי לך ילדה קאבר</v>
+        <v>מאיר בן הרוש - צל עץ תמר קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409676&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409769&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תאי חבאני - נשבעתי לך ילדה קאבר</v>
+        <v>מאיר בן הרוש - צל עץ תמר קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלמה דעוס - היום קאבר</v>
+        <v>לינוי אוחנה - שכחת את הכל קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409675&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409768&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלמה דעוס - היום קאבר</v>
+        <v>לינוי אוחנה - שכחת את הכל קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתנאל סורילוב - מאשאפ חשבונות שמיים &amp; ביחד איתי</v>
+        <v>ליאם פרץ - צעקתי בלילה קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409674&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409767&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתנאל סורילוב - מאשאפ חשבונות שמיים &amp; ביחד איתי</v>
+        <v>ליאם פרץ - צעקתי בלילה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מאיר שטרית - תמאלי מעאק קאבר</v>
+        <v>ליאור קקון - היום קמתי שמח קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409673&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409766&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מאיר שטרית - תמאלי מעאק קאבר</v>
+        <v>ליאור קקון - היום קמתי שמח קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>זוהר אשירוב &amp; בתאל אדרי - תגידי קאבר</v>
+        <v>ליאור לוי - אלוהים אלוהים קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409672&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409765&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>זוהר אשירוב &amp; בתאל אדרי - תגידי קאבר</v>
+        <v>ליאור לוי - אלוהים אלוהים קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הודיה שמואל - רוח ים קאבר</v>
+        <v>ליאור חייט - יש בך הכל קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409671&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409764&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>הודיה שמואל - רוח ים קאבר</v>
+        <v>ליאור חייט - יש בך הכל קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלון מיכאל - חבקי אותי קאבר</v>
+        <v>יהונתן לוי - אם אשכחך קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409670&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409763&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אלון מיכאל - חבקי אותי קאבר</v>
+        <v>יהונתן לוי - אם אשכחך קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אחיה קובי &amp; שלומי אמסלם - לכה דודי קאבר</v>
+        <v>חן גז - רולקס וקסקט קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409669&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409762&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אחיה קובי &amp; שלומי אמסלם - לכה דודי קאבר</v>
+        <v>חן גז - רולקס וקסקט קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אושר פלמן - בואי אמא קאבר</v>
+        <v>חיים משה - בואי בשלום קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409668&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409761&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אושר פלמן - בואי אמא קאבר</v>
+        <v>חיים משה - בואי בשלום קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבנר הררי &amp; איתי הררי - בין הטוב והרע קאבר</v>
+        <v>הראל מעודה - תמיד שמח קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409667&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409760&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבנר הררי &amp; איתי הררי - בין הטוב והרע קאבר</v>
+        <v>הראל מעודה - תמיד שמח קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אבירם ברמי - תחזרי קאבר</v>
+        <v>בן מירן - רק אל תגידי קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409666&amp;sid=1d2db5b1333d25f65c24eb3f2c1667e1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409759&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,12 +849,202 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אבירם ברמי - תחזרי קאבר</v>
+        <v>בן מירן - רק אל תגידי קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>בן יוסף דניאל - אני מקווה קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409758&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>בן יוסף דניאל - אני מקווה קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אריאל דימנט - כשאתה קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409757&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אריאל דימנט - כשאתה קאבר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אלון דהן - נבראתי לך קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409756&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אלון דהן - נבראתי לך קאבר</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אלון דהן - דברים שרציתי לומר קאבר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409755&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אלון דהן - דברים שרציתי לומר קאבר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>איתמר הרוש - ממעמקים &amp; תפילות</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409754&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>איתמר הרוש - ממעמקים &amp; תפילות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאיר בן הרוש - צל עץ תמר קאבר</v>
+        <v>צורי תלבי - אמא קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409769&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409775&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאיר בן הרוש - צל עץ תמר קאבר</v>
+        <v>צורי תלבי - אמא קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>לינוי אוחנה - שכחת את הכל קאבר</v>
+        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409768&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409774&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>לינוי אוחנה - שכחת את הכל קאבר</v>
+        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאם פרץ - צעקתי בלילה קאבר</v>
+        <v>נתנאל ביטון - פינה של שקט קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409767&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409773&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאם פרץ - צעקתי בלילה קאבר</v>
+        <v>נתנאל ביטון - פינה של שקט קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ליאור קקון - היום קמתי שמח קאבר</v>
+        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409766&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409772&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-26</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ליאור קקון - היום קמתי שמח קאבר</v>
+        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור לוי - אלוהים אלוהים קאבר</v>
+        <v>גלית - מאשאפ חתונה 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409765&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409771&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-26</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור לוי - אלוהים אלוהים קאבר</v>
+        <v>גלית - מאשאפ חתונה 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאור חייט - יש בך הכל קאבר</v>
+        <v>גלית - לאהוב אותך כל יום קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409764&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409770&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-26</v>
@@ -659,392 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאור חייט - יש בך הכל קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>יהונתן לוי - אם אשכחך קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409763&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>יהונתן לוי - אם אשכחך קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>חן גז - רולקס וקסקט קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409762&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>חן גז - רולקס וקסקט קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>חיים משה - בואי בשלום קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409761&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>חיים משה - בואי בשלום קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>הראל מעודה - תמיד שמח קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409760&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>הראל מעודה - תמיד שמח קאבר</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>בן מירן - רק אל תגידי קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409759&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>בן מירן - רק אל תגידי קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>בן יוסף דניאל - אני מקווה קאבר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409758&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>בן יוסף דניאל - אני מקווה קאבר</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אריאל דימנט - כשאתה קאבר</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409757&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אריאל דימנט - כשאתה קאבר</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אלון דהן - נבראתי לך קאבר</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409756&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אלון דהן - נבראתי לך קאבר</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אלון דהן - דברים שרציתי לומר קאבר</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409755&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אלון דהן - דברים שרציתי לומר קאבר</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>איתמר הרוש - ממעמקים &amp; תפילות</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409754&amp;sid=8814a6a20910d3663f73afea7cae5e33</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>איתמר הרוש - ממעמקים &amp; תפילות</v>
+        <v>גלית - לאהוב אותך כל יום קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צורי תלבי - אמא קאבר</v>
+        <v>שיר מזרחי - ממעמקים &amp; הנך יפה קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409775&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409782&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צורי תלבי - אמא קאבר</v>
+        <v>שיר מזרחי - ממעמקים &amp; הנך יפה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
+        <v>שיר חסון - עכשיו התור לאהבה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409774&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409781&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>חנוך שובל - פיסה מזכרוני קאבר</v>
+        <v>שיר חסון - עכשיו התור לאהבה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתנאל ביטון - פינה של שקט קאבר</v>
+        <v>שילת סופר - מרצדס שחורה קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409773&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409780&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתנאל ביטון - פינה של שקט קאבר</v>
+        <v>שילת סופר - מרצדס שחורה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
+        <v>שגיא גטר - הסכם שלום (צרפתית) + מדאם</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409772&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409779&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-26</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>משה כהן - שלווה בארמונותייך &amp; תפילות קאבר</v>
+        <v>שגיא גטר - הסכם שלום (צרפתית) + מדאם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>גלית - מאשאפ חתונה 2026</v>
+        <v>קורין גמליאל - סינדרלה קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409771&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409778&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-26</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>גלית - מאשאפ חתונה 2026</v>
+        <v>קורין גמליאל - סינדרלה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>גלית - לאהוב אותך כל יום קאבר</v>
+        <v>צורי תלבי - איפה את קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409770&amp;sid=8c75bba932c4bbf7981a04fd1e636dcf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409777&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-26</v>
@@ -659,12 +659,50 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>גלית - לאהוב אותך כל יום קאבר</v>
+        <v>צורי תלבי - איפה את קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מיקו אנג'ל &amp; ישראל שטרית - אמא אל תבכי קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409776&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מיקו אנג'ל &amp; ישראל שטרית - אמא אל תבכי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר מזרחי - ממעמקים &amp; הנך יפה קאבר</v>
+        <v>שלו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409782&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409858&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר מזרחי - ממעמקים &amp; הנך יפה קאבר</v>
+        <v>שלו חנן - כל הדרך הביתה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שיר חסון - עכשיו התור לאהבה קאבר</v>
+        <v>עילאי גניש - שכחת את הכל קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409781&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409857&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שיר חסון - עכשיו התור לאהבה קאבר</v>
+        <v>עילאי גניש - שכחת את הכל קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שילת סופר - מרצדס שחורה קאבר</v>
+        <v>נועם דדון - שירו של צנחן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409780&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409856&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שילת סופר - מרצדס שחורה קאבר</v>
+        <v>נועם דדון - שירו של צנחן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שגיא גטר - הסכם שלום (צרפתית) + מדאם</v>
+        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409779&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409855&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שגיא גטר - הסכם שלום (צרפתית) + מדאם</v>
+        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>קורין גמליאל - סינדרלה קאבר</v>
+        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409778&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409854&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>קורין גמליאל - סינדרלה קאבר</v>
+        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>צורי תלבי - איפה את קאבר</v>
+        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409777&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409853&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>צורי תלבי - איפה את קאבר</v>
+        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>מיקו אנג'ל &amp; ישראל שטרית - אמא אל תבכי קאבר</v>
+        <v>ליאור כהן - הצייר קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409776&amp;sid=f304e5d13091c1440f6437d3794a846f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409852&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-26</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,12 +697,50 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>מיקו אנג'ל &amp; ישראל שטרית - אמא אל תבכי קאבר</v>
+        <v>ליאור כהן - הצייר קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409851&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלו חנן - כל הדרך הביתה קאבר</v>
+        <v>שלמה דעוס - צעקתי בלילה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409858&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409894&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלו חנן - כל הדרך הביתה קאבר</v>
+        <v>שלמה דעוס - צעקתי בלילה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עילאי גניש - שכחת את הכל קאבר</v>
+        <v>נועם דדון - בכה כינור קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409857&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409893&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עילאי גניש - שכחת את הכל קאבר</v>
+        <v>נועם דדון - בכה כינור קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם דדון - שירו של צנחן קאבר</v>
+        <v>ליאור כהן - סיפור ישן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409856&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409892&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם דדון - שירו של צנחן קאבר</v>
+        <v>ליאור כהן - סיפור ישן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
+        <v>ליאור כהן - לב שבור לרסיסים קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409855&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409891&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
+        <v>ליאור כהן - לב שבור לרסיסים קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
+        <v>ליאור כהן - חלון לים התיכון קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409854&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409890&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
+        <v>ליאור כהן - חלון לים התיכון קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
+        <v>דניאל סעדון - באתי לגני קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-06</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409853&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409889&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליאור כהן - הצייר קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409852&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור כהן - הצייר קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409851&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
+        <v>דניאל סעדון - באתי לגני קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלמה דעוס - צעקתי בלילה קאבר</v>
+        <v>ניסים ניסן - מאושרת קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409894&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409941&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלמה דעוס - צעקתי בלילה קאבר</v>
+        <v>ניסים ניסן - מאושרת קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נועם דדון - בכה כינור קאבר</v>
+        <v>נדב קקון - ילדים של אלוקים קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409893&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409940&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נועם דדון - בכה כינור קאבר</v>
+        <v>נדב קקון - ילדים של אלוקים קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור כהן - סיפור ישן קאבר</v>
+        <v>ליאור כהן - חייל משמר הגבול קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409892&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409939&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור כהן - סיפור ישן קאבר</v>
+        <v>ליאור כהן - חייל משמר הגבול קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ליאור כהן - לב שבור לרסיסים קאבר</v>
+        <v>ליאור כהן - אבא קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409891&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409938&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ליאור כהן - לב שבור לרסיסים קאבר</v>
+        <v>ליאור כהן - אבא קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור כהן - חלון לים התיכון קאבר</v>
+        <v>יקיר לנקרי - כל הכח קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409890&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409937&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור כהן - חלון לים התיכון קאבר</v>
+        <v>יקיר לנקרי - כל הכח קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דניאל סעדון - באתי לגני קאבר</v>
+        <v>ינון אלהרר - דמייני קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409889&amp;sid=777f5398e0d54987117ada7c31c3a1c7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409936&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-07</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,164 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דניאל סעדון - באתי לגני קאבר</v>
+        <v>ינון אלהרר - דמייני קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>חנוך שובל - השיר שאת אהבת קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409935&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>חנוך שובל - השיר שאת אהבת קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אלרום יעקב - שוב חוזרת קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409934&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אלרום יעקב - שוב חוזרת קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלקנה אדרי &amp; שלום עברי - עומד בשער &amp; שמחות קטנות קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409933&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלקנה אדרי &amp; שלום עברי - עומד בשער &amp; שמחות קטנות קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אלון מיכאל - מלון בהוואי קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409932&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אלון מיכאל - מלון בהוואי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ניסים ניסן - מאושרת קאבר</v>
+        <v>נועם דדון - אני נשאר קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409941&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409990&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ניסים ניסן - מאושרת קאבר</v>
+        <v>נועם דדון - אני נשאר קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נדב קקון - ילדים של אלוקים קאבר</v>
+        <v>מיכאל כורש - אדם</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409940&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409989&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נדב קקון - ילדים של אלוקים קאבר</v>
+        <v>מיכאל כורש - אדם</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור כהן - חייל משמר הגבול קאבר</v>
+        <v>מאיר אלפי - ילד שלי קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409939&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409988&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור כהן - חייל משמר הגבול קאבר</v>
+        <v>מאיר אלפי - ילד שלי קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ליאור כהן - אבא קאבר</v>
+        <v>לידור יוסף - קחי אותי אלייך קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409938&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409987&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ליאור כהן - אבא קאבר</v>
+        <v>לידור יוסף - קחי אותי אלייך קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יקיר לנקרי - כל הכח קאבר</v>
+        <v>לידור יוסף - אתה הולך איתי קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409937&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409986&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יקיר לנקרי - כל הכח קאבר</v>
+        <v>לידור יוסף - אתה הולך איתי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ינון אלהרר - דמייני קאבר</v>
+        <v>לידור יוסף - אהיה לך בית קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409936&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409985&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ינון אלהרר - דמייני קאבר</v>
+        <v>לידור יוסף - אהיה לך בית קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>חנוך שובל - השיר שאת אהבת קאבר</v>
+        <v>יאיר יראי - ברגעים שאת הולכת &amp; נזכר בעיניה קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409935&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409984&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>חנוך שובל - השיר שאת אהבת קאבר</v>
+        <v>יאיר יראי - ברגעים שאת הולכת &amp; נזכר בעיניה קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אלרום יעקב - שוב חוזרת קאבר</v>
+        <v>דור שמר - מישל קאבר - גרסה עברית</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409934&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409983&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אלרום יעקב - שוב חוזרת קאבר</v>
+        <v>דור שמר - מישל קאבר - גרסה עברית</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלקנה אדרי &amp; שלום עברי - עומד בשער &amp; שמחות קטנות קאבר</v>
+        <v>אוראל מסיקה - אכבר גבר &amp; צונאמי קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409933&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409982&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,50 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלקנה אדרי &amp; שלום עברי - עומד בשער &amp; שמחות קטנות קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אלון מיכאל - מלון בהוואי קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409932&amp;sid=9faa59761d928bd79521face19c4dd2d</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אלון מיכאל - מלון בהוואי קאבר</v>
+        <v>אוראל מסיקה - אכבר גבר &amp; צונאמי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועם דדון - אני נשאר קאבר</v>
+        <v>שירז שוקרון - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409990&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410110&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועם דדון - אני נשאר קאבר</v>
+        <v>שירז שוקרון - לב לבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מיכאל כורש - אדם</v>
+        <v>שחר בן זקן - לב לבן קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409989&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410109&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מיכאל כורש - אדם</v>
+        <v>שחר בן זקן - לב לבן קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאיר אלפי - ילד שלי קאבר</v>
+        <v>רפא - Love Yourself Cover</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409988&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410108&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מאיר אלפי - ילד שלי קאבר</v>
+        <v>רפא - Love Yourself Cover</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>לידור יוסף - קחי אותי אלייך קאבר</v>
+        <v>עידו עמדור - כתובה בספרים קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409987&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410107&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>לידור יוסף - קחי אותי אלייך קאבר</v>
+        <v>עידו עמדור - כתובה בספרים קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לידור יוסף - אתה הולך איתי קאבר</v>
+        <v>מור שואף - תני לי לאהוב אותך קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409986&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410106&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>לידור יוסף - אתה הולך איתי קאבר</v>
+        <v>מור שואף - תני לי לאהוב אותך קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>לידור יוסף - אהיה לך בית קאבר</v>
+        <v>ליאל דגן - תגידי לי &amp; מלכת הדור קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409985&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410105&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>לידור יוסף - אהיה לך בית קאבר</v>
+        <v>ליאל דגן - תגידי לי &amp; מלכת הדור קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>יאיר יראי - ברגעים שאת הולכת &amp; נזכר בעיניה קאבר</v>
+        <v>יגאל עדי - מתגעגע קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409984&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410104&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>יאיר יראי - ברגעים שאת הולכת &amp; נזכר בעיניה קאבר</v>
+        <v>יגאל עדי - מתגעגע קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דור שמר - מישל קאבר - גרסה עברית</v>
+        <v>האחים כליף - אדם (מדאם) קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409983&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410103&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>דור שמר - מישל קאבר - גרסה עברית</v>
+        <v>האחים כליף - אדם (מדאם) קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אוראל מסיקה - אכבר גבר &amp; צונאמי קאבר</v>
+        <v>דניאל לוגסי - אהבת השם קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409982&amp;sid=63e223c9aa18bd6d1b95dc1debc44edb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410102&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,12 +773,506 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אוראל מסיקה - אכבר גבר &amp; צונאמי קאבר</v>
+        <v>דניאל לוגסי - אהבת השם קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ברטין - אבא סליחה טעיתי קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410101&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>ברטין - אבא סליחה טעיתי קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>בר אבירם - אפטרשוק קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410100&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>בר אבירם - אפטרשוק קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>בני אלבז &amp; אריה פרננד - ילדות נשכחת קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410099&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>בני אלבז &amp; אריה פרננד - ילדות נשכחת קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אלעד אביבי - מאשאפ אושר כהן</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410098&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אלעד אביבי - מאשאפ אושר כהן</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אליאן לוי - היא לא יודעת קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410097&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אליאן לוי - היא לא יודעת קאבר</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אלון מיכאל - מדוע חזרת קאבר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410096&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אלון מיכאל - מדוע חזרת קאבר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אלון מיכאל - אל תלכי קאבר</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410095&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אלון מיכאל - אל תלכי קאבר</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אושר אסרף - נשבע קאבר</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410094&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אושר אסרף - נשבע קאבר</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>אורי יונה - Mi Gna Cover</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410093&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>אורי יונה - Mi Gna Cover</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אהרון אזולאי &amp; אליהו כהן - שבת קאבר</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410092&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אהרון אזולאי &amp; אליהו כהן - שבת קאבר</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>אבירם כהן - שלווה בארמונותייך &amp; ניגון ברדיצ׳ב קאבר</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410091&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>אבירם כהן - שלווה בארמונותייך &amp; ניגון ברדיצ׳ב קאבר</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>אביחי טהיא - מתפלל קאבר</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410090&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>אביחי טהיא - מתפלל קאבר</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>אביב טל - אמא קאבר</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410089&amp;sid=903848668391b666aaff5c70f1cb5ac2</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>אביב טל - אמא קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור כהן - שתי אצבעות מצידון קאבר</v>
+        <v>חיים דבש - בלדה לשוטר קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410111&amp;sid=d9fde2e1eab8b08b2faa365bbd09a1de</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410216&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור כהן - שתי אצבעות מצידון קאבר</v>
+        <v>חיים דבש - בלדה לשוטר קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שלו חנן - אל נבקש קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410215&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שלו חנן - אל נבקש קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410214&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>פרחי ירושלים - מישל קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410213&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>פרחי ירושלים - מישל קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עמית בושארי - כוכבים קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410212&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עמית בושארי - כוכבים קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410211&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דודו אפגן - תמיד שמח קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410210&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דודו אפגן - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דניאל בן חיים - הכל זמני קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410209&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דניאל בן חיים - הכל זמני קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלעד אביבי - מדויק קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410208&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלעד אביבי - מדויק קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אושר גואטה - להינשא הלילה קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410207&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אושר גואטה - להינשא הלילה קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבישי עוזיאל - Forever Yang Cover</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410206&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבישי עוזיאל - Forever Yang Cover</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חיים דבש - בלדה לשוטר קאבר</v>
+        <v>יהונתן אברמוב - מציאות אחרת קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410216&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410230&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חיים דבש - בלדה לשוטר קאבר</v>
+        <v>יהונתן אברמוב - מציאות אחרת קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלו חנן - אל נבקש קאבר</v>
+        <v>שחר עזרא - אור האורות קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410215&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410229&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלו חנן - אל נבקש קאבר</v>
+        <v>שחר עזרא - אור האורות קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+        <v>שיר דוד גדסי - אעופה אשכונה קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410214&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410228&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קורל אמויאל - אהבה של כאב קאבר</v>
+        <v>שיר דוד גדסי - אעופה אשכונה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>פרחי ירושלים - מישל קאבר</v>
+        <v>רון ביטון - מדויק קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410213&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410227&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>פרחי ירושלים - מישל קאבר</v>
+        <v>רון ביטון - מדויק קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמית בושארי - כוכבים קאבר</v>
+        <v>עמנואל זאודה - מאשאפ והיא שעמדה &amp; ענווים</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410212&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410226&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עמית בושארי - כוכבים קאבר</v>
+        <v>עמנואל זאודה - מאשאפ והיא שעמדה &amp; ענווים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+        <v>ניב סעד - כל החלומות שלי קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410211&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410225&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נועם דדון - עד נשימתי האחרונה קאבר</v>
+        <v>ניב סעד - כל החלומות שלי קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דודו אפגן - תמיד שמח קאבר</v>
+        <v>טל עזאני - עכשיו לצעוק קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410210&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410224&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דודו אפגן - תמיד שמח קאבר</v>
+        <v>טל עזאני - עכשיו לצעוק קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דניאל בן חיים - הכל זמני קאבר</v>
+        <v>הודיה אבני - לב לבן קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410209&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410223&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>דניאל בן חיים - הכל זמני קאבר</v>
+        <v>הודיה אבני - לב לבן קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלעד אביבי - מדויק קאבר</v>
+        <v>גיל אוליאל - נפש תאומה קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410208&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410222&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלעד אביבי - מדויק קאבר</v>
+        <v>גיל אוליאל - נפש תאומה קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אושר גואטה - להינשא הלילה קאבר</v>
+        <v>גבריאל שרם - לב לבן בשילוב תפילה קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410207&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410221&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אושר גואטה - להינשא הלילה קאבר</v>
+        <v>גבריאל שרם - לב לבן בשילוב תפילה קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אבישי עוזיאל - Forever Yang Cover</v>
+        <v>אסף לוי - נוסע למיאמי קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410206&amp;sid=087020e8f879cbe60cf66850a72e1c53</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410220&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,12 +849,88 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אבישי עוזיאל - Forever Yang Cover</v>
+        <v>אסף לוי - נוסע למיאמי קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אושר לוי - גבר משתגע קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410219&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אושר לוי - גבר משתגע קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אהרון אזולאי &amp; אליהו כהן - עלה קטן שלי קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410218&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אהרון אזולאי &amp; אליהו כהן - עלה קטן שלי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהונתן אברמוב - מציאות אחרת קאבר</v>
+        <v>להקת נשמחה - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410230&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410320&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהונתן אברמוב - מציאות אחרת קאבר</v>
+        <v>להקת נשמחה - לב לבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שחר עזרא - אור האורות קאבר</v>
+        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410229&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410319&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שחר עזרא - אור האורות קאבר</v>
+        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שיר דוד גדסי - אעופה אשכונה קאבר</v>
+        <v>אריאל עדן - הוויה קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410228&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410318&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שיר דוד גדסי - אעופה אשכונה קאבר</v>
+        <v>אריאל עדן - הוויה קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רון ביטון - מדויק קאבר</v>
+        <v>אליאור נונה - שבע בערב קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410227&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410317&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>רון ביטון - מדויק קאבר</v>
+        <v>אליאור נונה - שבע בערב קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמנואל זאודה - מאשאפ והיא שעמדה &amp; ענווים</v>
+        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410226&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410316&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עמנואל זאודה - מאשאפ והיא שעמדה &amp; ענווים</v>
+        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ניב סעד - כל החלומות שלי קאבר</v>
+        <v>אברהם דהאן - בשורות טובות קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410225&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410315&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-28</v>
+        <v>2026-04-01</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,278 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ניב סעד - כל החלומות שלי קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>טל עזאני - עכשיו לצעוק קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410224&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>טל עזאני - עכשיו לצעוק קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>הודיה אבני - לב לבן קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410223&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>הודיה אבני - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>גיל אוליאל - נפש תאומה קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410222&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>גיל אוליאל - נפש תאומה קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>גבריאל שרם - לב לבן בשילוב תפילה קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410221&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>גבריאל שרם - לב לבן בשילוב תפילה קאבר</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אסף לוי - נוסע למיאמי קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410220&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אסף לוי - נוסע למיאמי קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אושר לוי - גבר משתגע קאבר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410219&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אושר לוי - גבר משתגע קאבר</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אהרון אזולאי &amp; אליהו כהן - עלה קטן שלי קאבר</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410218&amp;sid=d786fba9def7fc02eff01a39eb78cac5</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אהרון אזולאי &amp; אליהו כהן - עלה קטן שלי קאבר</v>
+        <v>אברהם דהאן - בשורות טובות קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>להקת נשמחה - לב לבן קאבר</v>
+        <v>נויה ערבה - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410320&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410357&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>להקת נשמחה - לב לבן קאבר</v>
+        <v>נויה ערבה - לב לבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
+        <v>מתן חבקוק - והיא שעמדה קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410319&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410356&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>חביב חיים בן אריה - יוצא לאור קאבר</v>
+        <v>מתן חבקוק - והיא שעמדה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אריאל עדן - הוויה קאבר</v>
+        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410318&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410353&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,126 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אריאל עדן - הוויה קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>אליאור נונה - שבע בערב קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410317&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>אליאור נונה - שבע בערב קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410316&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אדיר ניזרי - דקלון ובית''ר - גרסת האוהדים</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אברהם דהאן - בשורות טובות קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410315&amp;sid=9ddf9caaab80e46f7790a438dc9f07e9</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אברהם דהאן - בשורות טובות קאבר</v>
+        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נויה ערבה - לב לבן קאבר</v>
+        <v>חגית ביטון חג'בי - תפילות קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410357&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410382&amp;sid=d001edcec81b3dfe9262a7ef1c4df041</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נויה ערבה - לב לבן קאבר</v>
+        <v>חגית ביטון חג'בי - תפילות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מתן חבקוק - והיא שעמדה קאבר</v>
+        <v>אביחי טהיא - לבחור נכון קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410356&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410377&amp;sid=d001edcec81b3dfe9262a7ef1c4df041</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,50 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מתן חבקוק - והיא שעמדה קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410353&amp;sid=98dc1c04e8e9667665107f61648b9751</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דניאל שם-טוב - מה אני רוצה באמת קאבר</v>
+        <v>אביחי טהיא - לבחור נכון קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חגית ביטון חג'בי - תפילות קאבר</v>
+        <v>רמי - מלכת הדור קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410382&amp;sid=d001edcec81b3dfe9262a7ef1c4df041</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410411&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חגית ביטון חג'בי - תפילות קאבר</v>
+        <v>רמי - מלכת הדור קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אביחי טהיא - לבחור נכון קאבר</v>
+        <v>רונן לוגסי - רחקי מכולם קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410377&amp;sid=d001edcec81b3dfe9262a7ef1c4df041</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410410&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,164 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אביחי טהיא - לבחור נכון קאבר</v>
+        <v>רונן לוגסי - רחקי מכולם קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רונן לוגסי - לא אבגוד יותר ילדה קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410409&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רונן לוגסי - לא אבגוד יותר ילדה קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נהוראי מלאכי - לב לבן קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410408&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נהוראי מלאכי - לב לבן קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יהונתן לוי - לב לבן קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410407&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יהונתן לוי - לב לבן קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אייל אלוש - סתכלי למעלה קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410406&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אייל אלוש - סתכלי למעלה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רמי - מלכת הדור קאבר</v>
+        <v>אביחיל איטח - אנא בכח קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410411&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410439&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רמי - מלכת הדור קאבר</v>
+        <v>אביחיל איטח - אנא בכח קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רונן לוגסי - רחקי מכולם קאבר</v>
+        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410410&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410433&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,164 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רונן לוגסי - רחקי מכולם קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רונן לוגסי - לא אבגוד יותר ילדה קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410409&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רונן לוגסי - לא אבגוד יותר ילדה קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נהוראי מלאכי - לב לבן קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410408&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נהוראי מלאכי - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יהונתן לוי - לב לבן קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410407&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יהונתן לוי - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אייל אלוש - סתכלי למעלה קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410406&amp;sid=5282030c474d06c8d3f47f55125499bf</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אייל אלוש - סתכלי למעלה קאבר</v>
+        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביחיל איטח - אנא בכח קאבר</v>
+        <v>שחר יעקב - בית מזכוכית - גרסת היוצר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410439&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410462&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביחיל איטח - אנא בכח קאבר</v>
+        <v>שחר יעקב - בית מזכוכית - גרסת היוצר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
+        <v>לינוי אוחנה - הכל שתיקות קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410433&amp;sid=63c03b012cb2d5e2b320a1be7c6a54f9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410461&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,316 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אייל אלוש - בואי &amp; ציון קאבר</v>
+        <v>לינוי אוחנה - הכל שתיקות קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יקיר יהודה יאיר - השב זכה וברה - גרסה ווקאלית</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410460&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יקיר יהודה יאיר - השב זכה וברה - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יוסי בר - יום חדש עולה על צה''ל קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410459&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יוסי בר - יום חדש עולה על צה''ל קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>חמוטל - בדד קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410458&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>חמוטל - בדד קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אלרום יעקב - התמונות שבאלבום קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410457&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אלרום יעקב - התמונות שבאלבום קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלעד אביבי - אין לי בט איתך קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410456&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלעד אביבי - אין לי בט איתך קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אליה לוי - הלוואי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410455&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אליה לוי - הלוואי קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אור חרזי - שיר בעיפרון קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410454&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אור חרזי - שיר בעיפרון קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אופיר לוי &amp; ינאי בן חמו - כמה אהבה &amp; קחי אותי אלייך</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410453&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אופיר לוי &amp; ינאי בן חמו - כמה אהבה &amp; קחי אותי אלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר יעקב - בית מזכוכית - גרסת היוצר</v>
+        <v>שלומי ברק מארח את סהר כרמלי - חי קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410462&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410487&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר יעקב - בית מזכוכית - גרסת היוצר</v>
+        <v>שלומי ברק מארח את סהר כרמלי - חי קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>לינוי אוחנה - הכל שתיקות קאבר</v>
+        <v>שחר לוטטי - Ginete Cover</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410461&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410486&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>לינוי אוחנה - הכל שתיקות קאבר</v>
+        <v>שחר לוטטי - Ginete Cover</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יקיר יהודה יאיר - השב זכה וברה - גרסה ווקאלית</v>
+        <v>רותם הכהן - אפר ואבק קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410460&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410485&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יקיר יהודה יאיר - השב זכה וברה - גרסה ווקאלית</v>
+        <v>רותם הכהן - אפר ואבק קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יוסי בר - יום חדש עולה על צה''ל קאבר</v>
+        <v>עידו עמדור - ביום ובלילה קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410459&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410484&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יוסי בר - יום חדש עולה על צה''ל קאבר</v>
+        <v>עידו עמדור - ביום ובלילה קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חמוטל - בדד קאבר</v>
+        <v>יוסי רביב - מקלט לדמעותיי קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410458&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410483&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,202 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חמוטל - בדד קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אלרום יעקב - התמונות שבאלבום קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410457&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אלרום יעקב - התמונות שבאלבום קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלעד אביבי - אין לי בט איתך קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410456&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלעד אביבי - אין לי בט איתך קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אליה לוי - הלוואי קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410455&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אליה לוי - הלוואי קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אור חרזי - שיר בעיפרון קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410454&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אור חרזי - שיר בעיפרון קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אופיר לוי &amp; ינאי בן חמו - כמה אהבה &amp; קחי אותי אלייך</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410453&amp;sid=70c833b25a9f0d118babf72b883089a2</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אופיר לוי &amp; ינאי בן חמו - כמה אהבה &amp; קחי אותי אלייך</v>
+        <v>יוסי רביב - מקלט לדמעותיי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ברק מארח את סהר כרמלי - חי קאבר</v>
+        <v>ברטין - Belki Cover</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410487&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410508&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ברק מארח את סהר כרמלי - חי קאבר</v>
+        <v>ברטין - Belki Cover</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שחר לוטטי - Ginete Cover</v>
+        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410486&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410507&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שחר לוטטי - Ginete Cover</v>
+        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רותם הכהן - אפר ואבק קאבר</v>
+        <v>אליאור נונה - בי נשבעתי קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410485&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410506&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רותם הכהן - אפר ואבק קאבר</v>
+        <v>אליאור נונה - בי נשבעתי קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עידו עמדור - ביום ובלילה קאבר</v>
+        <v>אופק לוי - מהרגע הראשון קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410484&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410505&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עידו עמדור - ביום ובלילה קאבר</v>
+        <v>אופק לוי - מהרגע הראשון קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסי רביב - מקלט לדמעותיי קאבר</v>
+        <v>אביב חרזי - יפה כלבנה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410483&amp;sid=d14fa1900eda8196d972a3449b0a0db6</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410504&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,12 +621,50 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסי רביב - מקלט לדמעותיי קאבר</v>
+        <v>אביב חרזי - יפה כלבנה קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410503&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ברטין - Belki Cover</v>
+        <v>אליה שטרית - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410508&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410516&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ברטין - Belki Cover</v>
+        <v>אליה שטרית - לב לבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
+        <v>ישראל שרביט - לב ליבי קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410507&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410515&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בנימין ברון &amp; מוריאל - בן שלך מלך קאבר</v>
+        <v>ישראל שרביט - לב ליבי קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אליאור נונה - בי נשבעתי קאבר</v>
+        <v>אבירם כהן - לב לבן קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410506&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410514&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אליאור נונה - בי נשבעתי קאבר</v>
+        <v>אבירם כהן - לב לבן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אופק לוי - מהרגע הראשון קאבר</v>
+        <v>שירה שוורץ - תקופה חרא קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410505&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410513&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אופק לוי - מהרגע הראשון קאבר</v>
+        <v>שירה שוורץ - תקופה חרא קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אביב חרזי - יפה כלבנה קאבר</v>
+        <v>שיר אסייג - את המחר שלי קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410504&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410512&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-17</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אביב חרזי - יפה כלבנה קאבר</v>
+        <v>שיר אסייג - את המחר שלי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
+        <v>עילאי אהרוני - כשאלך קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410503&amp;sid=b24407a44a4ec297dc30a0cea8cfeb7e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410511&amp;sid=c8a3f687dc532662677681ba737935f0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-17</v>
@@ -659,12 +659,88 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אביאל קוגן - מאשאפ אלייך + מצייר אותך</v>
+        <v>עילאי אהרוני - כשאלך קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ליאור כהן - השיר האחרון קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410510&amp;sid=c8a3f687dc532662677681ba737935f0</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ליאור כהן - השיר האחרון קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>טליה אייזנקוט - לב לבן קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410509&amp;sid=c8a3f687dc532662677681ba737935f0</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>טליה אייזנקוט - לב לבן קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אליה שטרית - לב לבן קאבר</v>
+        <v>נאור בן דוד - תודה על הכל קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410516&amp;sid=c8a3f687dc532662677681ba737935f0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410518&amp;sid=61eedd5bd59ee327b8582a6c9bd3efd8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אליה שטרית - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ישראל שרביט - לב ליבי קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410515&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ישראל שרביט - לב ליבי קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אבירם כהן - לב לבן קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410514&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אבירם כהן - לב לבן קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שירה שוורץ - תקופה חרא קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410513&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שירה שוורץ - תקופה חרא קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>שיר אסייג - את המחר שלי קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410512&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>שיר אסייג - את המחר שלי קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>עילאי אהרוני - כשאלך קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410511&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>עילאי אהרוני - כשאלך קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליאור כהן - השיר האחרון קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410510&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור כהן - השיר האחרון קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>טליה אייזנקוט - לב לבן קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410509&amp;sid=c8a3f687dc532662677681ba737935f0</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>טליה אייזנקוט - לב לבן קאבר</v>
+        <v>נאור בן דוד - תודה על הכל קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נאור בן דוד - תודה על הכל קאבר</v>
+        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410518&amp;sid=61eedd5bd59ee327b8582a6c9bd3efd8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410539&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נאור בן דוד - תודה על הכל קאבר</v>
+        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>איתי עמר - אהובתי קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410533&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>איתי עמר - אהובתי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
+        <v>עומרי פרחן - גיבורים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410539&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410561&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור מזרחי - מקלט לדמעותיי קאבר</v>
+        <v>עומרי פרחן - גיבורים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>איתי עמר - אהובתי קאבר</v>
+        <v>יהב חדד - החול יזכור קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410533&amp;sid=2ed35c4ba0b7bddf7b481a8419bf43c4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410560&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,240 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>איתי עמר - אהובתי קאבר</v>
+        <v>יהב חדד - החול יזכור קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>בן ימין - את ההוכחה שיש אלוהים קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410559&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>בן ימין - את ההוכחה שיש אלוהים קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אילאי גואריהן - המכתב האחרון קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410558&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אילאי גואריהן - המכתב האחרון קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אילאי ברדה - כאב של לוחמים קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410557&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אילאי ברדה - כאב של לוחמים קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אבישי לוי - כאב של לוחמים קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410556&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אבישי לוי - כאב של לוחמים קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אבירם ברמי &amp; יובל בדלין - כל החיילים חוזרים הביתה קאבר הורדה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410555&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אבירם ברמי &amp; יובל בדלין - כל החיילים חוזרים הביתה קאבר הורדה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אבירם ברמי - ארץ צבי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410554&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אבירם ברמי - ארץ צבי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומרי פרחן - גיבורים קאבר</v>
+        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410561&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410585&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומרי פרחן - גיבורים קאבר</v>
+        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהב חדד - החול יזכור קאבר</v>
+        <v>קורין גמליאל - יהיה בסדר קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410560&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410581&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהב חדד - החול יזכור קאבר</v>
+        <v>קורין גמליאל - יהיה בסדר קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>בן ימין - את ההוכחה שיש אלוהים קאבר</v>
+        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410559&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410580&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-21</v>
+        <v>2026-04-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,202 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>בן ימין - את ההוכחה שיש אלוהים קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>אילאי גואריהן - המכתב האחרון קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410558&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>אילאי גואריהן - המכתב האחרון קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אילאי ברדה - כאב של לוחמים קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410557&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אילאי ברדה - כאב של לוחמים קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אבישי לוי - כאב של לוחמים קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410556&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אבישי לוי - כאב של לוחמים קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אבירם ברמי &amp; יובל בדלין - כל החיילים חוזרים הביתה קאבר הורדה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410555&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אבירם ברמי &amp; יובל בדלין - כל החיילים חוזרים הביתה קאבר הורדה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אבירם ברמי - ארץ צבי קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410554&amp;sid=f953034c531e8dec5617bebde01f7d9c</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אבירם ברמי - ארץ צבי קאבר</v>
+        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
+        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410585&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410606&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
+        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קורין גמליאל - יהיה בסדר קאבר</v>
+        <v>אהרון כהן - תקופה חרא קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410581&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410605&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קורין גמליאל - יהיה בסדר קאבר</v>
+        <v>אהרון כהן - תקופה חרא קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
+        <v>אהרון כהן - לב לבן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410580&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410604&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,12 +545,50 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
+        <v>אהרון כהן - לב לבן קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אהרון כהן - יפה בלבן קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410603&amp;sid=b930a72629ecb842626bba50456fa521</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אהרון כהן - יפה בלבן קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
+        <v>נועה שירי - לב שבור קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410606&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410638&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
+        <v>נועה שירי - לב שבור קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אהרון כהן - תקופה חרא קאבר</v>
+        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410605&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410637&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אהרון כהן - תקופה חרא קאבר</v>
+        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אהרון כהן - לב לבן קאבר</v>
+        <v>דנה חן - אהובי קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410604&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410636&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אהרון כהן - לב לבן קאבר</v>
+        <v>דנה חן - אהובי קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אהרון כהן - יפה בלבן קאבר</v>
+        <v>גליה - יש לי חלום קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410603&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410635&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אהרון כהן - יפה בלבן קאבר</v>
+        <v>גליה - יש לי חלום קאבר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה שירי - לב שבור קאבר</v>
+        <v>שיר בלעיש - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410638&amp;sid=a402efda2c448b65e7157027e659573c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410639&amp;sid=8e6f38dfc3c99a038eabbdc986840695</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה שירי - לב שבור קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410637&amp;sid=a402efda2c448b65e7157027e659573c</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דנה חן - אהובי קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410636&amp;sid=a402efda2c448b65e7157027e659573c</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דנה חן - אהובי קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>גליה - יש לי חלום קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410635&amp;sid=a402efda2c448b65e7157027e659573c</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>גליה - יש לי חלום קאבר</v>
+        <v>שיר בלעיש - לב לבן קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר בלעיש - לב לבן קאבר</v>
+        <v>רוני יחיא - שלווה בארמונותייך קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410639&amp;sid=8e6f38dfc3c99a038eabbdc986840695</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410644&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-28</v>
@@ -469,12 +469,126 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר בלעיש - לב לבן קאבר</v>
+        <v>רוני יחיא - שלווה בארמונותייך קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עדן ששון - תמיד שמח קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410643&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עדן ששון - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נויה לוי - אליס קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410642&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נויה לוי - אליס קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אפריים פייסחוב - אהבה אמיתית קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410641&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אפריים פייסחוב - אהבה אמיתית קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רוני יחיא - שלווה בארמונותייך קאבר</v>
+        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410644&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410665&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רוני יחיא - שלווה בארמונותייך קאבר</v>
+        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עדן ששון - תמיד שמח קאבר</v>
+        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410643&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410663&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עדן ששון - תמיד שמח קאבר</v>
+        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נויה לוי - אליס קאבר</v>
+        <v>אוראל מנצור - האיש ההוא קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410642&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410658&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נויה לוי - אליס קאבר</v>
+        <v>אוראל מנצור - האיש ההוא קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אפריים פייסחוב - אהבה אמיתית קאבר</v>
+        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410641&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410657&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אפריים פייסחוב - אהבה אמיתית קאבר</v>
+        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
+        <v>יעקב מלכי - שעות לא שעות קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410665&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410683&amp;sid=27bae473bfbefcf3b372051115b6e45a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
+        <v>יעקב מלכי - שעות לא שעות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
+        <v>גל וקנין - שלווה בארמונתייך קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410663&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410680&amp;sid=27bae473bfbefcf3b372051115b6e45a</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,88 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אוראל מנצור - האיש ההוא קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410658&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אוראל מנצור - האיש ההוא קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410657&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
+        <v>גל וקנין - שלווה בארמונתייך קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יעקב מלכי - שעות לא שעות קאבר</v>
+        <v>נריה ביבי - משהו בי נשבר קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-08</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410683&amp;sid=27bae473bfbefcf3b372051115b6e45a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410778&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-08</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יעקב מלכי - שעות לא שעות קאבר</v>
+        <v>נריה ביבי - משהו בי נשבר קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>גל וקנין - שלווה בארמונתייך קאבר</v>
+        <v>נועם דדון - הלב צמא קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-08</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410680&amp;sid=27bae473bfbefcf3b372051115b6e45a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410777&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-08</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,316 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>גל וקנין - שלווה בארמונתייך קאבר</v>
+        <v>נועם דדון - הלב צמא קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>כפיר אלקיים - תשאירי לי מקום לחבק אותך קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410776&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>כפיר אלקיים - תשאירי לי מקום לחבק אותך קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ינון אלהרר - אני לא מדונה קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410775&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ינון אלהרר - אני לא מדונה קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יגאל עדי - את לא שמה קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410774&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יגאל עדי - את לא שמה קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אלעד אביבי - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410773&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אלעד אביבי - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אליהו חזן - אני העבד קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410772&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אליהו חזן - אני העבד קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אילון לוי - ילדה מבורכת קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410771&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אילון לוי - ילדה מבורכת קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אדיר בוסטז &amp; יוסף מהצרי - לא אשכחך ירושלים קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410770&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אדיר בוסטז &amp; יוסף מהצרי - לא אשכחך ירושלים קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אבישי לוי - תמיד אמא קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410769&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אבישי לוי - תמיד אמא קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נריה ביבי - משהו בי נשבר קאבר</v>
+        <v>תאי חבאני - נווה הדרים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410778&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410855&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נריה ביבי - משהו בי נשבר קאבר</v>
+        <v>תאי חבאני - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נועם דדון - הלב צמא קאבר</v>
+        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410777&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410854&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נועם דדון - הלב צמא קאבר</v>
+        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>כפיר אלקיים - תשאירי לי מקום לחבק אותך קאבר</v>
+        <v>צליל אבקסיס - לב לבן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410776&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410853&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>כפיר אלקיים - תשאירי לי מקום לחבק אותך קאבר</v>
+        <v>צליל אבקסיס - לב לבן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ינון אלהרר - אני לא מדונה קאבר</v>
+        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410775&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410852&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ינון אלהרר - אני לא מדונה קאבר</v>
+        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יגאל עדי - את לא שמה קאבר</v>
+        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410774&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410851&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יגאל עדי - את לא שמה קאבר</v>
+        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אלעד אביבי - עיניים עצובות קאבר</v>
+        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410773&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410850&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אלעד אביבי - עיניים עצובות קאבר</v>
+        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אליהו חזן - אני העבד קאבר</v>
+        <v>ליאור כהן - אהובה קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410772&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410849&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אליהו חזן - אני העבד קאבר</v>
+        <v>ליאור כהן - אהובה קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אילון לוי - ילדה מבורכת קאבר</v>
+        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410771&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410848&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אילון לוי - ילדה מבורכת קאבר</v>
+        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אדיר בוסטז &amp; יוסף מהצרי - לא אשכחך ירושלים קאבר</v>
+        <v>הקצב של המזרח - ציפור זרה קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410770&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410847&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אדיר בוסטז &amp; יוסף מהצרי - לא אשכחך ירושלים קאבר</v>
+        <v>הקצב של המזרח - ציפור זרה קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבישי לוי - תמיד אמא קאבר</v>
+        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410769&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410846&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,164 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבישי לוי - תמיד אמא קאבר</v>
+        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אסף פפל - איפה את קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410845&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אסף פפל - איפה את קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410844&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410843&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410842&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תאי חבאני - נווה הדרים קאבר</v>
+        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410855&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410861&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-13</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תאי חבאני - נווה הדרים קאבר</v>
+        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
+        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410854&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410860&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-13</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
+        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>צליל אבקסיס - לב לבן קאבר</v>
+        <v>משה כהן - אהבת עולם קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410853&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410859&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-13</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>צליל אבקסיס - לב לבן קאבר</v>
+        <v>משה כהן - אהבת עולם קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
+        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410852&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410858&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-13</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
+        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
+        <v>ליאור כהן - תפילה קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410851&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410857&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-13</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
+        <v>ליאור כהן - תפילה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
+        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410850&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410856&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-13</v>
@@ -659,316 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליאור כהן - אהובה קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410849&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור כהן - אהובה קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410848&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>הקצב של המזרח - ציפור זרה קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410847&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>הקצב של המזרח - ציפור זרה קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410846&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אסף פפל - איפה את קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410845&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אסף פפל - איפה את קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410844&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410843&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410842&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
+        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
+        <v>נוריאל חדד - מה לך ילדה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410861&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410865&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
+        <v>נוריאל חדד - מה לך ילדה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
+        <v>קובי יעקובוב - היית לי שקט קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410860&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410864&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
+        <v>קובי יעקובוב - היית לי שקט קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>משה כהן - אהבת עולם קאבר</v>
+        <v>לירז מדיזדה - חצי לב קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410859&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410863&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>משה כהן - אהבת עולם קאבר</v>
+        <v>לירז מדיזדה - חצי לב קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
+        <v>ינון אלהרר - עיניים עצובות קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410858&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410862&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,88 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ליאור כהן - תפילה קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410857&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ליאור כהן - תפילה קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410856&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
+        <v>ינון אלהרר - עיניים עצובות קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נוריאל חדד - מה לך ילדה קאבר</v>
+        <v>ליאור קקון - ירושלים של זהב קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-15</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410865&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410890&amp;sid=513c45e169eaf116aa2433598953ea9f</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-15</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נוריאל חדד - מה לך ילדה קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>קובי יעקובוב - היית לי שקט קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410864&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>קובי יעקובוב - היית לי שקט קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>לירז מדיזדה - חצי לב קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410863&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>לירז מדיזדה - חצי לב קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ינון אלהרר - עיניים עצובות קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410862&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>ינון אלהרר - עיניים עצובות קאבר</v>
+        <v>ליאור קקון - ירושלים של זהב קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור קקון - ירושלים של זהב קאבר</v>
+        <v>קובי צור - לאן קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410890&amp;sid=513c45e169eaf116aa2433598953ea9f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410986&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-22</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,620 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור קקון - ירושלים של זהב קאבר</v>
+        <v>קובי צור - לאן קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>צביקה חי - עטלף עיוור קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410985&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>צביקה חי - עטלף עיוור קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עפרה &amp; עידן עינב - ירושלים של זהב קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410984&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עפרה &amp; עידן עינב - ירושלים של זהב קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עמיחי שרעבי - לב לבן קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410983&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עמיחי שרעבי - לב לבן קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נוריאל פיאמנטה - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410982&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נוריאל פיאמנטה - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מתנאל סבח - בית מזכוכית קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410981&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מתנאל סבח - בית מזכוכית קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מתן סממה - נווה הדרים קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410980&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מתן סממה - נווה הדרים קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מירב ארז - מונו קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410979&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מירב ארז - מונו קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מאי היגאני - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410978&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מאי היגאני - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ליאור לוי - נדלקתי נערה קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410977&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>ליאור לוי - נדלקתי נערה קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יוסף חיים - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410976&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יוסף חיים - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>טל לוי &amp; ברטין - חלף הגעגוע קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410975&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>טל לוי &amp; ברטין - חלף הגעגוע קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>חיים דדון - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410974&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>חיים דדון - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>דליה מזרחי - נפש תאומה קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410973&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>דליה מזרחי - נפש תאומה קאבר</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אליאור נונה - סיגליות קאבר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410972&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אליאור נונה - סיגליות קאבר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אורית יצחק - חי קאבר</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410971&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אורית יצחק - חי קאבר</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אורי ראובני - עוד ישמע קאבר</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410970&amp;sid=0c663eec05b5a7d50c6538af1e240981</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אורי ראובני - עוד ישמע קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בניטה - אכאב בשקט קאבר</v>
+        <v>אביחי טהיא - אל נבקש קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410989&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410990&amp;sid=ffec9639250a4b1c014231eebf5db17d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בניטה - אכאב בשקט קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רונן לוגסי - אבא יקר קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410988&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רונן לוגסי - אבא יקר קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410987&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
+        <v>אביחי טהיא - אל נבקש קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביחי טהיא - אל נבקש קאבר</v>
+        <v>טודיאל - חדר מסתובב קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410990&amp;sid=ffec9639250a4b1c014231eebf5db17d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411086&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,430 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביחי טהיא - אל נבקש קאבר</v>
+        <v>טודיאל - חדר מסתובב קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רון דבוש - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411082&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רון דבוש - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתי יהב - אחות קטנה קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411081&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתי יהב - אחות קטנה קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נריה שריה עדני - אהובתי קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411080&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נריה שריה עדני - אהובתי קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מימון בן שושן - תני ללכת קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411079&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מימון בן שושן - תני ללכת קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מימון בן שושן - אהבה בת 20 קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411078&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מימון בן שושן - אהבה בת 20 קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יהונתן גד נגר - רוקד עם הכאב קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411077&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יהונתן גד נגר - רוקד עם הכאב קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יאיר כהן - רעשים קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411076&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יאיר כהן - רעשים קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בן גורן - בואי בשלום קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411075&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בן גורן - בואי בשלום קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אפיק מרחום - פרחים מנייר קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411074&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אפיק מרחום - פרחים מנייר קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אליאור איצקוביץ׳ כהן - אליך אלוהיי קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411073&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אליאור איצקוביץ׳ כהן - אליך אלוהיי קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אושר פלמן - מכל האהבות קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411072&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אושר פלמן - מכל האהבות קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>טודיאל - חדר מסתובב קאבר</v>
+        <v>שלומי הלימי - נווה הדרים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411086&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411199&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>טודיאל - חדר מסתובב קאבר</v>
+        <v>שלומי הלימי - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון דבוש - עיניים עצובות קאבר</v>
+        <v>שיר לוי - פרחים מנייר קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411082&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411198&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון דבוש - עיניים עצובות קאבר</v>
+        <v>שיר לוי - פרחים מנייר קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתי יהב - אחות קטנה קאבר</v>
+        <v>שילת סופר - נווה הדרים קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411081&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411197&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתי יהב - אחות קטנה קאבר</v>
+        <v>שילת סופר - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נריה שריה עדני - אהובתי קאבר</v>
+        <v>שי עמר - את יפה קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411080&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411196&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נריה שריה עדני - אהובתי קאבר</v>
+        <v>שי עמר - את יפה קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מימון בן שושן - תני ללכת קאבר</v>
+        <v>רפא' - מאשאפ בואי &amp; ציון</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411079&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411195&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מימון בן שושן - תני ללכת קאבר</v>
+        <v>רפא' - מאשאפ בואי &amp; ציון</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מימון בן שושן - אהבה בת 20 קאבר</v>
+        <v>בנימין עזר &amp; דוד עזר - קולות קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411078&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411194&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מימון בן שושן - אהבה בת 20 קאבר</v>
+        <v>בנימין עזר &amp; דוד עזר - קולות קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>יהונתן גד נגר - רוקד עם הכאב קאבר</v>
+        <v>רזיאל עורקבי - נווה הדרים קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411077&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411193&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>יהונתן גד נגר - רוקד עם הכאב קאבר</v>
+        <v>רזיאל עורקבי - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יאיר כהן - רעשים קאבר</v>
+        <v>רביד שלו - גן עדן קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411076&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411192&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>יאיר כהן - רעשים קאבר</v>
+        <v>רביד שלו - גן עדן קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>בן גורן - בואי בשלום קאבר</v>
+        <v>עומר יונה - לא תשבור אותי קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411075&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411191&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>בן גורן - בואי בשלום קאבר</v>
+        <v>עומר יונה - לא תשבור אותי קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אפיק מרחום - פרחים מנייר קאבר</v>
+        <v>נתנאל ואנונו - נווה הדרים קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411074&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411190&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אפיק מרחום - פרחים מנייר קאבר</v>
+        <v>נתנאל ואנונו - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אליאור איצקוביץ׳ כהן - אליך אלוהיי קאבר</v>
+        <v>נתי כהן - בראשית עולם קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411073&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411189&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אליאור איצקוביץ׳ כהן - אליך אלוהיי קאבר</v>
+        <v>נתי כהן - בראשית עולם קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אושר פלמן - מכל האהבות קאבר</v>
+        <v>נועם דדון - שיר לערב חג קאבר</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411072&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411188&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,12 +887,202 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אושר פלמן - מכל האהבות קאבר</v>
+        <v>נועם דדון - שיר לערב חג קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>לינוי הגג - הכל שתיקות קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411186&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>לינוי הגג - הכל שתיקות קאבר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>לביא לוי - נווה הדרים קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411184&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>לביא לוי - נווה הדרים קאבר</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>יאיר ברוך - נווה הדרים קאבר</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411183&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>יאיר ברוך - נווה הדרים קאבר</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אילון לוי - עוד ישמע קאבר</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411181&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אילון לוי - עוד ישמע קאבר</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אבישי עוזיאל - מחזיק לך תיד קאבר</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411180&amp;sid=a85ca8ef30bfde649d428d952bc8fa37</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אבישי עוזיאל - מחזיק לך תיד קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אבישי עוזיאל - חצי לב קאבר</v>
+        <v>עילאי גניש - השריטה שלי קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411200&amp;sid=95591e0ceb4fc6da844103df3a206d98</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411275&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-08</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,126 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אבישי עוזיאל - חצי לב קאבר</v>
+        <v>עילאי גניש - השריטה שלי קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ליהיא - לב לבן קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411274&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ליהיא - לב לבן קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יעקב הראל - ככה באמת קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411273&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יעקב הראל - ככה באמת קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אפיק מרחום - אני רוצה קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411272&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אפיק מרחום - אני רוצה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>